--- a/Financial Analysis/CRSR.xlsx
+++ b/Financial Analysis/CRSR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE76D48-2E8B-4AE6-8C6E-0D0E81DCFECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DAD6A3-8B53-4998-88BF-3A458FF519B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{D4154116-B837-4443-B5D0-8DB112D6F8D0}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="85">
   <si>
     <t>CRSR</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>NPV (FCF)</t>
+  </si>
+  <si>
+    <t>Provisions</t>
   </si>
 </sst>
 </file>
@@ -424,15 +427,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -448,7 +451,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15179040" y="0"/>
+          <a:off x="16398240" y="0"/>
           <a:ext cx="0" cy="9403080"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -482,7 +485,7 @@
     <xdr:to>
       <xdr:col>37</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -847,17 +850,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>7.37</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="E3" s="3">
-        <v>45751</v>
+        <v>45898</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45751</v>
+        <v>45898</v>
       </c>
       <c r="G3" s="3">
-        <v>45777</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
@@ -865,11 +868,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="4">
-        <f>104.9</f>
-        <v>104.9</v>
+        <f>106</f>
+        <v>106</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
@@ -878,7 +881,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>773.11300000000006</v>
+        <v>941.28000000000009</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
@@ -886,11 +889,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <f>109.4</f>
-        <v>109.4</v>
+        <f>104.6+2.6</f>
+        <v>107.19999999999999</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
@@ -898,11 +901,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="4">
-        <f>12.2+161.3</f>
-        <v>173.5</v>
+        <f>6.1+118.3</f>
+        <v>124.39999999999999</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
@@ -911,7 +914,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6-D7</f>
-        <v>-64.099999999999994</v>
+        <v>-17.200000000000003</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
@@ -920,7 +923,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>837.21300000000008</v>
+        <v>958.48000000000013</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
@@ -936,7 +939,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DA03470-03C6-4965-A90A-C28BA0FB6465}">
-  <dimension ref="B2:FB49"/>
+  <dimension ref="B2:FB50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -1147,12 +1150,10 @@
         <v>413.6</v>
       </c>
       <c r="Y3" s="8">
-        <f>U3*1.05</f>
-        <v>354.16500000000002</v>
+        <v>369.8</v>
       </c>
       <c r="Z3" s="8">
-        <f>V3*1.15</f>
-        <v>300.495</v>
+        <v>320.10000000000002</v>
       </c>
       <c r="AA3" s="8">
         <f>W3*1.2</f>
@@ -1190,47 +1191,47 @@
       </c>
       <c r="AL3" s="8">
         <f>SUM(Y3:AB3)</f>
-        <v>1453.98</v>
+        <v>1489.22</v>
       </c>
       <c r="AM3" s="8">
         <f>AL3*1.06</f>
-        <v>1541.2188000000001</v>
+        <v>1578.5732</v>
       </c>
       <c r="AN3" s="8">
         <f>AM3*1.05</f>
-        <v>1618.2797400000002</v>
+        <v>1657.5018600000001</v>
       </c>
       <c r="AO3" s="8">
         <f>AN3*1.04</f>
-        <v>1683.0109296000003</v>
+        <v>1723.8019344000002</v>
       </c>
       <c r="AP3" s="8">
         <f>AO3*1.03</f>
-        <v>1733.5012574880004</v>
+        <v>1775.5159924320003</v>
       </c>
       <c r="AQ3" s="8">
         <f>AP3*1.02</f>
-        <v>1768.1712826377604</v>
+        <v>1811.0263122806402</v>
       </c>
       <c r="AR3" s="8">
         <f t="shared" ref="AR3:AV3" si="1">AQ3*1.02</f>
-        <v>1803.5347082905157</v>
+        <v>1847.246838526253</v>
       </c>
       <c r="AS3" s="8">
         <f t="shared" si="1"/>
-        <v>1839.6054024563261</v>
+        <v>1884.1917752967781</v>
       </c>
       <c r="AT3" s="8">
         <f t="shared" si="1"/>
-        <v>1876.3975105054526</v>
+        <v>1921.8756108027137</v>
       </c>
       <c r="AU3" s="8">
         <f t="shared" si="1"/>
-        <v>1913.9254607155617</v>
+        <v>1960.313123018768</v>
       </c>
       <c r="AV3" s="8">
         <f t="shared" si="1"/>
-        <v>1952.203969929873</v>
+        <v>1999.5193854791435</v>
       </c>
     </row>
     <row r="4" spans="2:158" x14ac:dyDescent="0.3">
@@ -1301,15 +1302,13 @@
         <v>305.39999999999998</v>
       </c>
       <c r="Y4" s="4">
-        <f>Y3-Y5</f>
-        <v>265.62375000000003</v>
+        <v>267.39999999999998</v>
       </c>
       <c r="Z4" s="4">
-        <f t="shared" ref="Z4:AB4" si="2">Z3-Z5</f>
-        <v>225.37125</v>
+        <v>234.2</v>
       </c>
       <c r="AA4" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="AA4:AB4" si="2">AA3-AA5</f>
         <v>273.77999999999997</v>
       </c>
       <c r="AB4" s="4">
@@ -1344,47 +1343,47 @@
       </c>
       <c r="AL4" s="4">
         <f>SUM(Y4:AB4)</f>
-        <v>1086.1422</v>
+        <v>1096.7471999999998</v>
       </c>
       <c r="AM4" s="4">
         <f t="shared" ref="AM4:AR4" si="3">AM3-AM5</f>
-        <v>1140.5019120000002</v>
+        <v>1168.144168</v>
       </c>
       <c r="AN4" s="4">
         <f t="shared" si="3"/>
-        <v>1181.3442102000001</v>
+        <v>1209.9763578</v>
       </c>
       <c r="AO4" s="4">
         <f t="shared" si="3"/>
-        <v>1211.7678693120001</v>
+        <v>1241.1373927680002</v>
       </c>
       <c r="AP4" s="4">
         <f t="shared" si="3"/>
-        <v>1248.1209053913603</v>
+        <v>1278.37151455104</v>
       </c>
       <c r="AQ4" s="4">
         <f t="shared" si="3"/>
-        <v>1273.0833234991874</v>
+        <v>1303.9389448420609</v>
       </c>
       <c r="AR4" s="4">
         <f t="shared" si="3"/>
-        <v>1298.5449899691712</v>
+        <v>1330.0177237389021</v>
       </c>
       <c r="AS4" s="4">
         <f t="shared" ref="AS4:AV4" si="4">AS3-AS5</f>
-        <v>1324.5158897685546</v>
+        <v>1356.6180782136803</v>
       </c>
       <c r="AT4" s="4">
         <f t="shared" si="4"/>
-        <v>1351.0062075639257</v>
+        <v>1383.7504397779539</v>
       </c>
       <c r="AU4" s="4">
         <f t="shared" si="4"/>
-        <v>1378.0263317152044</v>
+        <v>1411.4254485735128</v>
       </c>
       <c r="AV4" s="4">
         <f t="shared" si="4"/>
-        <v>1405.5868583495085</v>
+        <v>1439.6539575449833</v>
       </c>
     </row>
     <row r="5" spans="2:158" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1404,7 +1403,7 @@
         <v>78.599999999999994</v>
       </c>
       <c r="G5" s="8">
-        <f t="shared" ref="G5:X5" si="5">G3-G4</f>
+        <f t="shared" ref="G5:Z5" si="5">G3-G4</f>
         <v>127.90000000000003</v>
       </c>
       <c r="H5" s="8">
@@ -1476,15 +1475,15 @@
         <v>108.20000000000005</v>
       </c>
       <c r="Y5" s="8">
-        <f>Y3*0.25</f>
-        <v>88.541250000000005</v>
+        <f t="shared" si="5"/>
+        <v>102.40000000000003</v>
       </c>
       <c r="Z5" s="8">
-        <f t="shared" ref="Z5:AA5" si="6">Z3*0.25</f>
-        <v>75.123750000000001</v>
+        <f t="shared" si="5"/>
+        <v>85.900000000000034</v>
       </c>
       <c r="AA5" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="AA5" si="6">AA3*0.25</f>
         <v>91.259999999999991</v>
       </c>
       <c r="AB5" s="8">
@@ -1522,47 +1521,47 @@
       </c>
       <c r="AL5" s="8">
         <f t="shared" si="7"/>
-        <v>367.83780000000002</v>
+        <v>392.47280000000023</v>
       </c>
       <c r="AM5" s="8">
         <f>AM3*0.26</f>
-        <v>400.71688800000004</v>
+        <v>410.42903200000001</v>
       </c>
       <c r="AN5" s="8">
         <f>AN3*0.27</f>
-        <v>436.9355298000001</v>
+        <v>447.52550220000006</v>
       </c>
       <c r="AO5" s="8">
         <f>AO3*0.28</f>
-        <v>471.24306028800015</v>
+        <v>482.66454163200007</v>
       </c>
       <c r="AP5" s="8">
         <f t="shared" ref="AP5:AV5" si="8">AP3*0.28</f>
-        <v>485.38035209664014</v>
+        <v>497.14447788096015</v>
       </c>
       <c r="AQ5" s="8">
         <f t="shared" si="8"/>
-        <v>495.08795913857296</v>
+        <v>507.08736743857929</v>
       </c>
       <c r="AR5" s="8">
         <f t="shared" si="8"/>
-        <v>504.98971832134447</v>
+        <v>517.22911478735091</v>
       </c>
       <c r="AS5" s="8">
         <f t="shared" si="8"/>
-        <v>515.08951268777139</v>
+        <v>527.57369708309795</v>
       </c>
       <c r="AT5" s="8">
         <f t="shared" si="8"/>
-        <v>525.39130294152676</v>
+        <v>538.12517102475988</v>
       </c>
       <c r="AU5" s="8">
         <f t="shared" si="8"/>
-        <v>535.89912900035733</v>
+        <v>548.88767444525513</v>
       </c>
       <c r="AV5" s="8">
         <f t="shared" si="8"/>
-        <v>546.61711158036451</v>
+        <v>559.86542793416027</v>
       </c>
     </row>
     <row r="6" spans="2:158" x14ac:dyDescent="0.3">
@@ -1633,20 +1632,18 @@
         <v>85.3</v>
       </c>
       <c r="Y6" s="4">
-        <f>U6*1.02</f>
-        <v>81.804000000000002</v>
+        <v>87</v>
       </c>
       <c r="Z6" s="4">
-        <f>V6*1.1</f>
-        <v>77.440000000000012</v>
+        <v>85.3</v>
       </c>
       <c r="AA6" s="4">
         <f>W6*1.05</f>
         <v>77.804999999999993</v>
       </c>
       <c r="AB6" s="4">
-        <f t="shared" ref="AB6" si="9">X6*1.02</f>
-        <v>87.006</v>
+        <f>X6*1.08</f>
+        <v>92.124000000000009</v>
       </c>
       <c r="AC6" s="4"/>
       <c r="AE6" s="4">
@@ -1676,47 +1673,47 @@
       </c>
       <c r="AL6" s="4">
         <f>SUM(Y6:AB6)</f>
-        <v>324.05500000000006</v>
+        <v>342.22900000000004</v>
       </c>
       <c r="AM6" s="4">
         <f>AL6*1.03</f>
-        <v>333.77665000000007</v>
+        <v>352.49587000000002</v>
       </c>
       <c r="AN6" s="4">
         <f>AM6*1.02</f>
-        <v>340.4521830000001</v>
+        <v>359.54578740000005</v>
       </c>
       <c r="AO6" s="4">
-        <f t="shared" ref="AO6:AV6" si="10">AN6*1.01</f>
-        <v>343.85670483000013</v>
+        <f t="shared" ref="AO6:AV6" si="9">AN6*1.01</f>
+        <v>363.14124527400003</v>
       </c>
       <c r="AP6" s="4">
-        <f t="shared" si="10"/>
-        <v>347.29527187830013</v>
+        <f t="shared" si="9"/>
+        <v>366.77265772674002</v>
       </c>
       <c r="AQ6" s="4">
-        <f t="shared" si="10"/>
-        <v>350.76822459708313</v>
+        <f t="shared" si="9"/>
+        <v>370.44038430400741</v>
       </c>
       <c r="AR6" s="4">
-        <f t="shared" si="10"/>
-        <v>354.27590684305397</v>
+        <f t="shared" si="9"/>
+        <v>374.14478814704751</v>
       </c>
       <c r="AS6" s="4">
-        <f t="shared" si="10"/>
-        <v>357.81866591148452</v>
+        <f t="shared" si="9"/>
+        <v>377.886236028518</v>
       </c>
       <c r="AT6" s="4">
-        <f t="shared" si="10"/>
-        <v>361.39685257059938</v>
+        <f t="shared" si="9"/>
+        <v>381.66509838880319</v>
       </c>
       <c r="AU6" s="4">
-        <f t="shared" si="10"/>
-        <v>365.01082109630539</v>
+        <f t="shared" si="9"/>
+        <v>385.48174937269124</v>
       </c>
       <c r="AV6" s="4">
-        <f t="shared" si="10"/>
-        <v>368.66092930726847</v>
+        <f t="shared" si="9"/>
+        <v>389.33656686641814</v>
       </c>
     </row>
     <row r="7" spans="2:158" x14ac:dyDescent="0.3">
@@ -1787,19 +1784,17 @@
         <v>17</v>
       </c>
       <c r="Y7" s="4">
-        <f>U7*1.03</f>
-        <v>17.098000000000003</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="Z7" s="4">
-        <f t="shared" ref="Z7:AB7" si="11">V7*1.03</f>
-        <v>17.922000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="AA7" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="AA7:AB7" si="10">W7*1.03</f>
         <v>16.995000000000001</v>
       </c>
       <c r="AB7" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>17.510000000000002</v>
       </c>
       <c r="AC7" s="4"/>
@@ -1830,47 +1825,47 @@
       </c>
       <c r="AL7" s="4">
         <f>SUM(Y7:AB7)</f>
-        <v>69.525000000000006</v>
+        <v>69.605000000000004</v>
       </c>
       <c r="AM7" s="4">
         <f>AL7*1.02</f>
-        <v>70.915500000000009</v>
+        <v>70.997100000000003</v>
       </c>
       <c r="AN7" s="4">
-        <f t="shared" ref="AN7" si="12">AM7*1.02</f>
-        <v>72.333810000000014</v>
+        <f t="shared" ref="AN7" si="11">AM7*1.02</f>
+        <v>72.417042000000009</v>
       </c>
       <c r="AO7" s="4">
         <f>AN7*1.01</f>
-        <v>73.05714810000002</v>
+        <v>73.141212420000016</v>
       </c>
       <c r="AP7" s="4">
-        <f t="shared" ref="AP7:AV7" si="13">AO7*1.01</f>
-        <v>73.787719581000019</v>
+        <f t="shared" ref="AP7:AV7" si="12">AO7*1.01</f>
+        <v>73.872624544200022</v>
       </c>
       <c r="AQ7" s="4">
-        <f t="shared" si="13"/>
-        <v>74.525596776810019</v>
+        <f t="shared" si="12"/>
+        <v>74.611350789642017</v>
       </c>
       <c r="AR7" s="4">
-        <f t="shared" si="13"/>
-        <v>75.270852744578121</v>
+        <f t="shared" si="12"/>
+        <v>75.357464297538442</v>
       </c>
       <c r="AS7" s="4">
-        <f t="shared" si="13"/>
-        <v>76.023561272023898</v>
+        <f t="shared" si="12"/>
+        <v>76.111038940513822</v>
       </c>
       <c r="AT7" s="4">
-        <f t="shared" si="13"/>
-        <v>76.783796884744135</v>
+        <f t="shared" si="12"/>
+        <v>76.872149329918955</v>
       </c>
       <c r="AU7" s="4">
-        <f t="shared" si="13"/>
-        <v>77.55163485359158</v>
+        <f t="shared" si="12"/>
+        <v>77.640870823218151</v>
       </c>
       <c r="AV7" s="4">
-        <f t="shared" si="13"/>
-        <v>78.327151202127496</v>
+        <f t="shared" si="12"/>
+        <v>78.417279531450333</v>
       </c>
     </row>
     <row r="8" spans="2:158" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1886,7 +1881,7 @@
         <v>14.3</v>
       </c>
       <c r="E8" s="8">
-        <f t="shared" ref="E8" si="14">E5-E6-E7</f>
+        <f t="shared" ref="E8" si="13">E5-E6-E7</f>
         <v>13.299999999999992</v>
       </c>
       <c r="G8" s="8">
@@ -1898,43 +1893,43 @@
         <v>58.899999999999963</v>
       </c>
       <c r="I8" s="8">
-        <f t="shared" ref="I8" si="15">I5-I6-I7</f>
+        <f t="shared" ref="I8" si="14">I5-I6-I7</f>
         <v>67.199999999999946</v>
       </c>
       <c r="J8" s="8">
-        <f t="shared" ref="J8:Q8" si="16">J5-J6-J7</f>
+        <f t="shared" ref="J8:Q8" si="15">J5-J6-J7</f>
         <v>34.599999999999952</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>10.700000000000017</v>
       </c>
       <c r="L8" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>25.20000000000001</v>
       </c>
       <c r="M8" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-2.3999999999999844</v>
       </c>
       <c r="N8" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-54.900000000000034</v>
       </c>
       <c r="O8" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-10.899999999999983</v>
       </c>
       <c r="P8" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>13.600000000000012</v>
       </c>
       <c r="Q8" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1.0999999999999766</v>
       </c>
       <c r="R8" s="8">
-        <f t="shared" ref="R8" si="17">R5-R6-R7</f>
+        <f t="shared" ref="R8" si="16">R5-R6-R7</f>
         <v>-2.8000000000000167</v>
       </c>
       <c r="S8" s="8">
@@ -1950,7 +1945,7 @@
         <v>-10.099999999999987</v>
       </c>
       <c r="V8" s="8">
-        <f t="shared" ref="V8" si="18">V5-V6-V7</f>
+        <f t="shared" ref="V8" si="17">V5-V6-V7</f>
         <v>-24.699999999999982</v>
       </c>
       <c r="W8" s="8">
@@ -1962,20 +1957,20 @@
         <v>5.9000000000000483</v>
       </c>
       <c r="Y8" s="8">
-        <f t="shared" ref="Y8:AB8" si="19">Y5-Y6-Y7</f>
-        <v>-10.360749999999999</v>
+        <f t="shared" ref="Y8:AB8" si="18">Y5-Y6-Y7</f>
+        <v>-2.1999999999999673</v>
       </c>
       <c r="Z8" s="8">
-        <f t="shared" si="19"/>
-        <v>-20.238250000000011</v>
+        <f t="shared" si="18"/>
+        <v>-16.899999999999963</v>
       </c>
       <c r="AA8" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>-3.5400000000000027</v>
       </c>
       <c r="AB8" s="8">
-        <f t="shared" si="19"/>
-        <v>8.3968000000000167</v>
+        <f t="shared" si="18"/>
+        <v>3.2788000000000075</v>
       </c>
       <c r="AC8" s="8"/>
       <c r="AE8" s="8">
@@ -1995,60 +1990,60 @@
         <v>137.69999999999999</v>
       </c>
       <c r="AI8" s="8">
-        <f t="shared" ref="AI8:AR8" si="20">AI5-AI6-AI7</f>
+        <f t="shared" ref="AI8:AR8" si="19">AI5-AI6-AI7</f>
         <v>-54.600000000000165</v>
       </c>
       <c r="AJ8" s="8">
+        <f t="shared" si="19"/>
+        <v>9.7999999999999403</v>
+      </c>
+      <c r="AK8" s="8">
+        <f t="shared" si="19"/>
+        <v>-49.799999999999841</v>
+      </c>
+      <c r="AL8" s="8">
+        <f t="shared" si="19"/>
+        <v>-19.361199999999812</v>
+      </c>
+      <c r="AM8" s="8">
+        <f t="shared" si="19"/>
+        <v>-13.063938000000022</v>
+      </c>
+      <c r="AN8" s="8">
+        <f t="shared" si="19"/>
+        <v>15.562672800000001</v>
+      </c>
+      <c r="AO8" s="8">
+        <f t="shared" si="19"/>
+        <v>46.382083938000022</v>
+      </c>
+      <c r="AP8" s="8">
+        <f t="shared" si="19"/>
+        <v>56.499195610020109</v>
+      </c>
+      <c r="AQ8" s="8">
+        <f t="shared" si="19"/>
+        <v>62.035632344929866</v>
+      </c>
+      <c r="AR8" s="8">
+        <f t="shared" si="19"/>
+        <v>67.72686234276496</v>
+      </c>
+      <c r="AS8" s="8">
+        <f t="shared" ref="AS8:AV8" si="20">AS5-AS6-AS7</f>
+        <v>73.576422114066133</v>
+      </c>
+      <c r="AT8" s="8">
         <f t="shared" si="20"/>
-        <v>9.7999999999999403</v>
-      </c>
-      <c r="AK8" s="8">
+        <v>79.587923306037737</v>
+      </c>
+      <c r="AU8" s="8">
         <f t="shared" si="20"/>
-        <v>-49.799999999999841</v>
-      </c>
-      <c r="AL8" s="8">
+        <v>85.765054249345738</v>
+      </c>
+      <c r="AV8" s="8">
         <f t="shared" si="20"/>
-        <v>-25.742200000000054</v>
-      </c>
-      <c r="AM8" s="8">
-        <f t="shared" si="20"/>
-        <v>-3.9752620000000434</v>
-      </c>
-      <c r="AN8" s="8">
-        <f t="shared" si="20"/>
-        <v>24.149536799999979</v>
-      </c>
-      <c r="AO8" s="8">
-        <f t="shared" si="20"/>
-        <v>54.329207358000005</v>
-      </c>
-      <c r="AP8" s="8">
-        <f t="shared" si="20"/>
-        <v>64.297360637339992</v>
-      </c>
-      <c r="AQ8" s="8">
-        <f t="shared" si="20"/>
-        <v>69.794137764679803</v>
-      </c>
-      <c r="AR8" s="8">
-        <f t="shared" si="20"/>
-        <v>75.442958733712373</v>
-      </c>
-      <c r="AS8" s="8">
-        <f t="shared" ref="AS8:AV8" si="21">AS5-AS6-AS7</f>
-        <v>81.247285504262976</v>
-      </c>
-      <c r="AT8" s="8">
-        <f t="shared" si="21"/>
-        <v>87.210653486183247</v>
-      </c>
-      <c r="AU8" s="8">
-        <f t="shared" si="21"/>
-        <v>93.336673050460362</v>
-      </c>
-      <c r="AV8" s="8">
-        <f t="shared" si="21"/>
-        <v>99.629031070968537</v>
+        <v>92.111581536291794</v>
       </c>
     </row>
     <row r="9" spans="2:158" x14ac:dyDescent="0.3">
@@ -2119,19 +2114,17 @@
         <v>3.1</v>
       </c>
       <c r="Y9" s="4">
-        <f>U9*1.02</f>
-        <v>3.7740000000000005</v>
+        <v>2.7</v>
       </c>
       <c r="Z9" s="4">
-        <f t="shared" ref="Z9:AB9" si="22">V9*1.02</f>
-        <v>3.468</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="AA9:AB9" si="21">W9*1.02</f>
         <v>3.06</v>
       </c>
       <c r="AB9" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>3.1620000000000004</v>
       </c>
       <c r="AC9" s="4"/>
@@ -2162,47 +2155,47 @@
       </c>
       <c r="AL9" s="4">
         <f>SUM(Y9:AB9)</f>
-        <v>13.464000000000002</v>
+        <v>11.422000000000001</v>
       </c>
       <c r="AM9" s="4">
         <f>AL9*1.03</f>
-        <v>13.867920000000003</v>
+        <v>11.764660000000001</v>
       </c>
       <c r="AN9" s="4">
-        <f t="shared" ref="AN9:AV9" si="23">AM9*1.03</f>
-        <v>14.283957600000004</v>
+        <f t="shared" ref="AN9:AV9" si="22">AM9*1.03</f>
+        <v>12.117599800000001</v>
       </c>
       <c r="AO9" s="4">
-        <f t="shared" si="23"/>
-        <v>14.712476328000005</v>
+        <f t="shared" si="22"/>
+        <v>12.481127794000001</v>
       </c>
       <c r="AP9" s="4">
-        <f t="shared" si="23"/>
-        <v>15.153850617840005</v>
+        <f t="shared" si="22"/>
+        <v>12.85556162782</v>
       </c>
       <c r="AQ9" s="4">
-        <f t="shared" si="23"/>
-        <v>15.608466136375206</v>
+        <f t="shared" si="22"/>
+        <v>13.2412284766546</v>
       </c>
       <c r="AR9" s="4">
-        <f t="shared" si="23"/>
-        <v>16.076720120466462</v>
+        <f t="shared" si="22"/>
+        <v>13.638465330954238</v>
       </c>
       <c r="AS9" s="4">
-        <f t="shared" si="23"/>
-        <v>16.559021724080456</v>
+        <f t="shared" si="22"/>
+        <v>14.047619290882865</v>
       </c>
       <c r="AT9" s="4">
-        <f t="shared" si="23"/>
-        <v>17.05579237580287</v>
+        <f t="shared" si="22"/>
+        <v>14.469047869609351</v>
       </c>
       <c r="AU9" s="4">
-        <f t="shared" si="23"/>
-        <v>17.567466147076956</v>
+        <f t="shared" si="22"/>
+        <v>14.903119305697633</v>
       </c>
       <c r="AV9" s="4">
-        <f t="shared" si="23"/>
-        <v>18.094490131489266</v>
+        <f t="shared" si="22"/>
+        <v>15.350212884868562</v>
       </c>
     </row>
     <row r="10" spans="2:158" x14ac:dyDescent="0.3">
@@ -2281,10 +2274,12 @@
         <v>-0.3</v>
       </c>
       <c r="Y10" s="4">
-        <v>0</v>
+        <f>-0.6+3.9</f>
+        <v>3.3</v>
       </c>
       <c r="Z10" s="4">
-        <v>0</v>
+        <f>-0.6+1.9</f>
+        <v>1.2999999999999998</v>
       </c>
       <c r="AA10" s="4">
         <v>0</v>
@@ -2320,7 +2315,7 @@
       </c>
       <c r="AL10" s="4">
         <f>SUM(Y10:AB10)</f>
-        <v>0</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AM10" s="4">
         <v>0</v>
@@ -2366,7 +2361,7 @@
         <v>5.7000000000000011</v>
       </c>
       <c r="E11" s="8">
-        <f t="shared" ref="E11" si="24">E8-E9-E10</f>
+        <f t="shared" ref="E11" si="23">E8-E9-E10</f>
         <v>3.7999999999999914</v>
       </c>
       <c r="G11" s="8">
@@ -2378,43 +2373,43 @@
         <v>51.69999999999996</v>
       </c>
       <c r="I11" s="8">
-        <f t="shared" ref="I11" si="25">I8-I9-I10</f>
+        <f t="shared" ref="I11" si="24">I8-I9-I10</f>
         <v>59.899999999999949</v>
       </c>
       <c r="J11" s="8">
-        <f t="shared" ref="J11:Q11" si="26">J8-J9-J10</f>
+        <f t="shared" ref="J11:Q11" si="25">J8-J9-J10</f>
         <v>29.899999999999952</v>
       </c>
       <c r="K11" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>2.100000000000017</v>
       </c>
       <c r="L11" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>22.500000000000011</v>
       </c>
       <c r="M11" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>-4.1999999999999842</v>
       </c>
       <c r="N11" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>-56.000000000000036</v>
       </c>
       <c r="O11" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>-11.899999999999984</v>
       </c>
       <c r="P11" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>8.5000000000000107</v>
       </c>
       <c r="Q11" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>-2.2000000000000233</v>
       </c>
       <c r="R11" s="8">
-        <f t="shared" ref="R11" si="27">R8-R9-R10</f>
+        <f t="shared" ref="R11" si="26">R8-R9-R10</f>
         <v>-6.4000000000000163</v>
       </c>
       <c r="S11" s="8">
@@ -2430,7 +2425,7 @@
         <v>-12.699999999999987</v>
       </c>
       <c r="V11" s="8">
-        <f t="shared" ref="V11" si="28">V8-V9-V10</f>
+        <f t="shared" ref="V11" si="27">V8-V9-V10</f>
         <v>-27.399999999999981</v>
       </c>
       <c r="W11" s="8">
@@ -2442,20 +2437,20 @@
         <v>3.1000000000000481</v>
       </c>
       <c r="Y11" s="8">
-        <f t="shared" ref="Y11:AB11" si="29">Y8-Y9-Y10</f>
-        <v>-14.13475</v>
+        <f t="shared" ref="Y11:AB11" si="28">Y8-Y9-Y10</f>
+        <v>-8.1999999999999673</v>
       </c>
       <c r="Z11" s="8">
-        <f t="shared" si="29"/>
-        <v>-23.706250000000011</v>
+        <f t="shared" si="28"/>
+        <v>-20.699999999999964</v>
       </c>
       <c r="AA11" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>-6.6000000000000032</v>
       </c>
       <c r="AB11" s="8">
-        <f t="shared" si="29"/>
-        <v>5.2348000000000159</v>
+        <f t="shared" si="28"/>
+        <v>0.11680000000000712</v>
       </c>
       <c r="AC11" s="8"/>
       <c r="AE11" s="8">
@@ -2475,60 +2470,60 @@
         <v>114.39999999999999</v>
       </c>
       <c r="AI11" s="8">
-        <f t="shared" ref="AI11:AR11" si="30">AI8-AI9-AI10</f>
+        <f t="shared" ref="AI11:AR11" si="29">AI8-AI9-AI10</f>
         <v>-63.600000000000158</v>
       </c>
       <c r="AJ11" s="8">
+        <f t="shared" si="29"/>
+        <v>-3.5000000000000595</v>
+      </c>
+      <c r="AK11" s="8">
+        <f t="shared" si="29"/>
+        <v>-61.499999999999844</v>
+      </c>
+      <c r="AL11" s="8">
+        <f t="shared" si="29"/>
+        <v>-35.38319999999981</v>
+      </c>
+      <c r="AM11" s="8">
+        <f t="shared" si="29"/>
+        <v>-24.828598000000021</v>
+      </c>
+      <c r="AN11" s="8">
+        <f t="shared" si="29"/>
+        <v>3.4450730000000007</v>
+      </c>
+      <c r="AO11" s="8">
+        <f t="shared" si="29"/>
+        <v>33.90095614400002</v>
+      </c>
+      <c r="AP11" s="8">
+        <f t="shared" si="29"/>
+        <v>43.643633982200107</v>
+      </c>
+      <c r="AQ11" s="8">
+        <f t="shared" si="29"/>
+        <v>48.794403868275268</v>
+      </c>
+      <c r="AR11" s="8">
+        <f t="shared" si="29"/>
+        <v>54.08839701181072</v>
+      </c>
+      <c r="AS11" s="8">
+        <f t="shared" ref="AS11:AV11" si="30">AS8-AS9-AS10</f>
+        <v>59.52880282318327</v>
+      </c>
+      <c r="AT11" s="8">
         <f t="shared" si="30"/>
-        <v>-3.5000000000000595</v>
-      </c>
-      <c r="AK11" s="8">
+        <v>65.118875436428382</v>
+      </c>
+      <c r="AU11" s="8">
         <f t="shared" si="30"/>
-        <v>-61.499999999999844</v>
-      </c>
-      <c r="AL11" s="8">
+        <v>70.861934943648109</v>
+      </c>
+      <c r="AV11" s="8">
         <f t="shared" si="30"/>
-        <v>-39.206200000000052</v>
-      </c>
-      <c r="AM11" s="8">
-        <f t="shared" si="30"/>
-        <v>-17.843182000000049</v>
-      </c>
-      <c r="AN11" s="8">
-        <f t="shared" si="30"/>
-        <v>9.8655791999999742</v>
-      </c>
-      <c r="AO11" s="8">
-        <f t="shared" si="30"/>
-        <v>39.616731029999997</v>
-      </c>
-      <c r="AP11" s="8">
-        <f t="shared" si="30"/>
-        <v>49.143510019499985</v>
-      </c>
-      <c r="AQ11" s="8">
-        <f t="shared" si="30"/>
-        <v>54.185671628304597</v>
-      </c>
-      <c r="AR11" s="8">
-        <f t="shared" si="30"/>
-        <v>59.366238613245912</v>
-      </c>
-      <c r="AS11" s="8">
-        <f t="shared" ref="AS11:AV11" si="31">AS8-AS9-AS10</f>
-        <v>64.688263780182524</v>
-      </c>
-      <c r="AT11" s="8">
-        <f t="shared" si="31"/>
-        <v>70.154861110380381</v>
-      </c>
-      <c r="AU11" s="8">
-        <f t="shared" si="31"/>
-        <v>75.769206903383406</v>
-      </c>
-      <c r="AV11" s="8">
-        <f t="shared" si="31"/>
-        <v>81.534540939479271</v>
+        <v>76.761368651423226</v>
       </c>
     </row>
     <row r="12" spans="2:158" x14ac:dyDescent="0.3">
@@ -2599,20 +2594,18 @@
         <v>0.5</v>
       </c>
       <c r="Y12" s="4">
-        <f>Y11*0.2</f>
-        <v>-2.8269500000000001</v>
+        <v>2.1</v>
       </c>
       <c r="Z12" s="4">
-        <f t="shared" ref="Z12:AB12" si="32">Z11*0.2</f>
-        <v>-4.7412500000000026</v>
+        <v>-0.4</v>
       </c>
       <c r="AA12" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="AA12:AB12" si="31">AA11*0.2</f>
         <v>-1.3200000000000007</v>
       </c>
       <c r="AB12" s="4">
-        <f t="shared" si="32"/>
-        <v>1.0469600000000032</v>
+        <f t="shared" si="31"/>
+        <v>2.3360000000001425E-2</v>
       </c>
       <c r="AC12" s="4"/>
       <c r="AE12" s="4">
@@ -2642,47 +2635,47 @@
       </c>
       <c r="AL12" s="4">
         <f>SUM(Y12:AB12)</f>
-        <v>-7.84124</v>
+        <v>0.40336000000000088</v>
       </c>
       <c r="AM12" s="4">
-        <f t="shared" ref="AM12:AR12" si="33">AM11*0.19</f>
-        <v>-3.3902045800000091</v>
+        <f t="shared" ref="AM12:AR12" si="32">AM11*0.19</f>
+        <v>-4.717433620000004</v>
       </c>
       <c r="AN12" s="4">
+        <f t="shared" si="32"/>
+        <v>0.65456387000000016</v>
+      </c>
+      <c r="AO12" s="4">
+        <f t="shared" si="32"/>
+        <v>6.441181667360004</v>
+      </c>
+      <c r="AP12" s="4">
+        <f t="shared" si="32"/>
+        <v>8.2922904566180211</v>
+      </c>
+      <c r="AQ12" s="4">
+        <f t="shared" si="32"/>
+        <v>9.2709367349723006</v>
+      </c>
+      <c r="AR12" s="4">
+        <f t="shared" si="32"/>
+        <v>10.276795432244038</v>
+      </c>
+      <c r="AS12" s="4">
+        <f t="shared" ref="AS12:AV12" si="33">AS11*0.19</f>
+        <v>11.310472536404822</v>
+      </c>
+      <c r="AT12" s="4">
         <f t="shared" si="33"/>
-        <v>1.8744600479999951</v>
-      </c>
-      <c r="AO12" s="4">
+        <v>12.372586332921394</v>
+      </c>
+      <c r="AU12" s="4">
         <f t="shared" si="33"/>
-        <v>7.5271788956999997</v>
-      </c>
-      <c r="AP12" s="4">
+        <v>13.46376763929314</v>
+      </c>
+      <c r="AV12" s="4">
         <f t="shared" si="33"/>
-        <v>9.3372669037049967</v>
-      </c>
-      <c r="AQ12" s="4">
-        <f t="shared" si="33"/>
-        <v>10.295277609377873</v>
-      </c>
-      <c r="AR12" s="4">
-        <f t="shared" si="33"/>
-        <v>11.279585336516723</v>
-      </c>
-      <c r="AS12" s="4">
-        <f t="shared" ref="AS12:AV12" si="34">AS11*0.19</f>
-        <v>12.290770118234679</v>
-      </c>
-      <c r="AT12" s="4">
-        <f t="shared" si="34"/>
-        <v>13.329423610972272</v>
-      </c>
-      <c r="AU12" s="4">
-        <f t="shared" si="34"/>
-        <v>14.396149311642848</v>
-      </c>
-      <c r="AV12" s="4">
-        <f t="shared" si="34"/>
-        <v>15.491562778501061</v>
+        <v>14.584660043770413</v>
       </c>
     </row>
     <row r="13" spans="2:158" x14ac:dyDescent="0.3">
@@ -2751,10 +2744,10 @@
         <v>0.4</v>
       </c>
       <c r="Y13" s="4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Z13" s="4">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AA13" s="4">
         <v>0</v>
@@ -2804,7 +2797,7 @@
         <v>6.1000000000000014</v>
       </c>
       <c r="E14" s="8">
-        <f t="shared" ref="E14" si="35">E11-E12</f>
+        <f t="shared" ref="E14" si="34">E11-E12</f>
         <v>1.0999999999999912</v>
       </c>
       <c r="G14" s="8">
@@ -2816,84 +2809,84 @@
         <v>42.999999999999957</v>
       </c>
       <c r="I14" s="8">
-        <f t="shared" ref="I14" si="36">I11-I12</f>
+        <f t="shared" ref="I14" si="35">I11-I12</f>
         <v>46.699999999999946</v>
       </c>
       <c r="J14" s="8">
-        <f t="shared" ref="J14:X14" si="37">J11-J12-J13</f>
+        <f t="shared" ref="J14:X14" si="36">J11-J12-J13</f>
         <v>27.599999999999952</v>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>1.7000000000000171</v>
       </c>
       <c r="L14" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>24.800000000000011</v>
       </c>
       <c r="M14" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-5.0999999999999837</v>
       </c>
       <c r="N14" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-59.400000000000034</v>
       </c>
       <c r="O14" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-8.7999999999999847</v>
       </c>
       <c r="P14" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>12.500000000000011</v>
       </c>
       <c r="Q14" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-1.0000000000000231</v>
       </c>
       <c r="R14" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>1.0999999999999828</v>
       </c>
       <c r="S14" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-3.1000000000000241</v>
       </c>
       <c r="T14" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>6.0999999999999925</v>
       </c>
       <c r="U14" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-12.399999999999986</v>
       </c>
       <c r="V14" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-29.499999999999982</v>
       </c>
       <c r="W14" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-58.300000000000004</v>
       </c>
       <c r="X14" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>2.2000000000000481</v>
       </c>
       <c r="Y14" s="8">
-        <f t="shared" ref="Y14" si="38">Y11-Y12-Y13</f>
-        <v>-11.3078</v>
+        <f t="shared" ref="Y14" si="37">Y11-Y12-Y13</f>
+        <v>-10.399999999999967</v>
       </c>
       <c r="Z14" s="8">
-        <f t="shared" ref="Z14" si="39">Z11-Z12-Z13</f>
-        <v>-18.965000000000011</v>
+        <f t="shared" ref="Z14" si="38">Z11-Z12-Z13</f>
+        <v>-20.899999999999967</v>
       </c>
       <c r="AA14" s="8">
-        <f t="shared" ref="AA14" si="40">AA11-AA12-AA13</f>
+        <f t="shared" ref="AA14" si="39">AA11-AA12-AA13</f>
         <v>-5.2800000000000029</v>
       </c>
       <c r="AB14" s="8">
-        <f t="shared" ref="AB14" si="41">AB11-AB12-AB13</f>
-        <v>4.1878400000000129</v>
+        <f t="shared" ref="AB14" si="40">AB11-AB12-AB13</f>
+        <v>9.3440000000005699E-2</v>
       </c>
       <c r="AC14" s="8"/>
       <c r="AE14" s="8">
@@ -2913,500 +2906,500 @@
         <v>100.79999999999998</v>
       </c>
       <c r="AI14" s="8">
-        <f t="shared" ref="AI14:AV14" si="42">AI11-AI12-AI13</f>
+        <f t="shared" ref="AI14:AV14" si="41">AI11-AI12-AI13</f>
         <v>-60.800000000000161</v>
       </c>
       <c r="AJ14" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>3.0999999999999397</v>
       </c>
       <c r="AK14" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>-97.999999999999844</v>
       </c>
       <c r="AL14" s="8">
-        <f t="shared" si="42"/>
-        <v>-31.364960000000053</v>
+        <f t="shared" si="41"/>
+        <v>-35.78655999999981</v>
       </c>
       <c r="AM14" s="8">
-        <f t="shared" si="42"/>
-        <v>-14.452977420000039</v>
+        <f t="shared" si="41"/>
+        <v>-20.111164380000016</v>
       </c>
       <c r="AN14" s="8">
-        <f t="shared" si="42"/>
-        <v>7.9911191519999791</v>
+        <f t="shared" si="41"/>
+        <v>2.7905091300000007</v>
       </c>
       <c r="AO14" s="8">
-        <f t="shared" si="42"/>
-        <v>32.0895521343</v>
+        <f t="shared" si="41"/>
+        <v>27.459774476640014</v>
       </c>
       <c r="AP14" s="8">
-        <f t="shared" si="42"/>
-        <v>39.806243115794985</v>
+        <f t="shared" si="41"/>
+        <v>35.351343525582088</v>
       </c>
       <c r="AQ14" s="8">
-        <f t="shared" si="42"/>
-        <v>43.890394018926727</v>
+        <f t="shared" si="41"/>
+        <v>39.523467133302965</v>
       </c>
       <c r="AR14" s="8">
-        <f t="shared" si="42"/>
-        <v>48.086653276729187</v>
+        <f t="shared" si="41"/>
+        <v>43.811601579566684</v>
       </c>
       <c r="AS14" s="8">
-        <f t="shared" si="42"/>
-        <v>52.397493661947848</v>
+        <f t="shared" si="41"/>
+        <v>48.218330286778446</v>
       </c>
       <c r="AT14" s="8">
-        <f t="shared" si="42"/>
-        <v>56.82543749940811</v>
+        <f t="shared" si="41"/>
+        <v>52.746289103506989</v>
       </c>
       <c r="AU14" s="8">
-        <f t="shared" si="42"/>
-        <v>61.373057591740562</v>
+        <f t="shared" si="41"/>
+        <v>57.39816730435497</v>
       </c>
       <c r="AV14" s="8">
-        <f t="shared" si="42"/>
-        <v>66.042978160978208</v>
+        <f t="shared" si="41"/>
+        <v>62.176708607652813</v>
       </c>
       <c r="AW14" s="1">
         <f>AV14*(1+$AY$20)</f>
-        <v>65.38254837936843</v>
+        <v>61.554941521576282</v>
       </c>
       <c r="AX14" s="1">
-        <f t="shared" ref="AX14:DI14" si="43">AW14*(1+$AY$20)</f>
-        <v>64.728722895574748</v>
+        <f t="shared" ref="AX14:DI14" si="42">AW14*(1+$AY$20)</f>
+        <v>60.939392106360522</v>
       </c>
       <c r="AY14" s="1">
+        <f t="shared" si="42"/>
+        <v>60.329998185296915</v>
+      </c>
+      <c r="AZ14" s="1">
+        <f t="shared" si="42"/>
+        <v>59.726698203443945</v>
+      </c>
+      <c r="BA14" s="1">
+        <f t="shared" si="42"/>
+        <v>59.129431221409504</v>
+      </c>
+      <c r="BB14" s="1">
+        <f t="shared" si="42"/>
+        <v>58.538136909195408</v>
+      </c>
+      <c r="BC14" s="1">
+        <f t="shared" si="42"/>
+        <v>57.952755540103453</v>
+      </c>
+      <c r="BD14" s="1">
+        <f t="shared" si="42"/>
+        <v>57.373227984702417</v>
+      </c>
+      <c r="BE14" s="1">
+        <f t="shared" si="42"/>
+        <v>56.799495704855396</v>
+      </c>
+      <c r="BF14" s="1">
+        <f t="shared" si="42"/>
+        <v>56.231500747806841</v>
+      </c>
+      <c r="BG14" s="1">
+        <f t="shared" si="42"/>
+        <v>55.669185740328771</v>
+      </c>
+      <c r="BH14" s="1">
+        <f t="shared" si="42"/>
+        <v>55.112493882925484</v>
+      </c>
+      <c r="BI14" s="1">
+        <f t="shared" si="42"/>
+        <v>54.56136894409623</v>
+      </c>
+      <c r="BJ14" s="1">
+        <f t="shared" si="42"/>
+        <v>54.015755254655268</v>
+      </c>
+      <c r="BK14" s="1">
+        <f t="shared" si="42"/>
+        <v>53.475597702108715</v>
+      </c>
+      <c r="BL14" s="1">
+        <f t="shared" si="42"/>
+        <v>52.94084172508763</v>
+      </c>
+      <c r="BM14" s="1">
+        <f t="shared" si="42"/>
+        <v>52.411433307836752</v>
+      </c>
+      <c r="BN14" s="1">
+        <f t="shared" si="42"/>
+        <v>51.887318974758387</v>
+      </c>
+      <c r="BO14" s="1">
+        <f t="shared" si="42"/>
+        <v>51.368445785010799</v>
+      </c>
+      <c r="BP14" s="1">
+        <f t="shared" si="42"/>
+        <v>50.854761327160688</v>
+      </c>
+      <c r="BQ14" s="1">
+        <f t="shared" si="42"/>
+        <v>50.346213713889078</v>
+      </c>
+      <c r="BR14" s="1">
+        <f t="shared" si="42"/>
+        <v>49.842751576750189</v>
+      </c>
+      <c r="BS14" s="1">
+        <f t="shared" si="42"/>
+        <v>49.344324060982686</v>
+      </c>
+      <c r="BT14" s="1">
+        <f t="shared" si="42"/>
+        <v>48.850880820372858</v>
+      </c>
+      <c r="BU14" s="1">
+        <f t="shared" si="42"/>
+        <v>48.362372012169132</v>
+      </c>
+      <c r="BV14" s="1">
+        <f t="shared" si="42"/>
+        <v>47.87874829204744</v>
+      </c>
+      <c r="BW14" s="1">
+        <f t="shared" si="42"/>
+        <v>47.399960809126966</v>
+      </c>
+      <c r="BX14" s="1">
+        <f t="shared" si="42"/>
+        <v>46.925961201035697</v>
+      </c>
+      <c r="BY14" s="1">
+        <f t="shared" si="42"/>
+        <v>46.456701589025343</v>
+      </c>
+      <c r="BZ14" s="1">
+        <f t="shared" si="42"/>
+        <v>45.99213457313509</v>
+      </c>
+      <c r="CA14" s="1">
+        <f t="shared" si="42"/>
+        <v>45.532213227403737</v>
+      </c>
+      <c r="CB14" s="1">
+        <f t="shared" si="42"/>
+        <v>45.076891095129696</v>
+      </c>
+      <c r="CC14" s="1">
+        <f t="shared" si="42"/>
+        <v>44.626122184178399</v>
+      </c>
+      <c r="CD14" s="1">
+        <f t="shared" si="42"/>
+        <v>44.179860962336612</v>
+      </c>
+      <c r="CE14" s="1">
+        <f t="shared" si="42"/>
+        <v>43.738062352713243</v>
+      </c>
+      <c r="CF14" s="1">
+        <f t="shared" si="42"/>
+        <v>43.30068172918611</v>
+      </c>
+      <c r="CG14" s="1">
+        <f t="shared" si="42"/>
+        <v>42.867674911894248</v>
+      </c>
+      <c r="CH14" s="1">
+        <f t="shared" si="42"/>
+        <v>42.438998162775306</v>
+      </c>
+      <c r="CI14" s="1">
+        <f t="shared" si="42"/>
+        <v>42.014608181147551</v>
+      </c>
+      <c r="CJ14" s="1">
+        <f t="shared" si="42"/>
+        <v>41.594462099336077</v>
+      </c>
+      <c r="CK14" s="1">
+        <f t="shared" si="42"/>
+        <v>41.178517478342719</v>
+      </c>
+      <c r="CL14" s="1">
+        <f t="shared" si="42"/>
+        <v>40.766732303559294</v>
+      </c>
+      <c r="CM14" s="1">
+        <f t="shared" si="42"/>
+        <v>40.359064980523698</v>
+      </c>
+      <c r="CN14" s="1">
+        <f t="shared" si="42"/>
+        <v>39.955474330718459</v>
+      </c>
+      <c r="CO14" s="1">
+        <f t="shared" si="42"/>
+        <v>39.555919587411275</v>
+      </c>
+      <c r="CP14" s="1">
+        <f t="shared" si="42"/>
+        <v>39.160360391537161</v>
+      </c>
+      <c r="CQ14" s="1">
+        <f t="shared" si="42"/>
+        <v>38.76875678762179</v>
+      </c>
+      <c r="CR14" s="1">
+        <f t="shared" si="42"/>
+        <v>38.381069219745569</v>
+      </c>
+      <c r="CS14" s="1">
+        <f t="shared" si="42"/>
+        <v>37.997258527548112</v>
+      </c>
+      <c r="CT14" s="1">
+        <f t="shared" si="42"/>
+        <v>37.61728594227263</v>
+      </c>
+      <c r="CU14" s="1">
+        <f t="shared" si="42"/>
+        <v>37.241113082849907</v>
+      </c>
+      <c r="CV14" s="1">
+        <f t="shared" si="42"/>
+        <v>36.868701952021411</v>
+      </c>
+      <c r="CW14" s="1">
+        <f t="shared" si="42"/>
+        <v>36.500014932501195</v>
+      </c>
+      <c r="CX14" s="1">
+        <f t="shared" si="42"/>
+        <v>36.135014783176182</v>
+      </c>
+      <c r="CY14" s="1">
+        <f t="shared" si="42"/>
+        <v>35.773664635344417</v>
+      </c>
+      <c r="CZ14" s="1">
+        <f t="shared" si="42"/>
+        <v>35.415927988990973</v>
+      </c>
+      <c r="DA14" s="1">
+        <f t="shared" si="42"/>
+        <v>35.061768709101059</v>
+      </c>
+      <c r="DB14" s="1">
+        <f t="shared" si="42"/>
+        <v>34.71115102201005</v>
+      </c>
+      <c r="DC14" s="1">
+        <f t="shared" si="42"/>
+        <v>34.364039511789947</v>
+      </c>
+      <c r="DD14" s="1">
+        <f t="shared" si="42"/>
+        <v>34.020399116672046</v>
+      </c>
+      <c r="DE14" s="1">
+        <f t="shared" si="42"/>
+        <v>33.680195125505328</v>
+      </c>
+      <c r="DF14" s="1">
+        <f t="shared" si="42"/>
+        <v>33.343393174250274</v>
+      </c>
+      <c r="DG14" s="1">
+        <f t="shared" si="42"/>
+        <v>33.009959242507769</v>
+      </c>
+      <c r="DH14" s="1">
+        <f t="shared" si="42"/>
+        <v>32.67985965008269</v>
+      </c>
+      <c r="DI14" s="1">
+        <f t="shared" si="42"/>
+        <v>32.353061053581861</v>
+      </c>
+      <c r="DJ14" s="1">
+        <f t="shared" ref="DJ14:FB14" si="43">DI14*(1+$AY$20)</f>
+        <v>32.029530443046042</v>
+      </c>
+      <c r="DK14" s="1">
         <f t="shared" si="43"/>
-        <v>64.081435666619001</v>
-      </c>
-      <c r="AZ14" s="1">
+        <v>31.709235138615583</v>
+      </c>
+      <c r="DL14" s="1">
         <f t="shared" si="43"/>
-        <v>63.44062130995281</v>
-      </c>
-      <c r="BA14" s="1">
+        <v>31.392142787229428</v>
+      </c>
+      <c r="DM14" s="1">
         <f t="shared" si="43"/>
-        <v>62.806215096853279</v>
-      </c>
-      <c r="BB14" s="1">
+        <v>31.078221359357133</v>
+      </c>
+      <c r="DN14" s="1">
         <f t="shared" si="43"/>
-        <v>62.178152945884747</v>
-      </c>
-      <c r="BC14" s="1">
+        <v>30.767439145763561</v>
+      </c>
+      <c r="DO14" s="1">
         <f t="shared" si="43"/>
-        <v>61.556371416425897</v>
-      </c>
-      <c r="BD14" s="1">
+        <v>30.459764754305926</v>
+      </c>
+      <c r="DP14" s="1">
         <f t="shared" si="43"/>
-        <v>60.940807702261637</v>
-      </c>
-      <c r="BE14" s="1">
+        <v>30.155167106762867</v>
+      </c>
+      <c r="DQ14" s="1">
         <f t="shared" si="43"/>
-        <v>60.331399625239023</v>
-      </c>
-      <c r="BF14" s="1">
+        <v>29.853615435695239</v>
+      </c>
+      <c r="DR14" s="1">
         <f t="shared" si="43"/>
-        <v>59.728085628986634</v>
-      </c>
-      <c r="BG14" s="1">
+        <v>29.555079281338287</v>
+      </c>
+      <c r="DS14" s="1">
         <f t="shared" si="43"/>
-        <v>59.13080477269677</v>
-      </c>
-      <c r="BH14" s="1">
+        <v>29.259528488524904</v>
+      </c>
+      <c r="DT14" s="1">
         <f t="shared" si="43"/>
-        <v>58.539496724969801</v>
-      </c>
-      <c r="BI14" s="1">
+        <v>28.966933203639655</v>
+      </c>
+      <c r="DU14" s="1">
         <f t="shared" si="43"/>
-        <v>57.954101757720103</v>
-      </c>
-      <c r="BJ14" s="1">
+        <v>28.677263871603259</v>
+      </c>
+      <c r="DV14" s="1">
         <f t="shared" si="43"/>
-        <v>57.374560740142904</v>
-      </c>
-      <c r="BK14" s="1">
+        <v>28.390491232887225</v>
+      </c>
+      <c r="DW14" s="1">
         <f t="shared" si="43"/>
-        <v>56.800815132741477</v>
-      </c>
-      <c r="BL14" s="1">
+        <v>28.106586320558353</v>
+      </c>
+      <c r="DX14" s="1">
         <f t="shared" si="43"/>
-        <v>56.232806981414065</v>
-      </c>
-      <c r="BM14" s="1">
+        <v>27.82552045735277</v>
+      </c>
+      <c r="DY14" s="1">
         <f t="shared" si="43"/>
-        <v>55.670478911599922</v>
-      </c>
-      <c r="BN14" s="1">
+        <v>27.547265252779241</v>
+      </c>
+      <c r="DZ14" s="1">
         <f t="shared" si="43"/>
-        <v>55.113774122483925</v>
-      </c>
-      <c r="BO14" s="1">
+        <v>27.271792600251448</v>
+      </c>
+      <c r="EA14" s="1">
         <f t="shared" si="43"/>
-        <v>54.562636381259082</v>
-      </c>
-      <c r="BP14" s="1">
+        <v>26.999074674248934</v>
+      </c>
+      <c r="EB14" s="1">
         <f t="shared" si="43"/>
-        <v>54.017010017446488</v>
-      </c>
-      <c r="BQ14" s="1">
+        <v>26.729083927506444</v>
+      </c>
+      <c r="EC14" s="1">
         <f t="shared" si="43"/>
-        <v>53.476839917272024</v>
-      </c>
-      <c r="BR14" s="1">
+        <v>26.461793088231378</v>
+      </c>
+      <c r="ED14" s="1">
         <f t="shared" si="43"/>
-        <v>52.942071518099304</v>
-      </c>
-      <c r="BS14" s="1">
+        <v>26.197175157349065</v>
+      </c>
+      <c r="EE14" s="1">
         <f t="shared" si="43"/>
-        <v>52.412650802918314</v>
-      </c>
-      <c r="BT14" s="1">
+        <v>25.935203405775574</v>
+      </c>
+      <c r="EF14" s="1">
         <f t="shared" si="43"/>
-        <v>51.88852429488913</v>
-      </c>
-      <c r="BU14" s="1">
+        <v>25.675851371717819</v>
+      </c>
+      <c r="EG14" s="1">
         <f t="shared" si="43"/>
-        <v>51.36963905194024</v>
-      </c>
-      <c r="BV14" s="1">
+        <v>25.419092858000642</v>
+      </c>
+      <c r="EH14" s="1">
         <f t="shared" si="43"/>
-        <v>50.855942661420841</v>
-      </c>
-      <c r="BW14" s="1">
+        <v>25.164901929420637</v>
+      </c>
+      <c r="EI14" s="1">
         <f t="shared" si="43"/>
-        <v>50.347383234806628</v>
-      </c>
-      <c r="BX14" s="1">
+        <v>24.913252910126431</v>
+      </c>
+      <c r="EJ14" s="1">
         <f t="shared" si="43"/>
-        <v>49.843909402458564</v>
-      </c>
-      <c r="BY14" s="1">
+        <v>24.664120381025167</v>
+      </c>
+      <c r="EK14" s="1">
         <f t="shared" si="43"/>
-        <v>49.345470308433981</v>
-      </c>
-      <c r="BZ14" s="1">
+        <v>24.417479177214915</v>
+      </c>
+      <c r="EL14" s="1">
         <f t="shared" si="43"/>
-        <v>48.852015605349642</v>
-      </c>
-      <c r="CA14" s="1">
+        <v>24.173304385442766</v>
+      </c>
+      <c r="EM14" s="1">
         <f t="shared" si="43"/>
-        <v>48.363495449296146</v>
-      </c>
-      <c r="CB14" s="1">
+        <v>23.931571341588338</v>
+      </c>
+      <c r="EN14" s="1">
         <f t="shared" si="43"/>
-        <v>47.879860494803182</v>
-      </c>
-      <c r="CC14" s="1">
+        <v>23.692255628172454</v>
+      </c>
+      <c r="EO14" s="1">
         <f t="shared" si="43"/>
-        <v>47.40106188985515</v>
-      </c>
-      <c r="CD14" s="1">
+        <v>23.455333071890728</v>
+      </c>
+      <c r="EP14" s="1">
         <f t="shared" si="43"/>
-        <v>46.927051270956596</v>
-      </c>
-      <c r="CE14" s="1">
+        <v>23.220779741171821</v>
+      </c>
+      <c r="EQ14" s="1">
         <f t="shared" si="43"/>
-        <v>46.457780758247033</v>
-      </c>
-      <c r="CF14" s="1">
+        <v>22.988571943760103</v>
+      </c>
+      <c r="ER14" s="1">
         <f t="shared" si="43"/>
-        <v>45.993202950664561</v>
-      </c>
-      <c r="CG14" s="1">
+        <v>22.758686224322503</v>
+      </c>
+      <c r="ES14" s="1">
         <f t="shared" si="43"/>
-        <v>45.533270921157914</v>
-      </c>
-      <c r="CH14" s="1">
+        <v>22.531099362079278</v>
+      </c>
+      <c r="ET14" s="1">
         <f t="shared" si="43"/>
-        <v>45.077938211946332</v>
-      </c>
-      <c r="CI14" s="1">
+        <v>22.305788368458487</v>
+      </c>
+      <c r="EU14" s="1">
         <f t="shared" si="43"/>
-        <v>44.627158829826868</v>
-      </c>
-      <c r="CJ14" s="1">
+        <v>22.082730484773901</v>
+      </c>
+      <c r="EV14" s="1">
         <f t="shared" si="43"/>
-        <v>44.180887241528602</v>
-      </c>
-      <c r="CK14" s="1">
+        <v>21.861903179926163</v>
+      </c>
+      <c r="EW14" s="1">
         <f t="shared" si="43"/>
-        <v>43.739078369113315</v>
-      </c>
-      <c r="CL14" s="1">
+        <v>21.643284148126902</v>
+      </c>
+      <c r="EX14" s="1">
         <f t="shared" si="43"/>
-        <v>43.301687585422179</v>
-      </c>
-      <c r="CM14" s="1">
+        <v>21.426851306645634</v>
+      </c>
+      <c r="EY14" s="1">
         <f t="shared" si="43"/>
-        <v>42.868670709567958</v>
-      </c>
-      <c r="CN14" s="1">
+        <v>21.212582793579177</v>
+      </c>
+      <c r="EZ14" s="1">
         <f t="shared" si="43"/>
-        <v>42.439984002472279</v>
-      </c>
-      <c r="CO14" s="1">
+        <v>21.000456965643384</v>
+      </c>
+      <c r="FA14" s="1">
         <f t="shared" si="43"/>
-        <v>42.015584162447553</v>
-      </c>
-      <c r="CP14" s="1">
+        <v>20.79045239598695</v>
+      </c>
+      <c r="FB14" s="1">
         <f t="shared" si="43"/>
-        <v>41.595428320823075</v>
-      </c>
-      <c r="CQ14" s="1">
-        <f t="shared" si="43"/>
-        <v>41.179474037614845</v>
-      </c>
-      <c r="CR14" s="1">
-        <f t="shared" si="43"/>
-        <v>40.767679297238693</v>
-      </c>
-      <c r="CS14" s="1">
-        <f t="shared" si="43"/>
-        <v>40.360002504266305</v>
-      </c>
-      <c r="CT14" s="1">
-        <f t="shared" si="43"/>
-        <v>39.956402479223641</v>
-      </c>
-      <c r="CU14" s="1">
-        <f t="shared" si="43"/>
-        <v>39.556838454431407</v>
-      </c>
-      <c r="CV14" s="1">
-        <f t="shared" si="43"/>
-        <v>39.161270069887095</v>
-      </c>
-      <c r="CW14" s="1">
-        <f t="shared" si="43"/>
-        <v>38.769657369188224</v>
-      </c>
-      <c r="CX14" s="1">
-        <f t="shared" si="43"/>
-        <v>38.38196079549634</v>
-      </c>
-      <c r="CY14" s="1">
-        <f t="shared" si="43"/>
-        <v>37.998141187541378</v>
-      </c>
-      <c r="CZ14" s="1">
-        <f t="shared" si="43"/>
-        <v>37.618159775665966</v>
-      </c>
-      <c r="DA14" s="1">
-        <f t="shared" si="43"/>
-        <v>37.241978177909303</v>
-      </c>
-      <c r="DB14" s="1">
-        <f t="shared" si="43"/>
-        <v>36.869558396130209</v>
-      </c>
-      <c r="DC14" s="1">
-        <f t="shared" si="43"/>
-        <v>36.500862812168904</v>
-      </c>
-      <c r="DD14" s="1">
-        <f t="shared" si="43"/>
-        <v>36.135854184047211</v>
-      </c>
-      <c r="DE14" s="1">
-        <f t="shared" si="43"/>
-        <v>35.774495642206738</v>
-      </c>
-      <c r="DF14" s="1">
-        <f t="shared" si="43"/>
-        <v>35.41675068578467</v>
-      </c>
-      <c r="DG14" s="1">
-        <f t="shared" si="43"/>
-        <v>35.062583178926822</v>
-      </c>
-      <c r="DH14" s="1">
-        <f t="shared" si="43"/>
-        <v>34.711957347137556</v>
-      </c>
-      <c r="DI14" s="1">
-        <f t="shared" si="43"/>
-        <v>34.364837773666181</v>
-      </c>
-      <c r="DJ14" s="1">
-        <f t="shared" ref="DJ14:FB14" si="44">DI14*(1+$AY$20)</f>
-        <v>34.021189395929518</v>
-      </c>
-      <c r="DK14" s="1">
-        <f t="shared" si="44"/>
-        <v>33.680977501970226</v>
-      </c>
-      <c r="DL14" s="1">
-        <f t="shared" si="44"/>
-        <v>33.344167726950523</v>
-      </c>
-      <c r="DM14" s="1">
-        <f t="shared" si="44"/>
-        <v>33.010726049681018</v>
-      </c>
-      <c r="DN14" s="1">
-        <f t="shared" si="44"/>
-        <v>32.680618789184209</v>
-      </c>
-      <c r="DO14" s="1">
-        <f t="shared" si="44"/>
-        <v>32.353812601292368</v>
-      </c>
-      <c r="DP14" s="1">
-        <f t="shared" si="44"/>
-        <v>32.030274475279441</v>
-      </c>
-      <c r="DQ14" s="1">
-        <f t="shared" si="44"/>
-        <v>31.709971730526647</v>
-      </c>
-      <c r="DR14" s="1">
-        <f t="shared" si="44"/>
-        <v>31.392872013221378</v>
-      </c>
-      <c r="DS14" s="1">
-        <f t="shared" si="44"/>
-        <v>31.078943293089164</v>
-      </c>
-      <c r="DT14" s="1">
-        <f t="shared" si="44"/>
-        <v>30.768153860158272</v>
-      </c>
-      <c r="DU14" s="1">
-        <f t="shared" si="44"/>
-        <v>30.46047232155669</v>
-      </c>
-      <c r="DV14" s="1">
-        <f t="shared" si="44"/>
-        <v>30.155867598341121</v>
-      </c>
-      <c r="DW14" s="1">
-        <f t="shared" si="44"/>
-        <v>29.85430892235771</v>
-      </c>
-      <c r="DX14" s="1">
-        <f t="shared" si="44"/>
-        <v>29.555765833134132</v>
-      </c>
-      <c r="DY14" s="1">
-        <f t="shared" si="44"/>
-        <v>29.260208174802791</v>
-      </c>
-      <c r="DZ14" s="1">
-        <f t="shared" si="44"/>
-        <v>28.967606093054762</v>
-      </c>
-      <c r="EA14" s="1">
-        <f t="shared" si="44"/>
-        <v>28.677930032124213</v>
-      </c>
-      <c r="EB14" s="1">
-        <f t="shared" si="44"/>
-        <v>28.39115073180297</v>
-      </c>
-      <c r="EC14" s="1">
-        <f t="shared" si="44"/>
-        <v>28.107239224484939</v>
-      </c>
-      <c r="ED14" s="1">
-        <f t="shared" si="44"/>
-        <v>27.826166832240091</v>
-      </c>
-      <c r="EE14" s="1">
-        <f t="shared" si="44"/>
-        <v>27.54790516391769</v>
-      </c>
-      <c r="EF14" s="1">
-        <f t="shared" si="44"/>
-        <v>27.272426112278513</v>
-      </c>
-      <c r="EG14" s="1">
-        <f t="shared" si="44"/>
-        <v>26.999701851155727</v>
-      </c>
-      <c r="EH14" s="1">
-        <f t="shared" si="44"/>
-        <v>26.72970483264417</v>
-      </c>
-      <c r="EI14" s="1">
-        <f t="shared" si="44"/>
-        <v>26.46240778431773</v>
-      </c>
-      <c r="EJ14" s="1">
-        <f t="shared" si="44"/>
-        <v>26.197783706474553</v>
-      </c>
-      <c r="EK14" s="1">
-        <f t="shared" si="44"/>
-        <v>25.935805869409808</v>
-      </c>
-      <c r="EL14" s="1">
-        <f t="shared" si="44"/>
-        <v>25.676447810715711</v>
-      </c>
-      <c r="EM14" s="1">
-        <f t="shared" si="44"/>
-        <v>25.419683332608553</v>
-      </c>
-      <c r="EN14" s="1">
-        <f t="shared" si="44"/>
-        <v>25.165486499282469</v>
-      </c>
-      <c r="EO14" s="1">
-        <f t="shared" si="44"/>
-        <v>24.913831634289643</v>
-      </c>
-      <c r="EP14" s="1">
-        <f t="shared" si="44"/>
-        <v>24.664693317946746</v>
-      </c>
-      <c r="EQ14" s="1">
-        <f t="shared" si="44"/>
-        <v>24.41804638476728</v>
-      </c>
-      <c r="ER14" s="1">
-        <f t="shared" si="44"/>
-        <v>24.173865920919607</v>
-      </c>
-      <c r="ES14" s="1">
-        <f t="shared" si="44"/>
-        <v>23.932127261710409</v>
-      </c>
-      <c r="ET14" s="1">
-        <f t="shared" si="44"/>
-        <v>23.692805989093305</v>
-      </c>
-      <c r="EU14" s="1">
-        <f t="shared" si="44"/>
-        <v>23.455877929202373</v>
-      </c>
-      <c r="EV14" s="1">
-        <f t="shared" si="44"/>
-        <v>23.22131914991035</v>
-      </c>
-      <c r="EW14" s="1">
-        <f t="shared" si="44"/>
-        <v>22.989105958411248</v>
-      </c>
-      <c r="EX14" s="1">
-        <f t="shared" si="44"/>
-        <v>22.759214898827135</v>
-      </c>
-      <c r="EY14" s="1">
-        <f t="shared" si="44"/>
-        <v>22.531622749838863</v>
-      </c>
-      <c r="EZ14" s="1">
-        <f t="shared" si="44"/>
-        <v>22.306306522340474</v>
-      </c>
-      <c r="FA14" s="1">
-        <f t="shared" si="44"/>
-        <v>22.083243457117071</v>
-      </c>
-      <c r="FB14" s="1">
-        <f t="shared" si="44"/>
-        <v>21.862411022545899</v>
+        <v>20.582547872027082</v>
       </c>
     </row>
     <row r="15" spans="2:158" x14ac:dyDescent="0.3">
@@ -3478,20 +3471,20 @@
         <v>104.9</v>
       </c>
       <c r="Y15" s="4">
-        <f>104.9</f>
-        <v>104.9</v>
+        <f>105.8</f>
+        <v>105.8</v>
       </c>
       <c r="Z15" s="4">
-        <f>104.9</f>
-        <v>104.9</v>
+        <f>105.8</f>
+        <v>105.8</v>
       </c>
       <c r="AA15" s="4">
-        <f>104.9</f>
-        <v>104.9</v>
+        <f>105.8</f>
+        <v>105.8</v>
       </c>
       <c r="AB15" s="4">
-        <f>104.9</f>
-        <v>104.9</v>
+        <f>105.8</f>
+        <v>105.8</v>
       </c>
       <c r="AC15" s="4"/>
       <c r="AE15" s="4">
@@ -3513,52 +3506,52 @@
         <v>92.2</v>
       </c>
       <c r="AK15" s="4">
-        <f t="shared" ref="AK15:AV15" si="45">104.9</f>
+        <f t="shared" ref="AK15" si="44">104.9</f>
         <v>104.9</v>
       </c>
       <c r="AL15" s="4">
-        <f t="shared" si="45"/>
-        <v>104.9</v>
+        <f t="shared" ref="AL15:AV15" si="45">105.8</f>
+        <v>105.8</v>
       </c>
       <c r="AM15" s="4">
         <f t="shared" si="45"/>
-        <v>104.9</v>
+        <v>105.8</v>
       </c>
       <c r="AN15" s="4">
         <f t="shared" si="45"/>
-        <v>104.9</v>
+        <v>105.8</v>
       </c>
       <c r="AO15" s="4">
         <f t="shared" si="45"/>
-        <v>104.9</v>
+        <v>105.8</v>
       </c>
       <c r="AP15" s="4">
         <f t="shared" si="45"/>
-        <v>104.9</v>
+        <v>105.8</v>
       </c>
       <c r="AQ15" s="4">
         <f t="shared" si="45"/>
-        <v>104.9</v>
+        <v>105.8</v>
       </c>
       <c r="AR15" s="4">
         <f t="shared" si="45"/>
-        <v>104.9</v>
+        <v>105.8</v>
       </c>
       <c r="AS15" s="4">
         <f t="shared" si="45"/>
-        <v>104.9</v>
+        <v>105.8</v>
       </c>
       <c r="AT15" s="4">
         <f t="shared" si="45"/>
-        <v>104.9</v>
+        <v>105.8</v>
       </c>
       <c r="AU15" s="4">
         <f t="shared" si="45"/>
-        <v>104.9</v>
+        <v>105.8</v>
       </c>
       <c r="AV15" s="4">
         <f t="shared" si="45"/>
-        <v>104.9</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="16" spans="2:158" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3651,19 +3644,19 @@
       </c>
       <c r="Y16" s="7">
         <f t="shared" ref="Y16:AB16" si="51">Y14/Y15</f>
-        <v>-0.10779599618684461</v>
+        <v>-9.829867674858192E-2</v>
       </c>
       <c r="Z16" s="7">
         <f t="shared" si="51"/>
-        <v>-0.18079122974261211</v>
+        <v>-0.19754253308128514</v>
       </c>
       <c r="AA16" s="7">
         <f t="shared" si="51"/>
-        <v>-5.0333651096282198E-2</v>
+        <v>-4.9905482041587929E-2</v>
       </c>
       <c r="AB16" s="7">
         <f t="shared" si="51"/>
-        <v>3.9922211630124049E-2</v>
+        <v>8.8317580340270042E-4</v>
       </c>
       <c r="AC16" s="7"/>
       <c r="AE16" s="7">
@@ -3696,47 +3689,47 @@
       </c>
       <c r="AL16" s="7">
         <f t="shared" si="52"/>
-        <v>-0.29899866539561537</v>
+        <v>-0.33824725897920427</v>
       </c>
       <c r="AM16" s="7">
         <f t="shared" si="52"/>
-        <v>-0.13777862173498606</v>
+        <v>-0.19008661984877143</v>
       </c>
       <c r="AN16" s="7">
         <f t="shared" si="52"/>
-        <v>7.6178447588179016E-2</v>
+        <v>2.6375322589792069E-2</v>
       </c>
       <c r="AO16" s="7">
         <f t="shared" si="52"/>
-        <v>0.30590612139466156</v>
+        <v>0.25954418219886594</v>
       </c>
       <c r="AP16" s="7">
         <f t="shared" si="52"/>
-        <v>0.37946847584170623</v>
+        <v>0.33413368171627683</v>
       </c>
       <c r="AQ16" s="7">
         <f t="shared" si="52"/>
-        <v>0.41840223087632722</v>
+        <v>0.37356774228074635</v>
       </c>
       <c r="AR16" s="7">
         <f t="shared" si="52"/>
-        <v>0.45840470235204178</v>
+        <v>0.41409831360649041</v>
       </c>
       <c r="AS16" s="7">
         <f t="shared" ref="AS16:AV16" si="53">AS14/AS15</f>
-        <v>0.49949946293563247</v>
+        <v>0.4557498136746545</v>
       </c>
       <c r="AT16" s="7">
         <f t="shared" si="53"/>
-        <v>0.54171055766833276</v>
+        <v>0.49854715598777871</v>
       </c>
       <c r="AU16" s="7">
         <f t="shared" si="53"/>
-        <v>0.58506251279066313</v>
+        <v>0.5425157590203683</v>
       </c>
       <c r="AV16" s="7">
         <f t="shared" si="53"/>
-        <v>0.62958034471857205</v>
+        <v>0.58768155583792836</v>
       </c>
     </row>
     <row r="18" spans="2:51" x14ac:dyDescent="0.3">
@@ -3816,11 +3809,11 @@
       </c>
       <c r="Y18" s="9">
         <f t="shared" ref="Y18" si="67">Y3/U3-1</f>
-        <v>5.0000000000000044E-2</v>
+        <v>9.6353394604209885E-2</v>
       </c>
       <c r="Z18" s="9">
         <f t="shared" ref="Z18" si="68">Z3/V3-1</f>
-        <v>0.14999999999999991</v>
+        <v>0.22502870264064301</v>
       </c>
       <c r="AA18" s="9">
         <f t="shared" ref="AA18" si="69">AA3/W3-1</f>
@@ -3858,7 +3851,7 @@
       </c>
       <c r="AL18" s="9">
         <f t="shared" si="71"/>
-        <v>0.1045123062898814</v>
+        <v>0.13128228501975081</v>
       </c>
       <c r="AM18" s="9">
         <f t="shared" si="71"/>
@@ -3992,11 +3985,11 @@
       </c>
       <c r="Y19" s="9">
         <f t="shared" ref="Y19:AB19" si="79">Y5/Y3</f>
-        <v>0.25</v>
+        <v>0.27690643591130348</v>
       </c>
       <c r="Z19" s="9">
         <f t="shared" si="79"/>
-        <v>0.25</v>
+        <v>0.26835363948766017</v>
       </c>
       <c r="AA19" s="9">
         <f t="shared" si="79"/>
@@ -4037,7 +4030,7 @@
       </c>
       <c r="AL19" s="9">
         <f t="shared" si="80"/>
-        <v>0.25298683613254652</v>
+        <v>0.26354252561743746</v>
       </c>
       <c r="AM19" s="9">
         <f t="shared" si="80"/>
@@ -4171,11 +4164,11 @@
       </c>
       <c r="Y20" s="9">
         <f t="shared" ref="Y20:AB20" si="85">Y8/Y3</f>
-        <v>-2.9254020018917734E-2</v>
+        <v>-5.9491617090318208E-3</v>
       </c>
       <c r="Z20" s="9">
         <f t="shared" si="85"/>
-        <v>-6.734970631790882E-2</v>
+        <v>-5.2796001249609377E-2</v>
       </c>
       <c r="AA20" s="9">
         <f t="shared" si="85"/>
@@ -4183,7 +4176,7 @@
       </c>
       <c r="AB20" s="9">
         <f t="shared" si="85"/>
-        <v>1.9334991249884904E-2</v>
+        <v>7.5499677627337367E-3</v>
       </c>
       <c r="AC20" s="9"/>
       <c r="AE20" s="9">
@@ -4216,47 +4209,47 @@
       </c>
       <c r="AL20" s="9">
         <f t="shared" si="86"/>
-        <v>-1.7704645180814077E-2</v>
+        <v>-1.300089979989512E-2</v>
       </c>
       <c r="AM20" s="9">
         <f t="shared" si="86"/>
-        <v>-2.5792976311994399E-3</v>
+        <v>-8.2757885411965833E-3</v>
       </c>
       <c r="AN20" s="9">
         <f t="shared" si="86"/>
-        <v>1.492296801540627E-2</v>
+        <v>9.3892339885519038E-3</v>
       </c>
       <c r="AO20" s="9">
         <f t="shared" si="86"/>
-        <v>3.2280959322654179E-2</v>
+        <v>2.6906852238882149E-2</v>
       </c>
       <c r="AP20" s="9">
         <f t="shared" si="86"/>
-        <v>3.7091037782408458E-2</v>
+        <v>3.1821282292496131E-2</v>
       </c>
       <c r="AQ20" s="9">
         <f t="shared" si="86"/>
-        <v>3.9472498196306417E-2</v>
+        <v>3.4254406975903012E-2</v>
       </c>
       <c r="AR20" s="9">
         <f t="shared" si="86"/>
-        <v>4.1830610959087751E-2</v>
+        <v>3.6663677495747102E-2</v>
       </c>
       <c r="AS20" s="9">
         <f t="shared" ref="AS20:AV20" si="87">AS8/AS3</f>
-        <v>4.4165604969292789E-2</v>
+        <v>3.9049327716377036E-2</v>
       </c>
       <c r="AT20" s="9">
         <f t="shared" si="87"/>
-        <v>4.6477706881358508E-2</v>
+        <v>4.1411589209353714E-2</v>
       </c>
       <c r="AU20" s="9">
         <f t="shared" si="87"/>
-        <v>4.8767141127619706E-2</v>
+        <v>4.3750691275928691E-2</v>
       </c>
       <c r="AV20" s="9">
         <f t="shared" si="87"/>
-        <v>5.1034129940094021E-2</v>
+        <v>4.6066860969301959E-2</v>
       </c>
       <c r="AX20" t="s">
         <v>38</v>
@@ -4344,11 +4337,11 @@
       </c>
       <c r="Y21" s="9">
         <f t="shared" ref="Y21:Y22" si="90">Y6/U6-1</f>
-        <v>2.0000000000000018E-2</v>
+        <v>8.4788029925187081E-2</v>
       </c>
       <c r="Z21" s="9">
         <f t="shared" ref="Z21:Z22" si="91">Z6/V6-1</f>
-        <v>0.10000000000000009</v>
+        <v>0.21164772727272707</v>
       </c>
       <c r="AA21" s="9">
         <f t="shared" ref="AA21:AA22" si="92">AA6/W6-1</f>
@@ -4356,7 +4349,7 @@
       </c>
       <c r="AB21" s="9">
         <f t="shared" ref="AB21:AB22" si="93">AB6/X6-1</f>
-        <v>2.0000000000000018E-2</v>
+        <v>8.0000000000000071E-2</v>
       </c>
       <c r="AC21" s="9"/>
       <c r="AE21" s="9"/>
@@ -4386,7 +4379,7 @@
       </c>
       <c r="AL21" s="9">
         <f t="shared" si="94"/>
-        <v>4.5338709677419597E-2</v>
+        <v>0.10396451612903235</v>
       </c>
       <c r="AM21" s="9">
         <f t="shared" si="94"/>
@@ -4514,11 +4507,11 @@
       </c>
       <c r="Y22" s="9">
         <f t="shared" si="90"/>
-        <v>3.0000000000000027E-2</v>
+        <v>6.024096385542177E-2</v>
       </c>
       <c r="Z22" s="9">
         <f t="shared" si="91"/>
-        <v>3.0000000000000027E-2</v>
+        <v>5.7471264367816577E-3</v>
       </c>
       <c r="AA22" s="9">
         <f t="shared" si="92"/>
@@ -4556,7 +4549,7 @@
       </c>
       <c r="AL22" s="9">
         <f t="shared" si="100"/>
-        <v>3.0000000000000027E-2</v>
+        <v>3.1185185185185205E-2</v>
       </c>
       <c r="AM22" s="9">
         <f t="shared" si="100"/>
@@ -4603,7 +4596,7 @@
       </c>
       <c r="AY22" s="4">
         <f>NPV(AY21,AL14:FB14)</f>
-        <v>365.31081817900622</v>
+        <v>323.35757658859006</v>
       </c>
     </row>
     <row r="23" spans="2:51" x14ac:dyDescent="0.3">
@@ -4697,11 +4690,11 @@
       </c>
       <c r="Y23" s="9">
         <f t="shared" ref="Y23:AB23" si="104">Y12/Y11</f>
-        <v>0.2</v>
+        <v>-0.25609756097561076</v>
       </c>
       <c r="Z23" s="9">
         <f t="shared" si="104"/>
-        <v>0.2</v>
+        <v>1.9323671497584575E-2</v>
       </c>
       <c r="AA23" s="9">
         <f t="shared" si="104"/>
@@ -4742,7 +4735,7 @@
       </c>
       <c r="AL23" s="9">
         <f t="shared" si="105"/>
-        <v>0.19999999999999973</v>
+        <v>-1.1399760338239702E-2</v>
       </c>
       <c r="AM23" s="9">
         <f t="shared" si="105"/>
@@ -4758,7 +4751,7 @@
       </c>
       <c r="AP23" s="9">
         <f t="shared" si="105"/>
-        <v>0.19</v>
+        <v>0.19000000000000003</v>
       </c>
       <c r="AQ23" s="9">
         <f t="shared" si="105"/>
@@ -4766,7 +4759,7 @@
       </c>
       <c r="AR23" s="9">
         <f t="shared" si="105"/>
-        <v>0.19</v>
+        <v>0.19000000000000003</v>
       </c>
       <c r="AS23" s="9">
         <f t="shared" ref="AS23:AV23" si="106">AS12/AS11</f>
@@ -4789,7 +4782,7 @@
       </c>
       <c r="AY23" s="4">
         <f>Main!D8</f>
-        <v>-64.099999999999994</v>
+        <v>-17.200000000000003</v>
       </c>
     </row>
     <row r="24" spans="2:51" x14ac:dyDescent="0.3">
@@ -4883,11 +4876,11 @@
       </c>
       <c r="Y24" s="9">
         <f t="shared" ref="Y24:AB24" si="109">Y14/Y3</f>
-        <v>-3.1928056132028856E-2</v>
+        <v>-2.8123309897241662E-2</v>
       </c>
       <c r="Z24" s="9">
         <f t="shared" si="109"/>
-        <v>-6.3112530990532323E-2</v>
+        <v>-6.5292096219931164E-2</v>
       </c>
       <c r="AA24" s="9">
         <f t="shared" si="109"/>
@@ -4895,7 +4888,7 @@
       </c>
       <c r="AB24" s="9">
         <f t="shared" si="109"/>
-        <v>9.6431795155199704E-3</v>
+        <v>2.1516072579903678E-4</v>
       </c>
       <c r="AC24" s="9"/>
       <c r="AE24" s="9">
@@ -4928,54 +4921,54 @@
       </c>
       <c r="AL24" s="9">
         <f t="shared" si="110"/>
-        <v>-2.1571796035708919E-2</v>
+        <v>-2.4030405178549718E-2</v>
       </c>
       <c r="AM24" s="9">
         <f t="shared" si="110"/>
-        <v>-9.3776285495609304E-3</v>
+        <v>-1.2740089835555307E-2</v>
       </c>
       <c r="AN24" s="9">
         <f t="shared" si="110"/>
-        <v>4.9380332426333029E-3</v>
+        <v>1.6835631967254629E-3</v>
       </c>
       <c r="AO24" s="9">
         <f t="shared" si="110"/>
-        <v>1.9066752075060318E-2</v>
+        <v>1.5929773559627589E-2</v>
       </c>
       <c r="AP24" s="9">
         <f t="shared" si="110"/>
-        <v>2.2962915627461281E-2</v>
+        <v>1.991046190305492E-2</v>
       </c>
       <c r="AQ24" s="9">
         <f t="shared" si="110"/>
-        <v>2.482247871000991E-2</v>
+        <v>2.1823795085302067E-2</v>
       </c>
       <c r="AR24" s="9">
         <f t="shared" si="110"/>
-        <v>2.6662449608362806E-2</v>
+        <v>2.3717242691030885E-2</v>
       </c>
       <c r="AS24" s="9">
         <f t="shared" ref="AS24:AV24" si="111">AS14/AS3</f>
-        <v>2.8483007057918123E-2</v>
+        <v>2.5590988623853641E-2</v>
       </c>
       <c r="AT24" s="9">
         <f t="shared" si="111"/>
-        <v>3.0284327910934404E-2</v>
+        <v>2.7445214876043064E-2</v>
       </c>
       <c r="AU24" s="9">
         <f t="shared" si="111"/>
-        <v>3.2066587153710226E-2</v>
+        <v>2.9280101546208668E-2</v>
       </c>
       <c r="AV24" s="9">
         <f t="shared" si="111"/>
-        <v>3.382995792358244E-2</v>
+        <v>3.1095826856789112E-2</v>
       </c>
       <c r="AX24" t="s">
         <v>42</v>
       </c>
       <c r="AY24" s="4">
         <f>AY22+AY23</f>
-        <v>301.2108181790062</v>
+        <v>306.15757658859008</v>
       </c>
     </row>
     <row r="25" spans="2:51" x14ac:dyDescent="0.3">
@@ -4984,7 +4977,7 @@
       </c>
       <c r="AY25" s="5">
         <f>AY24/AR15</f>
-        <v>2.8714091342135957</v>
+        <v>2.8937389091549157</v>
       </c>
     </row>
     <row r="26" spans="2:51" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4995,6 +4988,10 @@
         <f>X14</f>
         <v>2.2000000000000481</v>
       </c>
+      <c r="Z26" s="8">
+        <f>Z14</f>
+        <v>-20.899999999999967</v>
+      </c>
       <c r="AG26" s="8">
         <f t="shared" ref="AG26:AL26" si="112">AG14</f>
         <v>103.30000000000001</v>
@@ -5017,54 +5014,54 @@
       </c>
       <c r="AL26" s="8">
         <f t="shared" si="112"/>
-        <v>-31.364960000000053</v>
+        <v>-35.78655999999981</v>
       </c>
       <c r="AM26" s="8">
         <f t="shared" ref="AM26:AV26" si="113">AM14</f>
-        <v>-14.452977420000039</v>
+        <v>-20.111164380000016</v>
       </c>
       <c r="AN26" s="8">
         <f t="shared" si="113"/>
-        <v>7.9911191519999791</v>
+        <v>2.7905091300000007</v>
       </c>
       <c r="AO26" s="8">
         <f t="shared" si="113"/>
-        <v>32.0895521343</v>
+        <v>27.459774476640014</v>
       </c>
       <c r="AP26" s="8">
         <f t="shared" si="113"/>
-        <v>39.806243115794985</v>
+        <v>35.351343525582088</v>
       </c>
       <c r="AQ26" s="8">
         <f t="shared" si="113"/>
-        <v>43.890394018926727</v>
+        <v>39.523467133302965</v>
       </c>
       <c r="AR26" s="8">
         <f t="shared" si="113"/>
-        <v>48.086653276729187</v>
+        <v>43.811601579566684</v>
       </c>
       <c r="AS26" s="8">
         <f t="shared" si="113"/>
-        <v>52.397493661947848</v>
+        <v>48.218330286778446</v>
       </c>
       <c r="AT26" s="8">
         <f t="shared" si="113"/>
-        <v>56.82543749940811</v>
+        <v>52.746289103506989</v>
       </c>
       <c r="AU26" s="8">
         <f t="shared" si="113"/>
-        <v>61.373057591740562</v>
+        <v>57.39816730435497</v>
       </c>
       <c r="AV26" s="8">
         <f t="shared" si="113"/>
-        <v>66.042978160978208</v>
+        <v>62.176708607652813</v>
       </c>
       <c r="AX26" t="s">
         <v>44</v>
       </c>
       <c r="AY26" s="5">
         <f>Main!D3</f>
-        <v>7.37</v>
+        <v>8.8800000000000008</v>
       </c>
     </row>
     <row r="27" spans="2:51" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5075,6 +5072,9 @@
         <f>2.7</f>
         <v>2.7</v>
       </c>
+      <c r="Z27" s="8">
+        <v>-30.6</v>
+      </c>
       <c r="AG27" s="8">
         <v>103.2</v>
       </c>
@@ -5092,54 +5092,54 @@
       </c>
       <c r="AL27" s="8">
         <f>AL26*0.9</f>
-        <v>-28.228464000000049</v>
+        <v>-32.207903999999829</v>
       </c>
       <c r="AM27" s="8">
         <f t="shared" ref="AM27:AV27" si="114">AM26*0.9</f>
-        <v>-13.007679678000036</v>
+        <v>-18.100047942000014</v>
       </c>
       <c r="AN27" s="8">
         <f t="shared" si="114"/>
-        <v>7.1920072367999817</v>
+        <v>2.5114582170000008</v>
       </c>
       <c r="AO27" s="8">
         <f t="shared" si="114"/>
-        <v>28.880596920870001</v>
+        <v>24.713797028976014</v>
       </c>
       <c r="AP27" s="8">
         <f t="shared" si="114"/>
-        <v>35.825618804215488</v>
+        <v>31.816209173023879</v>
       </c>
       <c r="AQ27" s="8">
         <f t="shared" si="114"/>
-        <v>39.501354617034053</v>
+        <v>35.571120419972672</v>
       </c>
       <c r="AR27" s="8">
         <f t="shared" si="114"/>
-        <v>43.277987949056268</v>
+        <v>39.43044142161002</v>
       </c>
       <c r="AS27" s="8">
         <f t="shared" si="114"/>
-        <v>47.157744295753062</v>
+        <v>43.396497258100602</v>
       </c>
       <c r="AT27" s="8">
         <f t="shared" si="114"/>
-        <v>51.142893749467298</v>
+        <v>47.471660193156289</v>
       </c>
       <c r="AU27" s="8">
         <f t="shared" si="114"/>
-        <v>55.235751832566507</v>
+        <v>51.658350573919478</v>
       </c>
       <c r="AV27" s="8">
         <f t="shared" si="114"/>
-        <v>59.438680344880389</v>
+        <v>55.959037746887532</v>
       </c>
       <c r="AX27" s="1" t="s">
         <v>45</v>
       </c>
       <c r="AY27" s="10">
         <f>AY25/AY26-1</f>
-        <v>-0.61039224773221235</v>
+        <v>-0.67412850122129331</v>
       </c>
     </row>
     <row r="28" spans="2:51" x14ac:dyDescent="0.3">
@@ -5149,6 +5149,9 @@
       <c r="X28" s="4">
         <v>7.5</v>
       </c>
+      <c r="Z28" s="4">
+        <v>18.7</v>
+      </c>
       <c r="AG28" s="4">
         <v>5.8</v>
       </c>
@@ -5221,6 +5224,9 @@
       <c r="X29" s="4">
         <v>4</v>
       </c>
+      <c r="Z29" s="4">
+        <v>6.7</v>
+      </c>
       <c r="AG29" s="4">
         <v>9.3000000000000007</v>
       </c>
@@ -5287,6 +5293,9 @@
       <c r="X30" s="4">
         <v>9.9</v>
       </c>
+      <c r="Z30" s="4">
+        <v>19.600000000000001</v>
+      </c>
       <c r="AG30" s="4">
         <v>33.9</v>
       </c>
@@ -5348,83 +5357,55 @@
     </row>
     <row r="31" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>82</v>
-      </c>
-      <c r="X31" s="4">
-        <v>-2.6</v>
-      </c>
-      <c r="AG31" s="4">
-        <f>2.6+4.1</f>
-        <v>6.6999999999999993</v>
-      </c>
-      <c r="AH31" s="4">
-        <f>1.5+4.9</f>
-        <v>6.4</v>
-      </c>
-      <c r="AI31" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="AJ31" s="4">
-        <v>0</v>
-      </c>
-      <c r="AK31" s="4">
-        <v>-2.6</v>
-      </c>
-      <c r="AL31" s="4">
-        <v>0</v>
-      </c>
-      <c r="AM31" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN31" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO31" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP31" s="4">
-        <v>0</v>
-      </c>
-      <c r="AQ31" s="4">
-        <v>0</v>
-      </c>
-      <c r="AR31" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS31" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT31" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU31" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV31" s="4">
-        <v>0</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="X31" s="4"/>
+      <c r="Z31" s="4">
+        <v>2.8</v>
+      </c>
+      <c r="AG31" s="4"/>
+      <c r="AH31" s="4"/>
+      <c r="AI31" s="4"/>
+      <c r="AJ31" s="4"/>
+      <c r="AK31" s="4"/>
+      <c r="AL31" s="4"/>
+      <c r="AM31" s="4"/>
+      <c r="AN31" s="4"/>
+      <c r="AO31" s="4"/>
+      <c r="AP31" s="4"/>
+      <c r="AQ31" s="4"/>
+      <c r="AR31" s="4"/>
+      <c r="AS31" s="4"/>
+      <c r="AT31" s="4"/>
+      <c r="AU31" s="4"/>
+      <c r="AV31" s="4"/>
     </row>
     <row r="32" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="X32" s="4">
-        <v>-1.4</v>
+        <v>-2.6</v>
+      </c>
+      <c r="Z32" s="4">
+        <v>2.6</v>
       </c>
       <c r="AG32" s="4">
-        <v>-7.5</v>
+        <f>2.6+4.1</f>
+        <v>6.6999999999999993</v>
       </c>
       <c r="AH32" s="4">
-        <v>-12</v>
+        <f>1.5+4.9</f>
+        <v>6.4</v>
       </c>
       <c r="AI32" s="4">
-        <v>-21.7</v>
+        <v>0.4</v>
       </c>
       <c r="AJ32" s="4">
-        <v>-6.3</v>
+        <v>0</v>
       </c>
       <c r="AK32" s="4">
-        <v>11.4</v>
+        <v>-2.6</v>
       </c>
       <c r="AL32" s="4">
         <v>0</v>
@@ -5462,25 +5443,28 @@
     </row>
     <row r="33" spans="2:143" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="X33" s="4">
-        <v>2.9</v>
+        <v>-1.4</v>
+      </c>
+      <c r="Z33" s="4">
+        <v>-3.3</v>
       </c>
       <c r="AG33" s="4">
-        <v>2.6</v>
+        <v>-7.5</v>
       </c>
       <c r="AH33" s="4">
-        <v>3.3</v>
+        <v>-12</v>
       </c>
       <c r="AI33" s="4">
-        <v>4.5</v>
+        <v>-21.7</v>
       </c>
       <c r="AJ33" s="4">
-        <v>4.9000000000000004</v>
+        <v>-6.3</v>
       </c>
       <c r="AK33" s="4">
-        <v>5.7</v>
+        <v>11.4</v>
       </c>
       <c r="AL33" s="4">
         <v>0</v>
@@ -5518,25 +5502,28 @@
     </row>
     <row r="34" spans="2:143" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X34" s="4">
-        <v>-42</v>
+        <v>2.9</v>
+      </c>
+      <c r="Z34" s="4">
+        <v>2.2999999999999998</v>
       </c>
       <c r="AG34" s="4">
-        <v>-91.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH34" s="4">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="AI34" s="4">
-        <v>55.8</v>
+        <v>4.5</v>
       </c>
       <c r="AJ34" s="4">
-        <v>-17.7</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AK34" s="4">
-        <v>32.299999999999997</v>
+        <v>5.7</v>
       </c>
       <c r="AL34" s="4">
         <v>0</v>
@@ -5574,25 +5561,28 @@
     </row>
     <row r="35" spans="2:143" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="X35" s="4">
-        <v>27.9</v>
+        <v>-42</v>
+      </c>
+      <c r="Z35" s="4">
+        <v>38</v>
       </c>
       <c r="AG35" s="4">
-        <v>-80.099999999999994</v>
+        <v>-91.5</v>
       </c>
       <c r="AH35" s="4">
-        <v>-71.3</v>
+        <v>0.4</v>
       </c>
       <c r="AI35" s="4">
-        <v>111.3</v>
+        <v>55.8</v>
       </c>
       <c r="AJ35" s="4">
-        <v>-39.5</v>
+        <v>-17.7</v>
       </c>
       <c r="AK35" s="4">
-        <v>18.3</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="AL35" s="4">
         <v>0</v>
@@ -5630,25 +5620,28 @@
     </row>
     <row r="36" spans="2:143" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X36" s="4">
-        <v>5.7</v>
+        <v>27.9</v>
+      </c>
+      <c r="Z36" s="4">
+        <v>-43.7</v>
       </c>
       <c r="AG36" s="4">
-        <v>-8</v>
+        <v>-80.099999999999994</v>
       </c>
       <c r="AH36" s="4">
-        <v>-13.2</v>
+        <v>-71.3</v>
       </c>
       <c r="AI36" s="4">
-        <v>1.3</v>
+        <v>111.3</v>
       </c>
       <c r="AJ36" s="4">
-        <v>1.9</v>
+        <v>-39.5</v>
       </c>
       <c r="AK36" s="4">
-        <v>5.9</v>
+        <v>18.3</v>
       </c>
       <c r="AL36" s="4">
         <v>0</v>
@@ -5686,25 +5679,28 @@
     </row>
     <row r="37" spans="2:143" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X37" s="4">
-        <v>21.8</v>
+        <v>5.7</v>
+      </c>
+      <c r="Z37" s="4">
+        <v>4</v>
       </c>
       <c r="AG37" s="4">
-        <v>116.5</v>
+        <v>-8</v>
       </c>
       <c r="AH37" s="4">
-        <v>-63.7</v>
+        <v>-13.2</v>
       </c>
       <c r="AI37" s="4">
-        <v>-65.900000000000006</v>
+        <v>1.3</v>
       </c>
       <c r="AJ37" s="4">
-        <v>62.2</v>
+        <v>1.9</v>
       </c>
       <c r="AK37" s="4">
-        <v>-39.5</v>
+        <v>5.9</v>
       </c>
       <c r="AL37" s="4">
         <v>0</v>
@@ -5742,705 +5738,778 @@
     </row>
     <row r="38" spans="2:143" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
+        <v>77</v>
+      </c>
+      <c r="X38" s="4">
+        <v>21.8</v>
+      </c>
+      <c r="Z38" s="4">
+        <v>49.6</v>
+      </c>
+      <c r="AG38" s="4">
+        <v>116.5</v>
+      </c>
+      <c r="AH38" s="4">
+        <v>-63.7</v>
+      </c>
+      <c r="AI38" s="4">
+        <v>-65.900000000000006</v>
+      </c>
+      <c r="AJ38" s="4">
+        <v>62.2</v>
+      </c>
+      <c r="AK38" s="4">
+        <v>-39.5</v>
+      </c>
+      <c r="AL38" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM38" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN38" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO38" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP38" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ38" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR38" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS38" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT38" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU38" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV38" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:143" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
         <v>78</v>
       </c>
-      <c r="X38" s="4">
+      <c r="X39" s="4">
         <v>19.2</v>
       </c>
-      <c r="AG38" s="4">
+      <c r="Z39" s="4">
+        <v>-17.7</v>
+      </c>
+      <c r="AG39" s="4">
         <v>77.900000000000006</v>
       </c>
-      <c r="AH38" s="4">
+      <c r="AH39" s="4">
         <v>7</v>
       </c>
-      <c r="AI38" s="4">
+      <c r="AI39" s="4">
         <v>-41</v>
       </c>
-      <c r="AJ38" s="4">
+      <c r="AJ39" s="4">
         <v>3.8</v>
       </c>
-      <c r="AK38" s="4">
+      <c r="AK39" s="4">
         <v>5.3</v>
       </c>
-      <c r="AL38" s="4">
-        <v>0</v>
-      </c>
-      <c r="AM38" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN38" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO38" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP38" s="4">
-        <v>0</v>
-      </c>
-      <c r="AQ38" s="4">
-        <v>0</v>
-      </c>
-      <c r="AR38" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS38" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT38" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU38" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV38" s="4">
+      <c r="AL39" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM39" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP39" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ39" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR39" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS39" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT39" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU39" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV39" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:143" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="1" t="s">
+    <row r="40" spans="2:143" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="X39" s="8">
-        <f>X26+SUM(X27:X38)</f>
-        <v>57.80000000000004</v>
-      </c>
-      <c r="AG39" s="8">
-        <f t="shared" ref="AG39:AM39" si="118">AG26+SUM(AG27:AG38)</f>
+      <c r="X40" s="8">
+        <f>X26+SUM(X28:X39)</f>
+        <v>55.100000000000037</v>
+      </c>
+      <c r="Z40" s="8">
+        <f>Z26+SUM(Z28:Z39)</f>
+        <v>58.700000000000045</v>
+      </c>
+      <c r="AG40" s="8">
+        <f t="shared" ref="AG40:AM40" si="118">AG26+SUM(AG27:AG39)</f>
         <v>272.10000000000002</v>
       </c>
-      <c r="AH39" s="8">
+      <c r="AH40" s="8">
         <f t="shared" si="118"/>
         <v>121.00000000000001</v>
       </c>
-      <c r="AI39" s="8">
+      <c r="AI40" s="8">
         <f t="shared" si="118"/>
         <v>5.6999999999998394</v>
       </c>
-      <c r="AJ39" s="8">
+      <c r="AJ40" s="8">
         <f t="shared" si="118"/>
         <v>92.999999999999929</v>
       </c>
-      <c r="AK39" s="8">
+      <c r="AK40" s="8">
         <f t="shared" si="118"/>
         <v>-62.199999999999847</v>
       </c>
-      <c r="AL39" s="8">
+      <c r="AL40" s="8">
         <f t="shared" si="118"/>
-        <v>22.806575999999893</v>
-      </c>
-      <c r="AM39" s="8">
+        <v>14.40553600000036</v>
+      </c>
+      <c r="AM40" s="8">
         <f t="shared" si="118"/>
-        <v>49.707342901999922</v>
-      </c>
-      <c r="AN39" s="8">
-        <f t="shared" ref="AN39:AV39" si="119">AN26+SUM(AN27:AN38)</f>
-        <v>87.841286388799958</v>
-      </c>
-      <c r="AO39" s="8">
+        <v>38.956787677999969</v>
+      </c>
+      <c r="AN40" s="8">
+        <f t="shared" ref="AN40:AV40" si="119">AN26+SUM(AN27:AN39)</f>
+        <v>77.960127346999997</v>
+      </c>
+      <c r="AO40" s="8">
         <f t="shared" si="119"/>
-        <v>129.73872025516999</v>
-      </c>
-      <c r="AP39" s="8">
+        <v>120.94214270561602</v>
+      </c>
+      <c r="AP40" s="8">
         <f t="shared" si="119"/>
-        <v>141.04441666401047</v>
-      </c>
-      <c r="AQ39" s="8">
+        <v>132.58010744260596</v>
+      </c>
+      <c r="AQ40" s="8">
         <f t="shared" si="119"/>
-        <v>145.90813163804077</v>
-      </c>
-      <c r="AR39" s="8">
+        <v>137.61097055535564</v>
+      </c>
+      <c r="AR40" s="8">
         <f t="shared" si="119"/>
-        <v>151.38198383521504</v>
-      </c>
-      <c r="AS39" s="8">
+        <v>143.2593856106063</v>
+      </c>
+      <c r="AS40" s="8">
         <f t="shared" si="119"/>
-        <v>157.41732596168197</v>
-      </c>
-      <c r="AT39" s="8">
+        <v>149.47691554886009</v>
+      </c>
+      <c r="AT40" s="8">
         <f t="shared" si="119"/>
-        <v>163.97357314188142</v>
-      </c>
-      <c r="AU39" s="8">
+        <v>156.22319118966931</v>
+      </c>
+      <c r="AU40" s="8">
         <f t="shared" si="119"/>
-        <v>171.0170150387479</v>
-      </c>
-      <c r="AV39" s="8">
+        <v>163.46472349271528</v>
+      </c>
+      <c r="AV40" s="8">
         <f t="shared" si="119"/>
-        <v>178.51980641966321</v>
+        <v>171.17389426834498</v>
       </c>
     </row>
-    <row r="40" spans="2:143" x14ac:dyDescent="0.3">
-      <c r="B40" t="s">
+    <row r="41" spans="2:143" x14ac:dyDescent="0.3">
+      <c r="B41" t="s">
         <v>80</v>
       </c>
-      <c r="X40" s="4">
+      <c r="X41" s="4">
         <v>1.5</v>
       </c>
-      <c r="AG40" s="4">
+      <c r="Z41" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="AG41" s="4">
         <v>9</v>
       </c>
-      <c r="AH40" s="4">
+      <c r="AH41" s="4">
         <v>11</v>
       </c>
-      <c r="AI40" s="4">
+      <c r="AI41" s="4">
         <v>12.8</v>
       </c>
-      <c r="AJ40" s="4">
+      <c r="AJ41" s="4">
         <v>12.8</v>
       </c>
-      <c r="AK40" s="4">
+      <c r="AK41" s="4">
         <v>9.8000000000000007</v>
       </c>
-      <c r="AL40" s="4">
-        <f>AK40*1.05</f>
+      <c r="AL41" s="4">
+        <f>AK41*1.05</f>
         <v>10.290000000000001</v>
       </c>
-      <c r="AM40" s="4">
-        <f t="shared" ref="AM40:AV40" si="120">AL40*1.05</f>
+      <c r="AM41" s="4">
+        <f t="shared" ref="AM41:AV41" si="120">AL41*1.05</f>
         <v>10.804500000000001</v>
       </c>
-      <c r="AN40" s="4">
+      <c r="AN41" s="4">
         <f t="shared" si="120"/>
         <v>11.344725000000002</v>
       </c>
-      <c r="AO40" s="4">
+      <c r="AO41" s="4">
         <f t="shared" si="120"/>
         <v>11.911961250000003</v>
       </c>
-      <c r="AP40" s="4">
+      <c r="AP41" s="4">
         <f t="shared" si="120"/>
         <v>12.507559312500003</v>
       </c>
-      <c r="AQ40" s="4">
+      <c r="AQ41" s="4">
         <f t="shared" si="120"/>
         <v>13.132937278125004</v>
       </c>
-      <c r="AR40" s="4">
+      <c r="AR41" s="4">
         <f t="shared" si="120"/>
         <v>13.789584142031254</v>
       </c>
-      <c r="AS40" s="4">
+      <c r="AS41" s="4">
         <f t="shared" si="120"/>
         <v>14.479063349132817</v>
       </c>
-      <c r="AT40" s="4">
+      <c r="AT41" s="4">
         <f t="shared" si="120"/>
         <v>15.203016516589459</v>
       </c>
-      <c r="AU40" s="4">
+      <c r="AU41" s="4">
         <f t="shared" si="120"/>
         <v>15.963167342418933</v>
       </c>
-      <c r="AV40" s="4">
+      <c r="AV41" s="4">
         <f t="shared" si="120"/>
         <v>16.761325709539879</v>
       </c>
     </row>
-    <row r="41" spans="2:143" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="1" t="s">
+    <row r="42" spans="2:143" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="X41" s="8">
-        <f>X39-X40</f>
-        <v>56.30000000000004</v>
-      </c>
-      <c r="AG41" s="8">
-        <f t="shared" ref="AG41:AM41" si="121">AG39-AG40</f>
+      <c r="X42" s="8">
+        <f>X40-X41</f>
+        <v>53.600000000000037</v>
+      </c>
+      <c r="Z42" s="8">
+        <f>Z40-Z41</f>
+        <v>52.900000000000048</v>
+      </c>
+      <c r="AG42" s="8">
+        <f t="shared" ref="AG42:AM42" si="121">AG40-AG41</f>
         <v>263.10000000000002</v>
       </c>
-      <c r="AH41" s="8">
+      <c r="AH42" s="8">
         <f t="shared" si="121"/>
         <v>110.00000000000001</v>
       </c>
-      <c r="AI41" s="8">
+      <c r="AI42" s="8">
         <f t="shared" si="121"/>
         <v>-7.1000000000001613</v>
       </c>
-      <c r="AJ41" s="8">
+      <c r="AJ42" s="8">
         <f t="shared" si="121"/>
         <v>80.199999999999932</v>
       </c>
-      <c r="AK41" s="8">
+      <c r="AK42" s="8">
         <f t="shared" si="121"/>
         <v>-71.999999999999844</v>
       </c>
-      <c r="AL41" s="8">
+      <c r="AL42" s="8">
         <f t="shared" si="121"/>
-        <v>12.516575999999892</v>
-      </c>
-      <c r="AM41" s="8">
+        <v>4.1155360000003594</v>
+      </c>
+      <c r="AM42" s="8">
         <f t="shared" si="121"/>
-        <v>38.902842901999918</v>
-      </c>
-      <c r="AN41" s="8">
-        <f t="shared" ref="AN41:AV41" si="122">AN39-AN40</f>
-        <v>76.496561388799961</v>
-      </c>
-      <c r="AO41" s="8">
+        <v>28.152287677999968</v>
+      </c>
+      <c r="AN42" s="8">
+        <f t="shared" ref="AN42:AV42" si="122">AN40-AN41</f>
+        <v>66.615402347</v>
+      </c>
+      <c r="AO42" s="8">
         <f t="shared" si="122"/>
-        <v>117.82675900516999</v>
-      </c>
-      <c r="AP41" s="8">
+        <v>109.03018145561602</v>
+      </c>
+      <c r="AP42" s="8">
         <f t="shared" si="122"/>
-        <v>128.53685735151046</v>
-      </c>
-      <c r="AQ41" s="8">
+        <v>120.07254813010596</v>
+      </c>
+      <c r="AQ42" s="8">
         <f t="shared" si="122"/>
-        <v>132.77519435991576</v>
-      </c>
-      <c r="AR41" s="8">
+        <v>124.47803327723064</v>
+      </c>
+      <c r="AR42" s="8">
         <f t="shared" si="122"/>
-        <v>137.59239969318378</v>
-      </c>
-      <c r="AS41" s="8">
+        <v>129.46980146857504</v>
+      </c>
+      <c r="AS42" s="8">
         <f t="shared" si="122"/>
-        <v>142.93826261254915</v>
-      </c>
-      <c r="AT41" s="8">
+        <v>134.99785219972728</v>
+      </c>
+      <c r="AT42" s="8">
         <f t="shared" si="122"/>
-        <v>148.77055662529196</v>
-      </c>
-      <c r="AU41" s="8">
+        <v>141.02017467307985</v>
+      </c>
+      <c r="AU42" s="8">
         <f t="shared" si="122"/>
-        <v>155.05384769632897</v>
-      </c>
-      <c r="AV41" s="8">
+        <v>147.50155615029635</v>
+      </c>
+      <c r="AV42" s="8">
         <f t="shared" si="122"/>
-        <v>161.75848071012334</v>
-      </c>
-      <c r="AW41" s="1">
-        <f>AV41*(1+$AY$20)</f>
-        <v>160.14089590302211</v>
-      </c>
-      <c r="AX41" s="1">
-        <f t="shared" ref="AX41:DI41" si="123">AW41*(1+$AY$20)</f>
-        <v>158.5394869439919</v>
-      </c>
-      <c r="AY41" s="1">
+        <v>154.41256855880511</v>
+      </c>
+      <c r="AW42" s="1">
+        <f>AV42*(1+$AY$20)</f>
+        <v>152.86844287321705</v>
+      </c>
+      <c r="AX42" s="1">
+        <f t="shared" ref="AX42:DI42" si="123">AW42*(1+$AY$20)</f>
+        <v>151.33975844448489</v>
+      </c>
+      <c r="AY42" s="1">
         <f t="shared" si="123"/>
-        <v>156.95409207455199</v>
-      </c>
-      <c r="AZ41" s="1">
+        <v>149.82636086004004</v>
+      </c>
+      <c r="AZ42" s="1">
         <f t="shared" si="123"/>
-        <v>155.38455115380648</v>
-      </c>
-      <c r="BA41" s="1">
+        <v>148.32809725143963</v>
+      </c>
+      <c r="BA42" s="1">
         <f t="shared" si="123"/>
-        <v>153.83070564226841</v>
-      </c>
-      <c r="BB41" s="1">
+        <v>146.84481627892524</v>
+      </c>
+      <c r="BB42" s="1">
         <f t="shared" si="123"/>
-        <v>152.29239858584572</v>
-      </c>
-      <c r="BC41" s="1">
+        <v>145.37636811613598</v>
+      </c>
+      <c r="BC42" s="1">
         <f t="shared" si="123"/>
-        <v>150.76947459998726</v>
-      </c>
-      <c r="BD41" s="1">
+        <v>143.92260443497463</v>
+      </c>
+      <c r="BD42" s="1">
         <f t="shared" si="123"/>
-        <v>149.26177985398738</v>
-      </c>
-      <c r="BE41" s="1">
+        <v>142.48337839062489</v>
+      </c>
+      <c r="BE42" s="1">
         <f t="shared" si="123"/>
-        <v>147.76916205544751</v>
-      </c>
-      <c r="BF41" s="1">
+        <v>141.05854460671864</v>
+      </c>
+      <c r="BF42" s="1">
         <f t="shared" si="123"/>
-        <v>146.29147043489303</v>
-      </c>
-      <c r="BG41" s="1">
+        <v>139.64795916065145</v>
+      </c>
+      <c r="BG42" s="1">
         <f t="shared" si="123"/>
-        <v>144.82855573054411</v>
-      </c>
-      <c r="BH41" s="1">
+        <v>138.25147956904493</v>
+      </c>
+      <c r="BH42" s="1">
         <f t="shared" si="123"/>
-        <v>143.38027017323867</v>
-      </c>
-      <c r="BI41" s="1">
+        <v>136.86896477335449</v>
+      </c>
+      <c r="BI42" s="1">
         <f t="shared" si="123"/>
-        <v>141.94646747150628</v>
-      </c>
-      <c r="BJ41" s="1">
+        <v>135.50027512562096</v>
+      </c>
+      <c r="BJ42" s="1">
         <f t="shared" si="123"/>
-        <v>140.52700279679121</v>
-      </c>
-      <c r="BK41" s="1">
+        <v>134.14527237436474</v>
+      </c>
+      <c r="BK42" s="1">
         <f t="shared" si="123"/>
-        <v>139.12173276882331</v>
-      </c>
-      <c r="BL41" s="1">
+        <v>132.80381965062108</v>
+      </c>
+      <c r="BL42" s="1">
         <f t="shared" si="123"/>
-        <v>137.73051544113508</v>
-      </c>
-      <c r="BM41" s="1">
+        <v>131.47578145411487</v>
+      </c>
+      <c r="BM42" s="1">
         <f t="shared" si="123"/>
-        <v>136.35321028672374</v>
-      </c>
-      <c r="BN41" s="1">
+        <v>130.16102363957373</v>
+      </c>
+      <c r="BN42" s="1">
         <f t="shared" si="123"/>
-        <v>134.98967818385651</v>
-      </c>
-      <c r="BO41" s="1">
+        <v>128.859413403178</v>
+      </c>
+      <c r="BO42" s="1">
         <f t="shared" si="123"/>
-        <v>133.63978140201795</v>
-      </c>
-      <c r="BP41" s="1">
+        <v>127.57081926914621</v>
+      </c>
+      <c r="BP42" s="1">
         <f t="shared" si="123"/>
-        <v>132.30338358799776</v>
-      </c>
-      <c r="BQ41" s="1">
+        <v>126.29511107645475</v>
+      </c>
+      <c r="BQ42" s="1">
         <f t="shared" si="123"/>
-        <v>130.98034975211777</v>
-      </c>
-      <c r="BR41" s="1">
+        <v>125.0321599656902</v>
+      </c>
+      <c r="BR42" s="1">
         <f t="shared" si="123"/>
-        <v>129.67054625459659</v>
-      </c>
-      <c r="BS41" s="1">
+        <v>123.7818383660333</v>
+      </c>
+      <c r="BS42" s="1">
         <f t="shared" si="123"/>
-        <v>128.37384079205063</v>
-      </c>
-      <c r="BT41" s="1">
+        <v>122.54401998237296</v>
+      </c>
+      <c r="BT42" s="1">
         <f t="shared" si="123"/>
-        <v>127.09010238413012</v>
-      </c>
-      <c r="BU41" s="1">
+        <v>121.31857978254922</v>
+      </c>
+      <c r="BU42" s="1">
         <f t="shared" si="123"/>
-        <v>125.81920136028882</v>
-      </c>
-      <c r="BV41" s="1">
+        <v>120.10539398472373</v>
+      </c>
+      <c r="BV42" s="1">
         <f t="shared" si="123"/>
-        <v>124.56100934668592</v>
-      </c>
-      <c r="BW41" s="1">
+        <v>118.90434004487649</v>
+      </c>
+      <c r="BW42" s="1">
         <f t="shared" si="123"/>
-        <v>123.31539925321906</v>
-      </c>
-      <c r="BX41" s="1">
+        <v>117.71529664442772</v>
+      </c>
+      <c r="BX42" s="1">
         <f t="shared" si="123"/>
-        <v>122.08224526068686</v>
-      </c>
-      <c r="BY41" s="1">
+        <v>116.53814367798344</v>
+      </c>
+      <c r="BY42" s="1">
         <f t="shared" si="123"/>
-        <v>120.86142280807999</v>
-      </c>
-      <c r="BZ41" s="1">
+        <v>115.3727622412036</v>
+      </c>
+      <c r="BZ42" s="1">
         <f t="shared" si="123"/>
-        <v>119.65280857999919</v>
-      </c>
-      <c r="CA41" s="1">
+        <v>114.21903461879157</v>
+      </c>
+      <c r="CA42" s="1">
         <f t="shared" si="123"/>
-        <v>118.45628049419919</v>
-      </c>
-      <c r="CB41" s="1">
+        <v>113.07684427260365</v>
+      </c>
+      <c r="CB42" s="1">
         <f t="shared" si="123"/>
-        <v>117.2717176892572</v>
-      </c>
-      <c r="CC41" s="1">
+        <v>111.94607582987761</v>
+      </c>
+      <c r="CC42" s="1">
         <f t="shared" si="123"/>
-        <v>116.09900051236463</v>
-      </c>
-      <c r="CD41" s="1">
+        <v>110.82661507157884</v>
+      </c>
+      <c r="CD42" s="1">
         <f t="shared" si="123"/>
-        <v>114.93801050724097</v>
-      </c>
-      <c r="CE41" s="1">
+        <v>109.71834892086305</v>
+      </c>
+      <c r="CE42" s="1">
         <f t="shared" si="123"/>
-        <v>113.78863040216856</v>
-      </c>
-      <c r="CF41" s="1">
+        <v>108.62116543165442</v>
+      </c>
+      <c r="CF42" s="1">
         <f t="shared" si="123"/>
-        <v>112.65074409814687</v>
-      </c>
-      <c r="CG41" s="1">
+        <v>107.53495377733788</v>
+      </c>
+      <c r="CG42" s="1">
         <f t="shared" si="123"/>
-        <v>111.5242366571654</v>
-      </c>
-      <c r="CH41" s="1">
+        <v>106.4596042395645</v>
+      </c>
+      <c r="CH42" s="1">
         <f t="shared" si="123"/>
-        <v>110.40899429059375</v>
-      </c>
-      <c r="CI41" s="1">
+        <v>105.39500819716885</v>
+      </c>
+      <c r="CI42" s="1">
         <f t="shared" si="123"/>
-        <v>109.30490434768781</v>
-      </c>
-      <c r="CJ41" s="1">
+        <v>104.34105811519716</v>
+      </c>
+      <c r="CJ42" s="1">
         <f t="shared" si="123"/>
-        <v>108.21185530421093</v>
-      </c>
-      <c r="CK41" s="1">
+        <v>103.29764753404518</v>
+      </c>
+      <c r="CK42" s="1">
         <f t="shared" si="123"/>
-        <v>107.12973675116882</v>
-      </c>
-      <c r="CL41" s="1">
+        <v>102.26467105870474</v>
+      </c>
+      <c r="CL42" s="1">
         <f t="shared" si="123"/>
-        <v>106.05843938365713</v>
-      </c>
-      <c r="CM41" s="1">
+        <v>101.24202434811768</v>
+      </c>
+      <c r="CM42" s="1">
         <f t="shared" si="123"/>
-        <v>104.99785498982055</v>
-      </c>
-      <c r="CN41" s="1">
+        <v>100.22960410463651</v>
+      </c>
+      <c r="CN42" s="1">
         <f t="shared" si="123"/>
-        <v>103.94787643992234</v>
-      </c>
-      <c r="CO41" s="1">
+        <v>99.227308063590144</v>
+      </c>
+      <c r="CO42" s="1">
         <f t="shared" si="123"/>
-        <v>102.90839767552312</v>
-      </c>
-      <c r="CP41" s="1">
+        <v>98.235034982954247</v>
+      </c>
+      <c r="CP42" s="1">
         <f t="shared" si="123"/>
-        <v>101.87931369876789</v>
-      </c>
-      <c r="CQ41" s="1">
+        <v>97.252684633124701</v>
+      </c>
+      <c r="CQ42" s="1">
         <f t="shared" si="123"/>
-        <v>100.86052056178021</v>
-      </c>
-      <c r="CR41" s="1">
+        <v>96.280157786793453</v>
+      </c>
+      <c r="CR42" s="1">
         <f t="shared" si="123"/>
-        <v>99.851915356162408</v>
-      </c>
-      <c r="CS41" s="1">
+        <v>95.317356208925517</v>
+      </c>
+      <c r="CS42" s="1">
         <f t="shared" si="123"/>
-        <v>98.853396202600777</v>
-      </c>
-      <c r="CT41" s="1">
+        <v>94.364182646836255</v>
+      </c>
+      <c r="CT42" s="1">
         <f t="shared" si="123"/>
-        <v>97.864862240574766</v>
-      </c>
-      <c r="CU41" s="1">
+        <v>93.42054082036789</v>
+      </c>
+      <c r="CU42" s="1">
         <f t="shared" si="123"/>
-        <v>96.886213618169023</v>
-      </c>
-      <c r="CV41" s="1">
+        <v>92.486335412164209</v>
+      </c>
+      <c r="CV42" s="1">
         <f t="shared" si="123"/>
-        <v>95.917351481987339</v>
-      </c>
-      <c r="CW41" s="1">
+        <v>91.561472058042568</v>
+      </c>
+      <c r="CW42" s="1">
         <f t="shared" si="123"/>
-        <v>94.958177967167458</v>
-      </c>
-      <c r="CX41" s="1">
+        <v>90.645857337462147</v>
+      </c>
+      <c r="CX42" s="1">
         <f t="shared" si="123"/>
-        <v>94.008596187495783</v>
-      </c>
-      <c r="CY41" s="1">
+        <v>89.739398764087525</v>
+      </c>
+      <c r="CY42" s="1">
         <f t="shared" si="123"/>
-        <v>93.068510225620827</v>
-      </c>
-      <c r="CZ41" s="1">
+        <v>88.842004776446643</v>
+      </c>
+      <c r="CZ42" s="1">
         <f t="shared" si="123"/>
-        <v>92.137825123364621</v>
-      </c>
-      <c r="DA41" s="1">
+        <v>87.953584728682173</v>
+      </c>
+      <c r="DA42" s="1">
         <f t="shared" si="123"/>
-        <v>91.216446872130973</v>
-      </c>
-      <c r="DB41" s="1">
+        <v>87.074048881395356</v>
+      </c>
+      <c r="DB42" s="1">
         <f t="shared" si="123"/>
-        <v>90.304282403409658</v>
-      </c>
-      <c r="DC41" s="1">
+        <v>86.203308392581405</v>
+      </c>
+      <c r="DC42" s="1">
         <f t="shared" si="123"/>
-        <v>89.401239579375556</v>
-      </c>
-      <c r="DD41" s="1">
+        <v>85.341275308655597</v>
+      </c>
+      <c r="DD42" s="1">
         <f t="shared" si="123"/>
-        <v>88.507227183581804</v>
-      </c>
-      <c r="DE41" s="1">
+        <v>84.487862555569038</v>
+      </c>
+      <c r="DE42" s="1">
         <f t="shared" si="123"/>
-        <v>87.62215491174598</v>
-      </c>
-      <c r="DF41" s="1">
+        <v>83.642983930013344</v>
+      </c>
+      <c r="DF42" s="1">
         <f t="shared" si="123"/>
-        <v>86.74593336262852</v>
-      </c>
-      <c r="DG41" s="1">
+        <v>82.806554090713206</v>
+      </c>
+      <c r="DG42" s="1">
         <f t="shared" si="123"/>
-        <v>85.878474029002234</v>
-      </c>
-      <c r="DH41" s="1">
+        <v>81.978488549806073</v>
+      </c>
+      <c r="DH42" s="1">
         <f t="shared" si="123"/>
-        <v>85.019689288712215</v>
-      </c>
-      <c r="DI41" s="1">
+        <v>81.158703664308007</v>
+      </c>
+      <c r="DI42" s="1">
         <f t="shared" si="123"/>
-        <v>84.169492395825088</v>
-      </c>
-      <c r="DJ41" s="1">
-        <f t="shared" ref="DJ41:EM41" si="124">DI41*(1+$AY$20)</f>
-        <v>83.32779747186683</v>
-      </c>
-      <c r="DK41" s="1">
+        <v>80.347116627664931</v>
+      </c>
+      <c r="DJ42" s="1">
+        <f t="shared" ref="DJ42:EM42" si="124">DI42*(1+$AY$20)</f>
+        <v>79.54364546138828</v>
+      </c>
+      <c r="DK42" s="1">
         <f t="shared" si="124"/>
-        <v>82.494519497148161</v>
-      </c>
-      <c r="DL41" s="1">
+        <v>78.748209006774402</v>
+      </c>
+      <c r="DL42" s="1">
         <f t="shared" si="124"/>
-        <v>81.669574302176684</v>
-      </c>
-      <c r="DM41" s="1">
+        <v>77.960726916706662</v>
+      </c>
+      <c r="DM42" s="1">
         <f t="shared" si="124"/>
-        <v>80.852878559154917</v>
-      </c>
-      <c r="DN41" s="1">
+        <v>77.181119647539589</v>
+      </c>
+      <c r="DN42" s="1">
         <f t="shared" si="124"/>
-        <v>80.044349773563368</v>
-      </c>
-      <c r="DO41" s="1">
+        <v>76.409308451064192</v>
+      </c>
+      <c r="DO42" s="1">
         <f t="shared" si="124"/>
-        <v>79.24390627582774</v>
-      </c>
-      <c r="DP41" s="1">
+        <v>75.645215366553543</v>
+      </c>
+      <c r="DP42" s="1">
         <f t="shared" si="124"/>
-        <v>78.451467213069463</v>
-      </c>
-      <c r="DQ41" s="1">
+        <v>74.888763212888009</v>
+      </c>
+      <c r="DQ42" s="1">
         <f t="shared" si="124"/>
-        <v>77.666952540938766</v>
-      </c>
-      <c r="DR41" s="1">
+        <v>74.139875580759124</v>
+      </c>
+      <c r="DR42" s="1">
         <f t="shared" si="124"/>
-        <v>76.890283015529377</v>
-      </c>
-      <c r="DS41" s="1">
+        <v>73.39847682495153</v>
+      </c>
+      <c r="DS42" s="1">
         <f t="shared" si="124"/>
-        <v>76.121380185374079</v>
-      </c>
-      <c r="DT41" s="1">
+        <v>72.664492056702016</v>
+      </c>
+      <c r="DT42" s="1">
         <f t="shared" si="124"/>
-        <v>75.360166383520337</v>
-      </c>
-      <c r="DU41" s="1">
+        <v>71.937847136134991</v>
+      </c>
+      <c r="DU42" s="1">
         <f t="shared" si="124"/>
-        <v>74.606564719685139</v>
-      </c>
-      <c r="DV41" s="1">
+        <v>71.218468664773638</v>
+      </c>
+      <c r="DV42" s="1">
         <f t="shared" si="124"/>
-        <v>73.860499072488281</v>
-      </c>
-      <c r="DW41" s="1">
+        <v>70.506283978125907</v>
+      </c>
+      <c r="DW42" s="1">
         <f t="shared" si="124"/>
-        <v>73.121894081763401</v>
-      </c>
-      <c r="DX41" s="1">
+        <v>69.801221138344644</v>
+      </c>
+      <c r="DX42" s="1">
         <f t="shared" si="124"/>
-        <v>72.39067514094576</v>
-      </c>
-      <c r="DY41" s="1">
+        <v>69.103208926961202</v>
+      </c>
+      <c r="DY42" s="1">
         <f t="shared" si="124"/>
-        <v>71.666768389536301</v>
-      </c>
-      <c r="DZ41" s="1">
+        <v>68.41217683769159</v>
+      </c>
+      <c r="DZ42" s="1">
         <f t="shared" si="124"/>
-        <v>70.950100705640935</v>
-      </c>
-      <c r="EA41" s="1">
+        <v>67.728055069314678</v>
+      </c>
+      <c r="EA42" s="1">
         <f t="shared" si="124"/>
-        <v>70.240599698584532</v>
-      </c>
-      <c r="EB41" s="1">
+        <v>67.050774518621537</v>
+      </c>
+      <c r="EB42" s="1">
         <f t="shared" si="124"/>
-        <v>69.538193701598686</v>
-      </c>
-      <c r="EC41" s="1">
+        <v>66.380266773435324</v>
+      </c>
+      <c r="EC42" s="1">
         <f t="shared" si="124"/>
-        <v>68.842811764582706</v>
-      </c>
-      <c r="ED41" s="1">
+        <v>65.716464105700965</v>
+      </c>
+      <c r="ED42" s="1">
         <f t="shared" si="124"/>
-        <v>68.154383646936878</v>
-      </c>
-      <c r="EE41" s="1">
+        <v>65.059299464643956</v>
+      </c>
+      <c r="EE42" s="1">
         <f t="shared" si="124"/>
-        <v>67.472839810467505</v>
-      </c>
-      <c r="EF41" s="1">
+        <v>64.408706469997512</v>
+      </c>
+      <c r="EF42" s="1">
         <f t="shared" si="124"/>
-        <v>66.798111412362829</v>
-      </c>
-      <c r="EG41" s="1">
+        <v>63.764619405297537</v>
+      </c>
+      <c r="EG42" s="1">
         <f t="shared" si="124"/>
-        <v>66.130130298239195</v>
-      </c>
-      <c r="EH41" s="1">
+        <v>63.126973211244561</v>
+      </c>
+      <c r="EH42" s="1">
         <f t="shared" si="124"/>
-        <v>65.4688289952568</v>
-      </c>
-      <c r="EI41" s="1">
+        <v>62.495703479132118</v>
+      </c>
+      <c r="EI42" s="1">
         <f t="shared" si="124"/>
-        <v>64.814140705304226</v>
-      </c>
-      <c r="EJ41" s="1">
+        <v>61.870746444340796</v>
+      </c>
+      <c r="EJ42" s="1">
         <f t="shared" si="124"/>
-        <v>64.16599929825118</v>
-      </c>
-      <c r="EK41" s="1">
+        <v>61.252038979897385</v>
+      </c>
+      <c r="EK42" s="1">
         <f t="shared" si="124"/>
-        <v>63.524339305268668</v>
-      </c>
-      <c r="EL41" s="1">
+        <v>60.639518590098412</v>
+      </c>
+      <c r="EL42" s="1">
         <f t="shared" si="124"/>
-        <v>62.889095912215979</v>
-      </c>
-      <c r="EM41" s="1">
+        <v>60.033123404197426</v>
+      </c>
+      <c r="EM42" s="1">
         <f t="shared" si="124"/>
-        <v>62.260204953093819</v>
-      </c>
-    </row>
-    <row r="44" spans="2:143" x14ac:dyDescent="0.3">
-      <c r="AX44" t="s">
-        <v>83</v>
-      </c>
-      <c r="AY44" s="4">
-        <f>NPV(AY21,AL41:EM41)</f>
-        <v>1163.3317621119409</v>
+        <v>59.432792170155452</v>
       </c>
     </row>
     <row r="45" spans="2:143" x14ac:dyDescent="0.3">
       <c r="AX45" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="AY45" s="4">
-        <f>Main!D8</f>
-        <v>-64.099999999999994</v>
+        <f>NPV(AY21,AL42:EM42)</f>
+        <v>1083.621430817195</v>
       </c>
     </row>
     <row r="46" spans="2:143" x14ac:dyDescent="0.3">
       <c r="AX46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AY46" s="4">
-        <f>AY44+AY45</f>
-        <v>1099.231762111941</v>
+        <f>Main!D8</f>
+        <v>-17.200000000000003</v>
       </c>
     </row>
     <row r="47" spans="2:143" x14ac:dyDescent="0.3">
       <c r="AX47" t="s">
-        <v>43</v>
-      </c>
-      <c r="AY47" s="5">
-        <f>AY46/AV15</f>
-        <v>10.478853785623841</v>
+        <v>42</v>
+      </c>
+      <c r="AY47" s="4">
+        <f>AY45+AY46</f>
+        <v>1066.421430817195</v>
       </c>
     </row>
     <row r="48" spans="2:143" x14ac:dyDescent="0.3">
       <c r="AX48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AY48" s="5">
-        <f>Main!D3</f>
-        <v>7.37</v>
+        <f>AY47/AV15</f>
+        <v>10.079597644774999</v>
       </c>
     </row>
     <row r="49" spans="50:51" x14ac:dyDescent="0.3">
-      <c r="AX49" s="1" t="s">
+      <c r="AX49" t="s">
+        <v>44</v>
+      </c>
+      <c r="AY49" s="5">
+        <f>Main!D3</f>
+        <v>8.8800000000000008</v>
+      </c>
+    </row>
+    <row r="50" spans="50:51" x14ac:dyDescent="0.3">
+      <c r="AX50" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AY49" s="10">
-        <f>AY47/AY48-1</f>
-        <v>0.42182547973186435</v>
+      <c r="AY50" s="10">
+        <f>AY48/AY49-1</f>
+        <v>0.13508982486204935</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/CRSR.xlsx
+++ b/Financial Analysis/CRSR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DAD6A3-8B53-4998-88BF-3A458FF519B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B7B5C6D-1C28-4225-B069-05C79A84C73A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{D4154116-B837-4443-B5D0-8DB112D6F8D0}"/>
   </bookViews>
@@ -850,14 +850,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>8.8800000000000008</v>
+        <v>7.97</v>
       </c>
       <c r="E3" s="3">
-        <v>45898</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45898</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="3">
         <v>45959</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>941.28000000000009</v>
+        <v>844.81999999999994</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
@@ -923,7 +923,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>958.48000000000013</v>
+        <v>862.02</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="AY26" s="5">
         <f>Main!D3</f>
-        <v>8.8800000000000008</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="27" spans="2:51" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="AY27" s="10">
         <f>AY25/AY26-1</f>
-        <v>-0.67412850122129331</v>
+        <v>-0.63692109044480349</v>
       </c>
     </row>
     <row r="28" spans="2:51" x14ac:dyDescent="0.3">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="AY49" s="5">
         <f>Main!D3</f>
-        <v>8.8800000000000008</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="50" spans="50:51" x14ac:dyDescent="0.3">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="AY50" s="10">
         <f>AY48/AY49-1</f>
-        <v>0.13508982486204935</v>
+        <v>0.26469230172835623</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/CRSR.xlsx
+++ b/Financial Analysis/CRSR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CACF973E-3FA9-409A-9AE3-F6DE9E4F6561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7F8ED6-7A3D-4550-BA03-21E6B26466C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{D4154116-B837-4443-B5D0-8DB112D6F8D0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D4154116-B837-4443-B5D0-8DB112D6F8D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -890,14 +890,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>6.53</v>
+        <v>5.04</v>
       </c>
       <c r="E3" s="3">
-        <v>45967</v>
+        <v>46052</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45967</v>
+        <v>46052</v>
       </c>
       <c r="G3" s="3">
         <v>46063</v>
@@ -921,7 +921,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>696.09799999999996</v>
+        <v>537.26400000000001</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
@@ -963,7 +963,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>752.99799999999993</v>
+        <v>594.16399999999999</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="AY30" s="5">
         <f>Main!D3</f>
-        <v>6.53</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="31" spans="2:51" x14ac:dyDescent="0.3">
@@ -5178,14 +5178,14 @@
       </c>
       <c r="AA31" s="13">
         <f>Main!D9/Model!AA30</f>
-        <v>0.6162517390948522</v>
+        <v>0.48626237826336027</v>
       </c>
       <c r="AX31" s="1" t="s">
         <v>45</v>
       </c>
       <c r="AY31" s="10">
         <f>AY29/AY30-1</f>
-        <v>-0.75351498118990501</v>
+        <v>-0.68064540221628556</v>
       </c>
     </row>
     <row r="32" spans="2:51" x14ac:dyDescent="0.3">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="AA32" s="9">
         <f>AA30/Main!D9-1</f>
-        <v>0.622713473342559</v>
+        <v>1.0565029183861698</v>
       </c>
       <c r="AX32" t="s">
         <v>46</v>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="AY56" s="5">
         <f>Main!D3</f>
-        <v>6.53</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="57" spans="2:143" x14ac:dyDescent="0.3">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="AY57" s="10">
         <f>AY55/AY56-1</f>
-        <v>0.4395156838887111</v>
+        <v>0.86508678884787371</v>
       </c>
     </row>
     <row r="58" spans="2:143" x14ac:dyDescent="0.3">

--- a/Financial Analysis/CRSR.xlsx
+++ b/Financial Analysis/CRSR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7F8ED6-7A3D-4550-BA03-21E6B26466C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3194C37-9ACB-456A-B15E-689D0B5FC859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D4154116-B837-4443-B5D0-8DB112D6F8D0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{D4154116-B837-4443-B5D0-8DB112D6F8D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <author>Anton Mniszek</author>
   </authors>
   <commentList>
-    <comment ref="AL5" authorId="0" shapeId="0" xr:uid="{660F90A3-4B49-4A4F-863A-113B2F196B39}">
+    <comment ref="AP5" authorId="0" shapeId="0" xr:uid="{660F90A3-4B49-4A4F-863A-113B2F196B39}">
       <text>
         <r>
           <rPr>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="98">
   <si>
     <t>CRSR</t>
   </si>
@@ -338,7 +338,22 @@
     <t>Systems y/y</t>
   </si>
   <si>
-    <t>Undervalued</t>
+    <t>Q425 8K</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -467,14 +482,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>61</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
@@ -491,8 +506,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17015460" y="0"/>
-          <a:ext cx="0" cy="10866120"/>
+          <a:off x="17617440" y="0"/>
+          <a:ext cx="0" cy="11231880"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -517,13 +532,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>37</xdr:col>
+      <xdr:col>42</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>37</xdr:col>
+      <xdr:col>42</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>62</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -541,8 +556,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23103840" y="0"/>
-          <a:ext cx="0" cy="9616440"/>
+          <a:off x="26151840" y="0"/>
+          <a:ext cx="0" cy="11445240"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -890,17 +905,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>5.04</v>
+        <v>6.79</v>
       </c>
       <c r="E3" s="3">
-        <v>46052</v>
+        <v>46067</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>46052</v>
+        <v>46067</v>
       </c>
       <c r="G3" s="3">
-        <v>46063</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
@@ -912,7 +927,7 @@
         <v>106.6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
@@ -921,7 +936,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>537.26400000000001</v>
+        <v>723.81399999999996</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
@@ -929,11 +944,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <f>64.4+1.4+0.2</f>
-        <v>66.000000000000014</v>
+        <f>98.6</f>
+        <v>98.6</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
@@ -941,11 +956,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="4">
-        <f>6.1+116.8</f>
-        <v>122.89999999999999</v>
+        <f>6.1+115.2</f>
+        <v>121.3</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
@@ -954,7 +969,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6-D7</f>
-        <v>-56.899999999999977</v>
+        <v>-22.700000000000003</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
@@ -963,7 +978,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>594.16399999999999</v>
+        <v>746.51400000000001</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
@@ -979,15 +994,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DA03470-03C6-4965-A90A-C28BA0FB6465}">
-  <dimension ref="B2:FB68"/>
+  <dimension ref="B2:FF68"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="12" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="12" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:158" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:162" x14ac:dyDescent="0.3">
       <c r="C2" s="6" t="s">
         <v>13</v>
       </c>
@@ -1066,63 +1081,75 @@
       <c r="AB2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="AC2" s="6"/>
-      <c r="AE2">
+      <c r="AC2" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AD2" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE2" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF2" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG2" s="6"/>
+      <c r="AI2">
         <v>2018</v>
       </c>
-      <c r="AF2">
+      <c r="AJ2">
         <v>2019</v>
       </c>
-      <c r="AG2">
+      <c r="AK2">
         <v>2020</v>
       </c>
-      <c r="AH2">
+      <c r="AL2">
         <v>2021</v>
       </c>
-      <c r="AI2">
+      <c r="AM2">
         <v>2022</v>
       </c>
-      <c r="AJ2">
+      <c r="AN2">
         <v>2023</v>
       </c>
-      <c r="AK2">
+      <c r="AO2">
         <v>2024</v>
       </c>
-      <c r="AL2">
+      <c r="AP2">
         <v>2025</v>
       </c>
-      <c r="AM2">
+      <c r="AQ2">
         <v>2026</v>
       </c>
-      <c r="AN2">
+      <c r="AR2">
         <v>2027</v>
       </c>
-      <c r="AO2">
+      <c r="AS2">
         <v>2028</v>
       </c>
-      <c r="AP2">
+      <c r="AT2">
         <v>2029</v>
       </c>
-      <c r="AQ2">
+      <c r="AU2">
         <v>2030</v>
       </c>
-      <c r="AR2">
+      <c r="AV2">
         <v>2031</v>
       </c>
-      <c r="AS2">
+      <c r="AW2">
         <v>2032</v>
       </c>
-      <c r="AT2">
+      <c r="AX2">
         <v>2033</v>
       </c>
-      <c r="AU2">
+      <c r="AY2">
         <v>2034</v>
       </c>
-      <c r="AV2">
+      <c r="AZ2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:158" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:162" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>88</v>
       </c>
@@ -1167,10 +1194,64 @@
       <c r="AA3" s="14">
         <v>112.7</v>
       </c>
-      <c r="AB3" s="6"/>
+      <c r="AB3" s="14">
+        <v>164.9</v>
+      </c>
       <c r="AC3" s="6"/>
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="6"/>
+      <c r="AF3" s="6"/>
+      <c r="AG3" s="6"/>
+      <c r="AO3" s="14">
+        <f>SUM(U3:X3)</f>
+        <v>472.79999999999995</v>
+      </c>
+      <c r="AP3" s="14">
+        <f>SUM(Y3:AB3)</f>
+        <v>492.20000000000005</v>
+      </c>
+      <c r="AQ3" s="4">
+        <f>AP3*1.1</f>
+        <v>541.42000000000007</v>
+      </c>
+      <c r="AR3" s="4">
+        <f>AQ3*1.08</f>
+        <v>584.73360000000014</v>
+      </c>
+      <c r="AS3" s="4">
+        <f>AR3*1.07</f>
+        <v>625.6649520000002</v>
+      </c>
+      <c r="AT3" s="4">
+        <f>AS3*1.06</f>
+        <v>663.20484912000029</v>
+      </c>
+      <c r="AU3" s="4">
+        <f>AT3*1.05</f>
+        <v>696.36509157600028</v>
+      </c>
+      <c r="AV3" s="4">
+        <f>AU3*1.04</f>
+        <v>724.21969523904033</v>
+      </c>
+      <c r="AW3" s="4">
+        <f>AV3*1.03</f>
+        <v>745.94628609621157</v>
+      </c>
+      <c r="AX3" s="4">
+        <f t="shared" ref="AX3:AZ3" si="0">AW3*1.03</f>
+        <v>768.32467467909794</v>
+      </c>
+      <c r="AY3" s="4">
+        <f t="shared" si="0"/>
+        <v>791.37441491947095</v>
+      </c>
+      <c r="AZ3" s="4">
+        <f t="shared" si="0"/>
+        <v>815.11564736705509</v>
+      </c>
     </row>
-    <row r="4" spans="2:158" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:162" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>89</v>
       </c>
@@ -1215,10 +1296,64 @@
       <c r="AA4" s="14">
         <v>233.1</v>
       </c>
-      <c r="AB4" s="6"/>
+      <c r="AB4" s="14">
+        <v>272</v>
+      </c>
       <c r="AC4" s="6"/>
+      <c r="AD4" s="6"/>
+      <c r="AE4" s="6"/>
+      <c r="AF4" s="6"/>
+      <c r="AG4" s="6"/>
+      <c r="AO4" s="14">
+        <f>SUM(U4:X4)</f>
+        <v>843.69999999999993</v>
+      </c>
+      <c r="AP4" s="14">
+        <f>SUM(Y4:AB4)</f>
+        <v>980.4</v>
+      </c>
+      <c r="AQ4" s="4">
+        <f>AP4*0.88</f>
+        <v>862.75199999999995</v>
+      </c>
+      <c r="AR4" s="4">
+        <f>AQ4*1.07</f>
+        <v>923.14463999999998</v>
+      </c>
+      <c r="AS4" s="4">
+        <f>AR4*1.05</f>
+        <v>969.301872</v>
+      </c>
+      <c r="AT4" s="4">
+        <f>AS4*1.04</f>
+        <v>1008.07394688</v>
+      </c>
+      <c r="AU4" s="4">
+        <f>AT4*1.03</f>
+        <v>1038.3161652864001</v>
+      </c>
+      <c r="AV4" s="4">
+        <f>AU4*1.02</f>
+        <v>1059.0824885921281</v>
+      </c>
+      <c r="AW4" s="4">
+        <f>AV4*1.01</f>
+        <v>1069.6733134780495</v>
+      </c>
+      <c r="AX4" s="4">
+        <f t="shared" ref="AX4:AZ4" si="1">AW4*1.01</f>
+        <v>1080.37004661283</v>
+      </c>
+      <c r="AY4" s="4">
+        <f t="shared" si="1"/>
+        <v>1091.1737470789583</v>
+      </c>
+      <c r="AZ4" s="4">
+        <f t="shared" si="1"/>
+        <v>1102.0854845497479</v>
+      </c>
     </row>
-    <row r="5" spans="2:158" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:162" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
@@ -1295,81 +1430,85 @@
         <v>345.8</v>
       </c>
       <c r="AB5" s="8">
-        <f>X5*1.01</f>
-        <v>417.73600000000005</v>
+        <f>SUM(AB3:AB4)</f>
+        <v>436.9</v>
       </c>
       <c r="AC5" s="8"/>
-      <c r="AE5" s="8">
+      <c r="AD5" s="8"/>
+      <c r="AE5" s="8"/>
+      <c r="AF5" s="8"/>
+      <c r="AG5" s="8"/>
+      <c r="AI5" s="8">
         <v>937.6</v>
       </c>
-      <c r="AF5" s="8">
+      <c r="AJ5" s="8">
         <v>1097.2</v>
       </c>
-      <c r="AG5" s="8">
+      <c r="AK5" s="8">
         <v>1702.4</v>
       </c>
-      <c r="AH5" s="8">
+      <c r="AL5" s="8">
         <f>SUM(I5:L5)</f>
         <v>1904</v>
       </c>
-      <c r="AI5" s="8">
+      <c r="AM5" s="8">
         <f>SUM(M5:P5)</f>
         <v>1375.1</v>
       </c>
-      <c r="AJ5" s="8">
+      <c r="AN5" s="8">
         <f>SUM(Q5:T5)</f>
         <v>1459.8999999999999</v>
       </c>
-      <c r="AK5" s="8">
+      <c r="AO5" s="8">
         <f>SUM(U5:X5)</f>
         <v>1316.4</v>
       </c>
-      <c r="AL5" s="8">
+      <c r="AP5" s="8">
         <f>SUM(Y5:AB5)</f>
-        <v>1453.4360000000001</v>
-      </c>
-      <c r="AM5" s="8">
-        <f>AL5*1.06</f>
-        <v>1540.6421600000003</v>
-      </c>
-      <c r="AN5" s="8">
-        <f>AM5*1.05</f>
-        <v>1617.6742680000004</v>
-      </c>
-      <c r="AO5" s="8">
-        <f>AN5*1.04</f>
-        <v>1682.3812387200005</v>
-      </c>
-      <c r="AP5" s="8">
-        <f>AO5*1.03</f>
-        <v>1732.8526758816006</v>
+        <v>1472.6</v>
       </c>
       <c r="AQ5" s="8">
-        <f>AP5*1.02</f>
-        <v>1767.5097293992326</v>
+        <f>SUM(AQ3:AQ4)</f>
+        <v>1404.172</v>
       </c>
       <c r="AR5" s="8">
-        <f t="shared" ref="AR5:AV5" si="0">AQ5*1.02</f>
-        <v>1802.8599239872174</v>
+        <f>AQ5*1.05</f>
+        <v>1474.3806000000002</v>
       </c>
       <c r="AS5" s="8">
-        <f t="shared" si="0"/>
-        <v>1838.9171224669617</v>
+        <f>AR5*1.04</f>
+        <v>1533.3558240000002</v>
       </c>
       <c r="AT5" s="8">
-        <f t="shared" si="0"/>
-        <v>1875.695464916301</v>
+        <f>AS5*1.03</f>
+        <v>1579.3564987200002</v>
       </c>
       <c r="AU5" s="8">
-        <f t="shared" si="0"/>
-        <v>1913.2093742146271</v>
+        <f>AT5*1.02</f>
+        <v>1610.9436286944003</v>
       </c>
       <c r="AV5" s="8">
-        <f t="shared" si="0"/>
-        <v>1951.4735616989196</v>
+        <f t="shared" ref="AV5:AZ5" si="2">AU5*1.02</f>
+        <v>1643.1625012682885</v>
+      </c>
+      <c r="AW5" s="8">
+        <f t="shared" si="2"/>
+        <v>1676.0257512936541</v>
+      </c>
+      <c r="AX5" s="8">
+        <f t="shared" si="2"/>
+        <v>1709.5462663195271</v>
+      </c>
+      <c r="AY5" s="8">
+        <f t="shared" si="2"/>
+        <v>1743.7371916459176</v>
+      </c>
+      <c r="AZ5" s="8">
+        <f t="shared" si="2"/>
+        <v>1778.6119354788359</v>
       </c>
     </row>
-    <row r="6" spans="2:158" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:162" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>22</v>
       </c>
@@ -1446,81 +1585,84 @@
         <v>252.7</v>
       </c>
       <c r="AB6" s="4">
-        <f t="shared" ref="AB6" si="1">AB5-AB7</f>
-        <v>300.76992000000001</v>
+        <v>292.3</v>
       </c>
       <c r="AC6" s="4"/>
-      <c r="AE6" s="4">
+      <c r="AD6" s="4"/>
+      <c r="AE6" s="4"/>
+      <c r="AF6" s="4"/>
+      <c r="AG6" s="4"/>
+      <c r="AI6" s="4">
         <v>744.9</v>
       </c>
-      <c r="AF6" s="4">
+      <c r="AJ6" s="4">
         <v>872.9</v>
       </c>
-      <c r="AG6" s="4">
+      <c r="AK6" s="4">
         <v>1236.9000000000001</v>
       </c>
-      <c r="AH6" s="4">
+      <c r="AL6" s="4">
         <f>SUM(I6:L6)</f>
         <v>1390.3</v>
       </c>
-      <c r="AI6" s="4">
+      <c r="AM6" s="4">
         <f>SUM(M6:P6)</f>
         <v>1078.4000000000001</v>
       </c>
-      <c r="AJ6" s="4">
+      <c r="AN6" s="4">
         <f>SUM(Q6:T6)</f>
         <v>1099.5999999999999</v>
       </c>
-      <c r="AK6" s="4">
+      <c r="AO6" s="4">
         <f>SUM(U6:X6)</f>
         <v>988.69999999999993</v>
       </c>
-      <c r="AL6" s="4">
+      <c r="AP6" s="4">
         <f>SUM(Y6:AB6)</f>
-        <v>1055.0699199999999</v>
-      </c>
-      <c r="AM6" s="4">
-        <f t="shared" ref="AM6:AR6" si="2">AM5-AM7</f>
-        <v>1124.6687768000002</v>
-      </c>
-      <c r="AN6" s="4">
-        <f t="shared" si="2"/>
-        <v>1180.9022156400003</v>
-      </c>
-      <c r="AO6" s="4">
-        <f t="shared" si="2"/>
-        <v>1211.3144918784003</v>
-      </c>
-      <c r="AP6" s="4">
-        <f t="shared" si="2"/>
-        <v>1247.6539266347525</v>
+        <v>1046.5999999999999</v>
       </c>
       <c r="AQ6" s="4">
-        <f t="shared" si="2"/>
-        <v>1272.6070051674474</v>
+        <f t="shared" ref="AQ6:AV6" si="3">AQ5-AQ7</f>
+        <v>1011.00384</v>
       </c>
       <c r="AR6" s="4">
-        <f t="shared" si="2"/>
-        <v>1298.0591452707965</v>
+        <f t="shared" si="3"/>
+        <v>1046.8102260000001</v>
       </c>
       <c r="AS6" s="4">
-        <f t="shared" ref="AS6:AV6" si="3">AS5-AS7</f>
-        <v>1324.0203281762124</v>
+        <f t="shared" si="3"/>
+        <v>1073.3490768000001</v>
       </c>
       <c r="AT6" s="4">
         <f t="shared" si="3"/>
-        <v>1350.5007347397368</v>
+        <v>1105.5495491040001</v>
       </c>
       <c r="AU6" s="4">
         <f t="shared" si="3"/>
-        <v>1377.5107494345316</v>
+        <v>1127.6605400860803</v>
       </c>
       <c r="AV6" s="4">
         <f t="shared" si="3"/>
-        <v>1405.0609644232222</v>
+        <v>1150.213750887802</v>
+      </c>
+      <c r="AW6" s="4">
+        <f t="shared" ref="AW6:AZ6" si="4">AW5-AW7</f>
+        <v>1173.2180259055579</v>
+      </c>
+      <c r="AX6" s="4">
+        <f t="shared" si="4"/>
+        <v>1196.682386423669</v>
+      </c>
+      <c r="AY6" s="4">
+        <f t="shared" si="4"/>
+        <v>1220.6160341521422</v>
+      </c>
+      <c r="AZ6" s="4">
+        <f t="shared" si="4"/>
+        <v>1245.0283548351852</v>
       </c>
     </row>
-    <row r="7" spans="2:158" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:162" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>23</v>
       </c>
@@ -1537,168 +1679,172 @@
         <v>78.599999999999994</v>
       </c>
       <c r="G7" s="8">
-        <f t="shared" ref="G7:AA7" si="4">G5-G6</f>
+        <f t="shared" ref="G7:AB7" si="5">G5-G6</f>
         <v>127.90000000000003</v>
       </c>
       <c r="H7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>153.79999999999995</v>
       </c>
       <c r="I7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>160.29999999999995</v>
       </c>
       <c r="J7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>130.29999999999995</v>
       </c>
       <c r="K7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>101.30000000000001</v>
       </c>
       <c r="L7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>121.80000000000001</v>
       </c>
       <c r="M7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>90.800000000000011</v>
       </c>
       <c r="N7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>36.499999999999972</v>
       </c>
       <c r="O7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>71.600000000000023</v>
       </c>
       <c r="P7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>97.800000000000011</v>
       </c>
       <c r="Q7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>85.399999999999977</v>
       </c>
       <c r="R7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>82.799999999999983</v>
       </c>
       <c r="S7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>89.399999999999977</v>
       </c>
       <c r="T7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>102.69999999999999</v>
       </c>
       <c r="U7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>86.700000000000017</v>
       </c>
       <c r="V7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>63.100000000000023</v>
       </c>
       <c r="W7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>69.699999999999989</v>
       </c>
       <c r="X7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>108.20000000000005</v>
       </c>
       <c r="Y7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>102.40000000000003</v>
       </c>
       <c r="Z7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>85.900000000000034</v>
       </c>
       <c r="AA7" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>93.100000000000023</v>
       </c>
       <c r="AB7" s="8">
-        <f>AB5*0.28</f>
-        <v>116.96608000000002</v>
+        <f t="shared" si="5"/>
+        <v>144.59999999999997</v>
       </c>
       <c r="AC7" s="8"/>
-      <c r="AE7" s="8">
-        <f>AE5-AE6</f>
+      <c r="AD7" s="8"/>
+      <c r="AE7" s="8"/>
+      <c r="AF7" s="8"/>
+      <c r="AG7" s="8"/>
+      <c r="AI7" s="8">
+        <f>AI5-AI6</f>
         <v>192.70000000000005</v>
       </c>
-      <c r="AF7" s="8">
-        <f>AF5-AF6</f>
+      <c r="AJ7" s="8">
+        <f>AJ5-AJ6</f>
         <v>224.30000000000007</v>
       </c>
-      <c r="AG7" s="8">
-        <f>AG5-AG6</f>
+      <c r="AK7" s="8">
+        <f>AK5-AK6</f>
         <v>465.5</v>
       </c>
-      <c r="AH7" s="8">
-        <f>AH5-AH6</f>
+      <c r="AL7" s="8">
+        <f>AL5-AL6</f>
         <v>513.70000000000005</v>
       </c>
-      <c r="AI7" s="8">
-        <f t="shared" ref="AI7:AL7" si="5">AI5-AI6</f>
+      <c r="AM7" s="8">
+        <f t="shared" ref="AM7:AP7" si="6">AM5-AM6</f>
         <v>296.69999999999982</v>
       </c>
-      <c r="AJ7" s="8">
-        <f t="shared" si="5"/>
+      <c r="AN7" s="8">
+        <f t="shared" si="6"/>
         <v>360.29999999999995</v>
       </c>
-      <c r="AK7" s="8">
-        <f t="shared" si="5"/>
+      <c r="AO7" s="8">
+        <f t="shared" si="6"/>
         <v>327.70000000000016</v>
       </c>
-      <c r="AL7" s="8">
-        <f t="shared" si="5"/>
-        <v>398.36608000000024</v>
-      </c>
-      <c r="AM7" s="8">
-        <f>AM5*0.27</f>
-        <v>415.97338320000011</v>
-      </c>
-      <c r="AN7" s="8">
-        <f>AN5*0.27</f>
-        <v>436.77205236000015</v>
-      </c>
-      <c r="AO7" s="8">
-        <f>AO5*0.28</f>
-        <v>471.06674684160021</v>
-      </c>
       <c r="AP7" s="8">
-        <f t="shared" ref="AP7:AV7" si="6">AP5*0.28</f>
-        <v>485.19874924684819</v>
+        <f t="shared" si="6"/>
+        <v>426</v>
       </c>
       <c r="AQ7" s="8">
-        <f t="shared" si="6"/>
-        <v>494.90272423178516</v>
+        <f>AQ5*0.28</f>
+        <v>393.16816000000006</v>
       </c>
       <c r="AR7" s="8">
-        <f t="shared" si="6"/>
-        <v>504.80077871642089</v>
+        <f>AR5*0.29</f>
+        <v>427.57037400000002</v>
       </c>
       <c r="AS7" s="8">
-        <f t="shared" si="6"/>
-        <v>514.89679429074931</v>
+        <f>AS5*0.3</f>
+        <v>460.00674720000006</v>
       </c>
       <c r="AT7" s="8">
-        <f t="shared" si="6"/>
-        <v>525.19473017656435</v>
+        <f t="shared" ref="AT7:AZ7" si="7">AT5*0.3</f>
+        <v>473.80694961600005</v>
       </c>
       <c r="AU7" s="8">
-        <f t="shared" si="6"/>
-        <v>535.69862478009566</v>
+        <f t="shared" si="7"/>
+        <v>483.2830886083201</v>
       </c>
       <c r="AV7" s="8">
-        <f t="shared" si="6"/>
-        <v>546.41259727569752</v>
+        <f t="shared" si="7"/>
+        <v>492.9487503804865</v>
+      </c>
+      <c r="AW7" s="8">
+        <f t="shared" si="7"/>
+        <v>502.80772538809623</v>
+      </c>
+      <c r="AX7" s="8">
+        <f t="shared" si="7"/>
+        <v>512.86387989585808</v>
+      </c>
+      <c r="AY7" s="8">
+        <f t="shared" si="7"/>
+        <v>523.12115749377529</v>
+      </c>
+      <c r="AZ7" s="8">
+        <f t="shared" si="7"/>
+        <v>533.58358064365075</v>
       </c>
     </row>
-    <row r="8" spans="2:158" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:162" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>24</v>
       </c>
@@ -1775,81 +1921,84 @@
         <v>82</v>
       </c>
       <c r="AB8" s="4">
-        <f>X8*1.07</f>
-        <v>91.271000000000001</v>
+        <v>100.4</v>
       </c>
       <c r="AC8" s="4"/>
-      <c r="AE8" s="4">
+      <c r="AD8" s="4"/>
+      <c r="AE8" s="4"/>
+      <c r="AF8" s="4"/>
+      <c r="AG8" s="4"/>
+      <c r="AI8" s="4">
         <v>138.9</v>
       </c>
-      <c r="AF8" s="4">
+      <c r="AJ8" s="4">
         <v>163</v>
       </c>
-      <c r="AG8" s="4">
+      <c r="AK8" s="4">
         <v>257</v>
       </c>
-      <c r="AH8" s="4">
+      <c r="AL8" s="4">
         <f>SUM(I8:L8)</f>
         <v>315.70000000000005</v>
       </c>
-      <c r="AI8" s="4">
+      <c r="AM8" s="4">
         <f>SUM(M8:P8)</f>
         <v>284.89999999999998</v>
       </c>
-      <c r="AJ8" s="4">
+      <c r="AN8" s="4">
         <f>SUM(Q8:T8)</f>
         <v>285.3</v>
       </c>
-      <c r="AK8" s="4">
+      <c r="AO8" s="4">
         <f>SUM(U8:X8)</f>
         <v>310</v>
       </c>
-      <c r="AL8" s="4">
+      <c r="AP8" s="4">
         <f>SUM(Y8:AB8)</f>
-        <v>345.57100000000003</v>
-      </c>
-      <c r="AM8" s="4">
-        <f>AL8*1.03</f>
-        <v>355.93813000000006</v>
-      </c>
-      <c r="AN8" s="4">
-        <f>AM8*1.02</f>
-        <v>363.05689260000008</v>
-      </c>
-      <c r="AO8" s="4">
-        <f t="shared" ref="AO8:AV8" si="7">AN8*1.01</f>
-        <v>366.68746152600011</v>
-      </c>
-      <c r="AP8" s="4">
-        <f t="shared" si="7"/>
-        <v>370.35433614126009</v>
+        <v>354.70000000000005</v>
       </c>
       <c r="AQ8" s="4">
-        <f t="shared" si="7"/>
-        <v>374.05787950267268</v>
+        <f>AP8*1.05</f>
+        <v>372.43500000000006</v>
       </c>
       <c r="AR8" s="4">
-        <f t="shared" si="7"/>
-        <v>377.79845829769943</v>
+        <f>AQ8*1.03</f>
+        <v>383.60805000000005</v>
       </c>
       <c r="AS8" s="4">
-        <f t="shared" si="7"/>
-        <v>381.57644288067644</v>
+        <f>AR8*1.02</f>
+        <v>391.28021100000007</v>
       </c>
       <c r="AT8" s="4">
-        <f t="shared" si="7"/>
-        <v>385.39220730948318</v>
+        <f>AS8*1.02</f>
+        <v>399.10581522000007</v>
       </c>
       <c r="AU8" s="4">
-        <f t="shared" si="7"/>
-        <v>389.24612938257803</v>
+        <f t="shared" ref="AU8:AZ8" si="8">AT8*1.01</f>
+        <v>403.09687337220009</v>
       </c>
       <c r="AV8" s="4">
-        <f t="shared" si="7"/>
-        <v>393.13859067640379</v>
+        <f t="shared" si="8"/>
+        <v>407.12784210592207</v>
+      </c>
+      <c r="AW8" s="4">
+        <f t="shared" si="8"/>
+        <v>411.19912052698129</v>
+      </c>
+      <c r="AX8" s="4">
+        <f t="shared" si="8"/>
+        <v>415.31111173225111</v>
+      </c>
+      <c r="AY8" s="4">
+        <f t="shared" si="8"/>
+        <v>419.46422284957362</v>
+      </c>
+      <c r="AZ8" s="4">
+        <f t="shared" si="8"/>
+        <v>423.65886507806937</v>
       </c>
     </row>
-    <row r="9" spans="2:158" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:162" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>25</v>
       </c>
@@ -1926,81 +2075,84 @@
         <v>16.7</v>
       </c>
       <c r="AB9" s="4">
-        <f t="shared" ref="AB9" si="8">X9*1.03</f>
-        <v>17.510000000000002</v>
+        <v>17.3</v>
       </c>
       <c r="AC9" s="4"/>
-      <c r="AE9" s="4">
+      <c r="AD9" s="4"/>
+      <c r="AE9" s="4"/>
+      <c r="AF9" s="4"/>
+      <c r="AG9" s="4"/>
+      <c r="AI9" s="4">
         <v>32</v>
       </c>
-      <c r="AF9" s="4">
+      <c r="AJ9" s="4">
         <v>37.5</v>
       </c>
-      <c r="AG9" s="4">
+      <c r="AK9" s="4">
         <v>50.1</v>
       </c>
-      <c r="AH9" s="4">
+      <c r="AL9" s="4">
         <f>SUM(I9:L9)</f>
         <v>60.300000000000004</v>
       </c>
-      <c r="AI9" s="4">
+      <c r="AM9" s="4">
         <f>SUM(M9:P9)</f>
         <v>66.400000000000006</v>
       </c>
-      <c r="AJ9" s="4">
+      <c r="AN9" s="4">
         <f>SUM(Q9:T9)</f>
         <v>65.2</v>
       </c>
-      <c r="AK9" s="4">
+      <c r="AO9" s="4">
         <f>SUM(U9:X9)</f>
         <v>67.5</v>
       </c>
-      <c r="AL9" s="4">
+      <c r="AP9" s="4">
         <f>SUM(Y9:AB9)</f>
-        <v>69.31</v>
-      </c>
-      <c r="AM9" s="4">
-        <f>AL9*1.02</f>
-        <v>70.696200000000005</v>
-      </c>
-      <c r="AN9" s="4">
-        <f t="shared" ref="AN9" si="9">AM9*1.02</f>
-        <v>72.110123999999999</v>
-      </c>
-      <c r="AO9" s="4">
-        <f>AN9*1.01</f>
-        <v>72.831225239999995</v>
-      </c>
-      <c r="AP9" s="4">
-        <f t="shared" ref="AP9:AV9" si="10">AO9*1.01</f>
-        <v>73.559537492399997</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="AQ9" s="4">
-        <f t="shared" si="10"/>
-        <v>74.295132867324</v>
+        <f>AP9*1.02</f>
+        <v>70.481999999999999</v>
       </c>
       <c r="AR9" s="4">
-        <f t="shared" si="10"/>
-        <v>75.038084195997243</v>
+        <f t="shared" ref="AR9" si="9">AQ9*1.02</f>
+        <v>71.891639999999995</v>
       </c>
       <c r="AS9" s="4">
-        <f t="shared" si="10"/>
-        <v>75.788465037957209</v>
+        <f>AR9*1.01</f>
+        <v>72.610556399999993</v>
       </c>
       <c r="AT9" s="4">
-        <f t="shared" si="10"/>
-        <v>76.546349688336775</v>
+        <f t="shared" ref="AT9:AZ9" si="10">AS9*1.01</f>
+        <v>73.336661963999987</v>
       </c>
       <c r="AU9" s="4">
         <f t="shared" si="10"/>
-        <v>77.311813185220146</v>
+        <v>74.070028583639981</v>
       </c>
       <c r="AV9" s="4">
         <f t="shared" si="10"/>
-        <v>78.084931317072346</v>
+        <v>74.810728869476378</v>
+      </c>
+      <c r="AW9" s="4">
+        <f t="shared" si="10"/>
+        <v>75.558836158171147</v>
+      </c>
+      <c r="AX9" s="4">
+        <f t="shared" si="10"/>
+        <v>76.314424519752862</v>
+      </c>
+      <c r="AY9" s="4">
+        <f t="shared" si="10"/>
+        <v>77.077568764950385</v>
+      </c>
+      <c r="AZ9" s="4">
+        <f t="shared" si="10"/>
+        <v>77.848344452599889</v>
       </c>
     </row>
-    <row r="10" spans="2:158" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:162" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>26</v>
       </c>
@@ -2102,83 +2254,87 @@
       </c>
       <c r="AB10" s="8">
         <f t="shared" si="16"/>
-        <v>8.185080000000017</v>
+        <v>26.899999999999959</v>
       </c>
       <c r="AC10" s="8"/>
-      <c r="AE10" s="8">
-        <f>AE7-AE8-AE9</f>
+      <c r="AD10" s="8"/>
+      <c r="AE10" s="8"/>
+      <c r="AF10" s="8"/>
+      <c r="AG10" s="8"/>
+      <c r="AI10" s="8">
+        <f>AI7-AI8-AI9</f>
         <v>21.80000000000004</v>
       </c>
-      <c r="AF10" s="8">
-        <f>AF7-AF8-AF9</f>
+      <c r="AJ10" s="8">
+        <f>AJ7-AJ8-AJ9</f>
         <v>23.800000000000068</v>
       </c>
-      <c r="AG10" s="8">
-        <f>AG7-AG8-AG9</f>
+      <c r="AK10" s="8">
+        <f>AK7-AK8-AK9</f>
         <v>158.4</v>
       </c>
-      <c r="AH10" s="8">
-        <f>AH7-AH8-AH9</f>
+      <c r="AL10" s="8">
+        <f>AL7-AL8-AL9</f>
         <v>137.69999999999999</v>
       </c>
-      <c r="AI10" s="8">
-        <f t="shared" ref="AI10:AR10" si="17">AI7-AI8-AI9</f>
+      <c r="AM10" s="8">
+        <f t="shared" ref="AM10:AV10" si="17">AM7-AM8-AM9</f>
         <v>-54.600000000000165</v>
       </c>
-      <c r="AJ10" s="8">
+      <c r="AN10" s="8">
         <f t="shared" si="17"/>
         <v>9.7999999999999403</v>
       </c>
-      <c r="AK10" s="8">
+      <c r="AO10" s="8">
         <f t="shared" si="17"/>
         <v>-49.799999999999841</v>
       </c>
-      <c r="AL10" s="8">
-        <f t="shared" si="17"/>
-        <v>-16.51491999999979</v>
-      </c>
-      <c r="AM10" s="8">
-        <f t="shared" si="17"/>
-        <v>-10.660946799999948</v>
-      </c>
-      <c r="AN10" s="8">
-        <f t="shared" si="17"/>
-        <v>1.6050357600000638</v>
-      </c>
-      <c r="AO10" s="8">
-        <f t="shared" si="17"/>
-        <v>31.548060075600105</v>
-      </c>
       <c r="AP10" s="8">
         <f t="shared" si="17"/>
-        <v>41.284875613188106</v>
+        <v>2.1999999999999602</v>
       </c>
       <c r="AQ10" s="8">
         <f t="shared" si="17"/>
-        <v>46.549711861788481</v>
+        <v>-49.748840000000001</v>
       </c>
       <c r="AR10" s="8">
         <f t="shared" si="17"/>
-        <v>51.964236222724224</v>
+        <v>-27.929316000000028</v>
       </c>
       <c r="AS10" s="8">
-        <f t="shared" ref="AS10:AV10" si="18">AS7-AS8-AS9</f>
-        <v>57.531886372115665</v>
+        <f t="shared" si="17"/>
+        <v>-3.8840201999999948</v>
       </c>
       <c r="AT10" s="8">
+        <f t="shared" si="17"/>
+        <v>1.3644724319999995</v>
+      </c>
+      <c r="AU10" s="8">
+        <f t="shared" si="17"/>
+        <v>6.1161866524800246</v>
+      </c>
+      <c r="AV10" s="8">
+        <f t="shared" si="17"/>
+        <v>11.010179405088053</v>
+      </c>
+      <c r="AW10" s="8">
+        <f t="shared" ref="AW10:AZ10" si="18">AW7-AW8-AW9</f>
+        <v>16.049768702943794</v>
+      </c>
+      <c r="AX10" s="8">
         <f t="shared" si="18"/>
-        <v>63.25617317874439</v>
-      </c>
-      <c r="AU10" s="8">
+        <v>21.238343643854108</v>
+      </c>
+      <c r="AY10" s="8">
         <f t="shared" si="18"/>
-        <v>69.140682212297477</v>
-      </c>
-      <c r="AV10" s="8">
+        <v>26.579365879251284</v>
+      </c>
+      <c r="AZ10" s="8">
         <f t="shared" si="18"/>
-        <v>75.189075282221381</v>
+        <v>32.076371112981491</v>
       </c>
     </row>
-    <row r="11" spans="2:158" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:162" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>27</v>
       </c>
@@ -2255,81 +2411,84 @@
         <v>2.1</v>
       </c>
       <c r="AB11" s="4">
-        <f t="shared" ref="AB11" si="19">X11*1.02</f>
-        <v>3.1620000000000004</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" s="4"/>
-      <c r="AE11" s="4">
+      <c r="AD11" s="4"/>
+      <c r="AE11" s="4"/>
+      <c r="AF11" s="4"/>
+      <c r="AG11" s="4"/>
+      <c r="AI11" s="4">
         <v>32.700000000000003</v>
       </c>
-      <c r="AF11" s="4">
+      <c r="AJ11" s="4">
         <v>35.5</v>
       </c>
-      <c r="AG11" s="4">
+      <c r="AK11" s="4">
         <v>35.1</v>
       </c>
-      <c r="AH11" s="4">
+      <c r="AL11" s="4">
         <f>SUM(I11:L11)</f>
         <v>17.600000000000001</v>
       </c>
-      <c r="AI11" s="4">
+      <c r="AM11" s="4">
         <f>SUM(M11:P11)</f>
         <v>9.6</v>
       </c>
-      <c r="AJ11" s="4">
+      <c r="AN11" s="4">
         <f>SUM(Q11:T11)</f>
         <v>17.5</v>
       </c>
-      <c r="AK11" s="4">
+      <c r="AO11" s="4">
         <f>SUM(U11:X11)</f>
         <v>13.2</v>
       </c>
-      <c r="AL11" s="4">
+      <c r="AP11" s="4">
         <f>SUM(Y11:AB11)</f>
-        <v>10.462000000000002</v>
-      </c>
-      <c r="AM11" s="4">
-        <f>AL11*1.03</f>
-        <v>10.775860000000002</v>
-      </c>
-      <c r="AN11" s="4">
-        <f t="shared" ref="AN11:AV11" si="20">AM11*1.03</f>
-        <v>11.099135800000003</v>
-      </c>
-      <c r="AO11" s="4">
-        <f t="shared" si="20"/>
-        <v>11.432109874000004</v>
-      </c>
-      <c r="AP11" s="4">
-        <f t="shared" si="20"/>
-        <v>11.775073170220004</v>
+        <v>9.4</v>
       </c>
       <c r="AQ11" s="4">
-        <f t="shared" si="20"/>
-        <v>12.128325365326605</v>
+        <f>AP11*1.03</f>
+        <v>9.6820000000000004</v>
       </c>
       <c r="AR11" s="4">
-        <f t="shared" si="20"/>
-        <v>12.492175126286403</v>
+        <f t="shared" ref="AR11:AZ11" si="19">AQ11*1.03</f>
+        <v>9.9724599999999999</v>
       </c>
       <c r="AS11" s="4">
-        <f t="shared" si="20"/>
-        <v>12.866940380074995</v>
+        <f t="shared" si="19"/>
+        <v>10.2716338</v>
       </c>
       <c r="AT11" s="4">
-        <f t="shared" si="20"/>
-        <v>13.252948591477246</v>
+        <f t="shared" si="19"/>
+        <v>10.579782814</v>
       </c>
       <c r="AU11" s="4">
-        <f t="shared" si="20"/>
-        <v>13.650537049221564</v>
+        <f t="shared" si="19"/>
+        <v>10.89717629842</v>
       </c>
       <c r="AV11" s="4">
-        <f t="shared" si="20"/>
-        <v>14.06005316069821</v>
+        <f t="shared" si="19"/>
+        <v>11.2240915873726</v>
+      </c>
+      <c r="AW11" s="4">
+        <f t="shared" si="19"/>
+        <v>11.560814334993779</v>
+      </c>
+      <c r="AX11" s="4">
+        <f t="shared" si="19"/>
+        <v>11.907638765043593</v>
+      </c>
+      <c r="AY11" s="4">
+        <f t="shared" si="19"/>
+        <v>12.264867927994901</v>
+      </c>
+      <c r="AZ11" s="4">
+        <f t="shared" si="19"/>
+        <v>12.632813965834748</v>
       </c>
     </row>
-    <row r="12" spans="2:158" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:162" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>28</v>
       </c>
@@ -2417,49 +2576,42 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="AB12" s="4">
-        <v>0</v>
+        <f>-0.3-0.1</f>
+        <v>-0.4</v>
       </c>
       <c r="AC12" s="4"/>
-      <c r="AE12" s="4">
+      <c r="AD12" s="4"/>
+      <c r="AE12" s="4"/>
+      <c r="AF12" s="4"/>
+      <c r="AG12" s="4"/>
+      <c r="AI12" s="4">
         <v>-0.2</v>
       </c>
-      <c r="AF12" s="4">
+      <c r="AJ12" s="4">
         <v>1.6</v>
       </c>
-      <c r="AG12" s="4">
+      <c r="AK12" s="4">
         <v>1.2</v>
       </c>
-      <c r="AH12" s="4">
+      <c r="AL12" s="4">
         <f>SUM(I12:L12)</f>
         <v>5.7</v>
       </c>
-      <c r="AI12" s="4">
+      <c r="AM12" s="4">
         <f>SUM(M12:P12)</f>
         <v>-0.59999999999999964</v>
       </c>
-      <c r="AJ12" s="4">
+      <c r="AN12" s="4">
         <f>SUM(Q12:T12)</f>
         <v>-4.2</v>
       </c>
-      <c r="AK12" s="4">
+      <c r="AO12" s="4">
         <f>SUM(U12:X12)</f>
         <v>-1.5</v>
       </c>
-      <c r="AL12" s="4">
+      <c r="AP12" s="4">
         <f>SUM(Y12:AB12)</f>
-        <v>5.1999999999999993</v>
-      </c>
-      <c r="AM12" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP12" s="4">
-        <v>0</v>
+        <v>4.7999999999999989</v>
       </c>
       <c r="AQ12" s="4">
         <v>0</v>
@@ -2479,8 +2631,20 @@
       <c r="AV12" s="4">
         <v>0</v>
       </c>
+      <c r="AW12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="2:158" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:162" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>29</v>
       </c>
@@ -2493,7 +2657,7 @@
         <v>5.7000000000000011</v>
       </c>
       <c r="E13" s="8">
-        <f t="shared" ref="E13" si="21">E10-E11-E12</f>
+        <f t="shared" ref="E13" si="20">E10-E11-E12</f>
         <v>3.7999999999999914</v>
       </c>
       <c r="G13" s="8">
@@ -2505,43 +2669,43 @@
         <v>51.69999999999996</v>
       </c>
       <c r="I13" s="8">
-        <f t="shared" ref="I13" si="22">I10-I11-I12</f>
+        <f t="shared" ref="I13" si="21">I10-I11-I12</f>
         <v>59.899999999999949</v>
       </c>
       <c r="J13" s="8">
-        <f t="shared" ref="J13:Q13" si="23">J10-J11-J12</f>
+        <f t="shared" ref="J13:Q13" si="22">J10-J11-J12</f>
         <v>29.899999999999952</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>2.100000000000017</v>
       </c>
       <c r="L13" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>22.500000000000011</v>
       </c>
       <c r="M13" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-4.1999999999999842</v>
       </c>
       <c r="N13" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-56.000000000000036</v>
       </c>
       <c r="O13" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-11.899999999999984</v>
       </c>
       <c r="P13" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>8.5000000000000107</v>
       </c>
       <c r="Q13" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>-2.2000000000000233</v>
       </c>
       <c r="R13" s="8">
-        <f t="shared" ref="R13" si="24">R10-R11-R12</f>
+        <f t="shared" ref="R13" si="23">R10-R11-R12</f>
         <v>-6.4000000000000163</v>
       </c>
       <c r="S13" s="8">
@@ -2557,7 +2721,7 @@
         <v>-12.699999999999987</v>
       </c>
       <c r="V13" s="8">
-        <f t="shared" ref="V13" si="25">V10-V11-V12</f>
+        <f t="shared" ref="V13" si="24">V10-V11-V12</f>
         <v>-27.399999999999981</v>
       </c>
       <c r="W13" s="8">
@@ -2569,96 +2733,100 @@
         <v>3.1000000000000481</v>
       </c>
       <c r="Y13" s="8">
-        <f t="shared" ref="Y13:AB13" si="26">Y10-Y11-Y12</f>
+        <f t="shared" ref="Y13:AB13" si="25">Y10-Y11-Y12</f>
         <v>-8.1999999999999673</v>
       </c>
       <c r="Z13" s="8">
+        <f t="shared" si="25"/>
+        <v>-20.699999999999964</v>
+      </c>
+      <c r="AA13" s="8">
+        <f t="shared" si="25"/>
+        <v>-8.2999999999999758</v>
+      </c>
+      <c r="AB13" s="8">
+        <f t="shared" si="25"/>
+        <v>25.199999999999957</v>
+      </c>
+      <c r="AC13" s="8"/>
+      <c r="AD13" s="8"/>
+      <c r="AE13" s="8"/>
+      <c r="AF13" s="8"/>
+      <c r="AG13" s="8"/>
+      <c r="AI13" s="8">
+        <f>AI10-AI11-AI12</f>
+        <v>-10.699999999999964</v>
+      </c>
+      <c r="AJ13" s="8">
+        <f>AJ10-AJ11-AJ12</f>
+        <v>-13.299999999999931</v>
+      </c>
+      <c r="AK13" s="8">
+        <f>AK10-AK11-AK12</f>
+        <v>122.10000000000001</v>
+      </c>
+      <c r="AL13" s="8">
+        <f>AL10-AL11-AL12</f>
+        <v>114.39999999999999</v>
+      </c>
+      <c r="AM13" s="8">
+        <f t="shared" ref="AM13:AV13" si="26">AM10-AM11-AM12</f>
+        <v>-63.600000000000158</v>
+      </c>
+      <c r="AN13" s="8">
         <f t="shared" si="26"/>
-        <v>-20.699999999999964</v>
-      </c>
-      <c r="AA13" s="8">
+        <v>-3.5000000000000595</v>
+      </c>
+      <c r="AO13" s="8">
         <f t="shared" si="26"/>
-        <v>-8.2999999999999758</v>
-      </c>
-      <c r="AB13" s="8">
+        <v>-61.499999999999844</v>
+      </c>
+      <c r="AP13" s="8">
         <f t="shared" si="26"/>
-        <v>5.0230800000000162</v>
-      </c>
-      <c r="AC13" s="8"/>
-      <c r="AE13" s="8">
-        <f>AE10-AE11-AE12</f>
-        <v>-10.699999999999964</v>
-      </c>
-      <c r="AF13" s="8">
-        <f>AF10-AF11-AF12</f>
-        <v>-13.299999999999931</v>
-      </c>
-      <c r="AG13" s="8">
-        <f>AG10-AG11-AG12</f>
-        <v>122.10000000000001</v>
-      </c>
-      <c r="AH13" s="8">
-        <f>AH10-AH11-AH12</f>
-        <v>114.39999999999999</v>
-      </c>
-      <c r="AI13" s="8">
-        <f t="shared" ref="AI13:AR13" si="27">AI10-AI11-AI12</f>
-        <v>-63.600000000000158</v>
-      </c>
-      <c r="AJ13" s="8">
+        <v>-12.000000000000039</v>
+      </c>
+      <c r="AQ13" s="8">
+        <f t="shared" si="26"/>
+        <v>-59.430840000000003</v>
+      </c>
+      <c r="AR13" s="8">
+        <f t="shared" si="26"/>
+        <v>-37.901776000000027</v>
+      </c>
+      <c r="AS13" s="8">
+        <f t="shared" si="26"/>
+        <v>-14.155653999999995</v>
+      </c>
+      <c r="AT13" s="8">
+        <f t="shared" si="26"/>
+        <v>-9.2153103820000002</v>
+      </c>
+      <c r="AU13" s="8">
+        <f t="shared" si="26"/>
+        <v>-4.7809896459399752</v>
+      </c>
+      <c r="AV13" s="8">
+        <f t="shared" si="26"/>
+        <v>-0.21391218228454711</v>
+      </c>
+      <c r="AW13" s="8">
+        <f t="shared" ref="AW13:AZ13" si="27">AW10-AW11-AW12</f>
+        <v>4.488954367950015</v>
+      </c>
+      <c r="AX13" s="8">
         <f t="shared" si="27"/>
-        <v>-3.5000000000000595</v>
-      </c>
-      <c r="AK13" s="8">
+        <v>9.3307048788105149</v>
+      </c>
+      <c r="AY13" s="8">
         <f t="shared" si="27"/>
-        <v>-61.499999999999844</v>
-      </c>
-      <c r="AL13" s="8">
+        <v>14.314497951256383</v>
+      </c>
+      <c r="AZ13" s="8">
         <f t="shared" si="27"/>
-        <v>-32.176919999999797</v>
-      </c>
-      <c r="AM13" s="8">
-        <f t="shared" si="27"/>
-        <v>-21.43680679999995</v>
-      </c>
-      <c r="AN13" s="8">
-        <f t="shared" si="27"/>
-        <v>-9.4941000399999389</v>
-      </c>
-      <c r="AO13" s="8">
-        <f t="shared" si="27"/>
-        <v>20.1159502016001</v>
-      </c>
-      <c r="AP13" s="8">
-        <f t="shared" si="27"/>
-        <v>29.509802442968102</v>
-      </c>
-      <c r="AQ13" s="8">
-        <f t="shared" si="27"/>
-        <v>34.421386496461878</v>
-      </c>
-      <c r="AR13" s="8">
-        <f t="shared" si="27"/>
-        <v>39.47206109643782</v>
-      </c>
-      <c r="AS13" s="8">
-        <f t="shared" ref="AS13:AV13" si="28">AS10-AS11-AS12</f>
-        <v>44.664945992040671</v>
-      </c>
-      <c r="AT13" s="8">
-        <f t="shared" si="28"/>
-        <v>50.003224587267141</v>
-      </c>
-      <c r="AU13" s="8">
-        <f t="shared" si="28"/>
-        <v>55.490145163075915</v>
-      </c>
-      <c r="AV13" s="8">
-        <f t="shared" si="28"/>
-        <v>61.129022121523171</v>
+        <v>19.443557147146741</v>
       </c>
     </row>
-    <row r="14" spans="2:158" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:162" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>30</v>
       </c>
@@ -2735,81 +2903,84 @@
         <v>2.1</v>
       </c>
       <c r="AB14" s="4">
-        <f t="shared" ref="AB14" si="29">AB13*0.2</f>
-        <v>1.0046160000000033</v>
+        <v>-1</v>
       </c>
       <c r="AC14" s="4"/>
-      <c r="AE14" s="4">
+      <c r="AD14" s="4"/>
+      <c r="AE14" s="4"/>
+      <c r="AF14" s="4"/>
+      <c r="AG14" s="4"/>
+      <c r="AI14" s="4">
         <v>3</v>
       </c>
-      <c r="AF14" s="4">
+      <c r="AJ14" s="4">
         <v>-5</v>
       </c>
-      <c r="AG14" s="4">
+      <c r="AK14" s="4">
         <v>18.8</v>
       </c>
-      <c r="AH14" s="4">
+      <c r="AL14" s="4">
         <f>SUM(I14:L14)</f>
         <v>13.600000000000001</v>
       </c>
-      <c r="AI14" s="4">
+      <c r="AM14" s="4">
         <f>SUM(M14:P14)</f>
         <v>-9.9</v>
       </c>
-      <c r="AJ14" s="4">
+      <c r="AN14" s="4">
         <f>SUM(Q14:T14)</f>
         <v>-2.4</v>
       </c>
-      <c r="AK14" s="4">
+      <c r="AO14" s="4">
         <f>SUM(U14:X14)</f>
         <v>21.7</v>
       </c>
-      <c r="AL14" s="4">
+      <c r="AP14" s="4">
         <f>SUM(Y14:AB14)</f>
-        <v>4.8046160000000038</v>
-      </c>
-      <c r="AM14" s="4">
-        <f t="shared" ref="AM14:AR14" si="30">AM13*0.19</f>
-        <v>-4.0729932919999907</v>
-      </c>
-      <c r="AN14" s="4">
-        <f t="shared" si="30"/>
-        <v>-1.8038790075999884</v>
-      </c>
-      <c r="AO14" s="4">
-        <f t="shared" si="30"/>
-        <v>3.822030538304019</v>
-      </c>
-      <c r="AP14" s="4">
-        <f t="shared" si="30"/>
-        <v>5.6068624641639397</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="AQ14" s="4">
-        <f t="shared" si="30"/>
-        <v>6.5400634343277568</v>
+        <f t="shared" ref="AQ14:AV14" si="28">AQ13*0.19</f>
+        <v>-11.2918596</v>
       </c>
       <c r="AR14" s="4">
-        <f t="shared" si="30"/>
-        <v>7.4996916083231859</v>
+        <f t="shared" si="28"/>
+        <v>-7.201337440000005</v>
       </c>
       <c r="AS14" s="4">
-        <f t="shared" ref="AS14:AV14" si="31">AS13*0.19</f>
-        <v>8.486339738487727</v>
+        <f t="shared" si="28"/>
+        <v>-2.6895742599999992</v>
       </c>
       <c r="AT14" s="4">
-        <f t="shared" si="31"/>
-        <v>9.5006126715807575</v>
+        <f t="shared" si="28"/>
+        <v>-1.75090897258</v>
       </c>
       <c r="AU14" s="4">
-        <f t="shared" si="31"/>
-        <v>10.543127580984423</v>
+        <f t="shared" si="28"/>
+        <v>-0.90838803272859525</v>
       </c>
       <c r="AV14" s="4">
-        <f t="shared" si="31"/>
-        <v>11.614514203089403</v>
+        <f t="shared" si="28"/>
+        <v>-4.0643314634063954E-2</v>
+      </c>
+      <c r="AW14" s="4">
+        <f t="shared" ref="AW14:AZ14" si="29">AW13*0.19</f>
+        <v>0.85290132991050283</v>
+      </c>
+      <c r="AX14" s="4">
+        <f t="shared" si="29"/>
+        <v>1.7728339269739979</v>
+      </c>
+      <c r="AY14" s="4">
+        <f t="shared" si="29"/>
+        <v>2.7197546107387129</v>
+      </c>
+      <c r="AZ14" s="4">
+        <f t="shared" si="29"/>
+        <v>3.6942758579578809</v>
       </c>
     </row>
-    <row r="15" spans="2:158" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:162" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>60</v>
       </c>
@@ -2884,41 +3055,45 @@
         <v>0.2</v>
       </c>
       <c r="AB15" s="4">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AC15" s="4"/>
+      <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
       <c r="AG15" s="4"/>
-      <c r="AH15" s="4"/>
-      <c r="AI15" s="4">
+      <c r="AI15" s="4"/>
+      <c r="AJ15" s="4"/>
+      <c r="AK15" s="4"/>
+      <c r="AL15" s="4"/>
+      <c r="AM15" s="4">
         <f>SUM(M15:P15)</f>
         <v>7.1000000000000005</v>
       </c>
-      <c r="AJ15" s="4">
+      <c r="AN15" s="4">
         <f>SUM(Q15:T15)</f>
         <v>-4.1999999999999993</v>
       </c>
-      <c r="AK15" s="4">
+      <c r="AO15" s="4">
         <f>SUM(U15:X15)</f>
         <v>14.8</v>
       </c>
-      <c r="AL15" s="4">
+      <c r="AP15" s="4">
         <f>SUM(Y15:AB15)</f>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="AM15" s="4"/>
-      <c r="AN15" s="4"/>
-      <c r="AO15" s="4"/>
-      <c r="AP15" s="4"/>
+        <v>1.2</v>
+      </c>
       <c r="AQ15" s="4"/>
       <c r="AR15" s="4"/>
       <c r="AS15" s="4"/>
       <c r="AT15" s="4"/>
       <c r="AU15" s="4"/>
       <c r="AV15" s="4"/>
+      <c r="AW15" s="4"/>
+      <c r="AX15" s="4"/>
+      <c r="AY15" s="4"/>
+      <c r="AZ15" s="4"/>
     </row>
-    <row r="16" spans="2:158" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:162" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
@@ -2931,7 +3106,7 @@
         <v>6.1000000000000014</v>
       </c>
       <c r="E16" s="8">
-        <f t="shared" ref="E16" si="32">E13-E14</f>
+        <f t="shared" ref="E16" si="30">E13-E14</f>
         <v>1.0999999999999912</v>
       </c>
       <c r="G16" s="8">
@@ -2943,600 +3118,604 @@
         <v>42.999999999999957</v>
       </c>
       <c r="I16" s="8">
-        <f t="shared" ref="I16" si="33">I13-I14</f>
+        <f t="shared" ref="I16" si="31">I13-I14</f>
         <v>46.699999999999946</v>
       </c>
       <c r="J16" s="8">
-        <f t="shared" ref="J16:X16" si="34">J13-J14-J15</f>
+        <f t="shared" ref="J16:X16" si="32">J13-J14-J15</f>
         <v>27.599999999999952</v>
       </c>
       <c r="K16" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1.7000000000000171</v>
       </c>
       <c r="L16" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>24.800000000000011</v>
       </c>
       <c r="M16" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>-5.0999999999999837</v>
       </c>
       <c r="N16" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>-59.400000000000034</v>
       </c>
       <c r="O16" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>-8.7999999999999847</v>
       </c>
       <c r="P16" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>12.500000000000011</v>
       </c>
       <c r="Q16" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>-1.0000000000000231</v>
       </c>
       <c r="R16" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1.0999999999999828</v>
       </c>
       <c r="S16" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>-3.1000000000000241</v>
       </c>
       <c r="T16" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>6.0999999999999925</v>
       </c>
       <c r="U16" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>-12.399999999999986</v>
       </c>
       <c r="V16" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>-29.499999999999982</v>
       </c>
       <c r="W16" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>-58.300000000000004</v>
       </c>
       <c r="X16" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>2.2000000000000481</v>
       </c>
       <c r="Y16" s="8">
-        <f t="shared" ref="Y16" si="35">Y13-Y14-Y15</f>
+        <f t="shared" ref="Y16" si="33">Y13-Y14-Y15</f>
         <v>-10.399999999999967</v>
       </c>
       <c r="Z16" s="8">
-        <f t="shared" ref="Z16" si="36">Z13-Z14-Z15</f>
+        <f t="shared" ref="Z16" si="34">Z13-Z14-Z15</f>
         <v>-20.899999999999967</v>
       </c>
       <c r="AA16" s="8">
-        <f t="shared" ref="AA16" si="37">AA13-AA14-AA15</f>
+        <f t="shared" ref="AA16" si="35">AA13-AA14-AA15</f>
         <v>-10.599999999999975</v>
       </c>
       <c r="AB16" s="8">
-        <f t="shared" ref="AB16" si="38">AB13-AB14-AB15</f>
-        <v>4.0184640000000131</v>
+        <f t="shared" ref="AB16" si="36">AB13-AB14-AB15</f>
+        <v>25.899999999999956</v>
       </c>
       <c r="AC16" s="8"/>
-      <c r="AE16" s="8">
-        <f>AE13-AE14</f>
+      <c r="AD16" s="8"/>
+      <c r="AE16" s="8"/>
+      <c r="AF16" s="8"/>
+      <c r="AG16" s="8"/>
+      <c r="AI16" s="8">
+        <f>AI13-AI14</f>
         <v>-13.699999999999964</v>
       </c>
-      <c r="AF16" s="8">
-        <f>AF13-AF14</f>
+      <c r="AJ16" s="8">
+        <f>AJ13-AJ14</f>
         <v>-8.2999999999999314</v>
       </c>
-      <c r="AG16" s="8">
-        <f>AG13-AG14</f>
+      <c r="AK16" s="8">
+        <f>AK13-AK14</f>
         <v>103.30000000000001</v>
       </c>
-      <c r="AH16" s="8">
-        <f>AH13-AH14</f>
+      <c r="AL16" s="8">
+        <f>AL13-AL14</f>
         <v>100.79999999999998</v>
       </c>
-      <c r="AI16" s="8">
-        <f t="shared" ref="AI16:AV16" si="39">AI13-AI14-AI15</f>
+      <c r="AM16" s="8">
+        <f t="shared" ref="AM16:AZ16" si="37">AM13-AM14-AM15</f>
         <v>-60.800000000000161</v>
       </c>
-      <c r="AJ16" s="8">
+      <c r="AN16" s="8">
+        <f t="shared" si="37"/>
+        <v>3.0999999999999397</v>
+      </c>
+      <c r="AO16" s="8">
+        <f t="shared" si="37"/>
+        <v>-97.999999999999844</v>
+      </c>
+      <c r="AP16" s="8">
+        <f t="shared" si="37"/>
+        <v>-16.000000000000039</v>
+      </c>
+      <c r="AQ16" s="8">
+        <f t="shared" si="37"/>
+        <v>-48.138980400000001</v>
+      </c>
+      <c r="AR16" s="8">
+        <f t="shared" si="37"/>
+        <v>-30.700438560000023</v>
+      </c>
+      <c r="AS16" s="8">
+        <f t="shared" si="37"/>
+        <v>-11.466079739999996</v>
+      </c>
+      <c r="AT16" s="8">
+        <f t="shared" si="37"/>
+        <v>-7.4644014094200006</v>
+      </c>
+      <c r="AU16" s="8">
+        <f t="shared" si="37"/>
+        <v>-3.8726016132113799</v>
+      </c>
+      <c r="AV16" s="8">
+        <f t="shared" si="37"/>
+        <v>-0.17326886765048316</v>
+      </c>
+      <c r="AW16" s="8">
+        <f t="shared" si="37"/>
+        <v>3.6360530380395124</v>
+      </c>
+      <c r="AX16" s="8">
+        <f t="shared" si="37"/>
+        <v>7.5578709518365166</v>
+      </c>
+      <c r="AY16" s="8">
+        <f t="shared" si="37"/>
+        <v>11.59474334051767</v>
+      </c>
+      <c r="AZ16" s="8">
+        <f t="shared" si="37"/>
+        <v>15.749281289188861</v>
+      </c>
+      <c r="BA16" s="1">
+        <f>AZ16*(1+$BC$24)</f>
+        <v>15.591788476296973</v>
+      </c>
+      <c r="BB16" s="1">
+        <f t="shared" ref="BB16:DM16" si="38">BA16*(1+$BC$24)</f>
+        <v>15.435870591534004</v>
+      </c>
+      <c r="BC16" s="1">
+        <f t="shared" si="38"/>
+        <v>15.281511885618663</v>
+      </c>
+      <c r="BD16" s="1">
+        <f t="shared" si="38"/>
+        <v>15.128696766762475</v>
+      </c>
+      <c r="BE16" s="1">
+        <f t="shared" si="38"/>
+        <v>14.97740979909485</v>
+      </c>
+      <c r="BF16" s="1">
+        <f t="shared" si="38"/>
+        <v>14.827635701103901</v>
+      </c>
+      <c r="BG16" s="1">
+        <f t="shared" si="38"/>
+        <v>14.679359344092862</v>
+      </c>
+      <c r="BH16" s="1">
+        <f t="shared" si="38"/>
+        <v>14.532565750651933</v>
+      </c>
+      <c r="BI16" s="1">
+        <f t="shared" si="38"/>
+        <v>14.387240093145413</v>
+      </c>
+      <c r="BJ16" s="1">
+        <f t="shared" si="38"/>
+        <v>14.243367692213958</v>
+      </c>
+      <c r="BK16" s="1">
+        <f t="shared" si="38"/>
+        <v>14.100934015291818</v>
+      </c>
+      <c r="BL16" s="1">
+        <f t="shared" si="38"/>
+        <v>13.9599246751389</v>
+      </c>
+      <c r="BM16" s="1">
+        <f t="shared" si="38"/>
+        <v>13.820325428387511</v>
+      </c>
+      <c r="BN16" s="1">
+        <f t="shared" si="38"/>
+        <v>13.682122174103636</v>
+      </c>
+      <c r="BO16" s="1">
+        <f t="shared" si="38"/>
+        <v>13.5453009523626</v>
+      </c>
+      <c r="BP16" s="1">
+        <f t="shared" si="38"/>
+        <v>13.409847942838974</v>
+      </c>
+      <c r="BQ16" s="1">
+        <f t="shared" si="38"/>
+        <v>13.275749463410584</v>
+      </c>
+      <c r="BR16" s="1">
+        <f t="shared" si="38"/>
+        <v>13.142991968776478</v>
+      </c>
+      <c r="BS16" s="1">
+        <f t="shared" si="38"/>
+        <v>13.011562049088713</v>
+      </c>
+      <c r="BT16" s="1">
+        <f t="shared" si="38"/>
+        <v>12.881446428597826</v>
+      </c>
+      <c r="BU16" s="1">
+        <f t="shared" si="38"/>
+        <v>12.752631964311847</v>
+      </c>
+      <c r="BV16" s="1">
+        <f t="shared" si="38"/>
+        <v>12.625105644668729</v>
+      </c>
+      <c r="BW16" s="1">
+        <f t="shared" si="38"/>
+        <v>12.498854588222041</v>
+      </c>
+      <c r="BX16" s="1">
+        <f t="shared" si="38"/>
+        <v>12.37386604233982</v>
+      </c>
+      <c r="BY16" s="1">
+        <f t="shared" si="38"/>
+        <v>12.250127381916421</v>
+      </c>
+      <c r="BZ16" s="1">
+        <f t="shared" si="38"/>
+        <v>12.127626108097257</v>
+      </c>
+      <c r="CA16" s="1">
+        <f t="shared" si="38"/>
+        <v>12.006349847016285</v>
+      </c>
+      <c r="CB16" s="1">
+        <f t="shared" si="38"/>
+        <v>11.886286348546122</v>
+      </c>
+      <c r="CC16" s="1">
+        <f t="shared" si="38"/>
+        <v>11.767423485060661</v>
+      </c>
+      <c r="CD16" s="1">
+        <f t="shared" si="38"/>
+        <v>11.649749250210053</v>
+      </c>
+      <c r="CE16" s="1">
+        <f t="shared" si="38"/>
+        <v>11.533251757707953</v>
+      </c>
+      <c r="CF16" s="1">
+        <f t="shared" si="38"/>
+        <v>11.417919240130873</v>
+      </c>
+      <c r="CG16" s="1">
+        <f t="shared" si="38"/>
+        <v>11.303740047729564</v>
+      </c>
+      <c r="CH16" s="1">
+        <f t="shared" si="38"/>
+        <v>11.190702647252268</v>
+      </c>
+      <c r="CI16" s="1">
+        <f t="shared" si="38"/>
+        <v>11.078795620779745</v>
+      </c>
+      <c r="CJ16" s="1">
+        <f t="shared" si="38"/>
+        <v>10.968007664571948</v>
+      </c>
+      <c r="CK16" s="1">
+        <f t="shared" si="38"/>
+        <v>10.858327587926228</v>
+      </c>
+      <c r="CL16" s="1">
+        <f t="shared" si="38"/>
+        <v>10.749744312046966</v>
+      </c>
+      <c r="CM16" s="1">
+        <f t="shared" si="38"/>
+        <v>10.642246868926495</v>
+      </c>
+      <c r="CN16" s="1">
+        <f t="shared" si="38"/>
+        <v>10.53582440023723</v>
+      </c>
+      <c r="CO16" s="1">
+        <f t="shared" si="38"/>
+        <v>10.430466156234857</v>
+      </c>
+      <c r="CP16" s="1">
+        <f t="shared" si="38"/>
+        <v>10.326161494672508</v>
+      </c>
+      <c r="CQ16" s="1">
+        <f t="shared" si="38"/>
+        <v>10.222899879725784</v>
+      </c>
+      <c r="CR16" s="1">
+        <f t="shared" si="38"/>
+        <v>10.120670880928525</v>
+      </c>
+      <c r="CS16" s="1">
+        <f t="shared" si="38"/>
+        <v>10.019464172119241</v>
+      </c>
+      <c r="CT16" s="1">
+        <f t="shared" si="38"/>
+        <v>9.9192695303980489</v>
+      </c>
+      <c r="CU16" s="1">
+        <f t="shared" si="38"/>
+        <v>9.8200768350940688</v>
+      </c>
+      <c r="CV16" s="1">
+        <f t="shared" si="38"/>
+        <v>9.7218760667431283</v>
+      </c>
+      <c r="CW16" s="1">
+        <f t="shared" si="38"/>
+        <v>9.6246573060756972</v>
+      </c>
+      <c r="CX16" s="1">
+        <f t="shared" si="38"/>
+        <v>9.5284107330149403</v>
+      </c>
+      <c r="CY16" s="1">
+        <f t="shared" si="38"/>
+        <v>9.4331266256847908</v>
+      </c>
+      <c r="CZ16" s="1">
+        <f t="shared" si="38"/>
+        <v>9.3387953594279427</v>
+      </c>
+      <c r="DA16" s="1">
+        <f t="shared" si="38"/>
+        <v>9.2454074058336637</v>
+      </c>
+      <c r="DB16" s="1">
+        <f t="shared" si="38"/>
+        <v>9.1529533317753273</v>
+      </c>
+      <c r="DC16" s="1">
+        <f t="shared" si="38"/>
+        <v>9.0614237984575734</v>
+      </c>
+      <c r="DD16" s="1">
+        <f t="shared" si="38"/>
+        <v>8.9708095604729969</v>
+      </c>
+      <c r="DE16" s="1">
+        <f t="shared" si="38"/>
+        <v>8.8811014648682676</v>
+      </c>
+      <c r="DF16" s="1">
+        <f t="shared" si="38"/>
+        <v>8.7922904502195856</v>
+      </c>
+      <c r="DG16" s="1">
+        <f t="shared" si="38"/>
+        <v>8.704367545717389</v>
+      </c>
+      <c r="DH16" s="1">
+        <f t="shared" si="38"/>
+        <v>8.6173238702602148</v>
+      </c>
+      <c r="DI16" s="1">
+        <f t="shared" si="38"/>
+        <v>8.5311506315576118</v>
+      </c>
+      <c r="DJ16" s="1">
+        <f t="shared" si="38"/>
+        <v>8.4458391252420348</v>
+      </c>
+      <c r="DK16" s="1">
+        <f t="shared" si="38"/>
+        <v>8.3613807339896145</v>
+      </c>
+      <c r="DL16" s="1">
+        <f t="shared" si="38"/>
+        <v>8.2777669266497185</v>
+      </c>
+      <c r="DM16" s="1">
+        <f t="shared" si="38"/>
+        <v>8.1949892573832219</v>
+      </c>
+      <c r="DN16" s="1">
+        <f t="shared" ref="DN16:FF16" si="39">DM16*(1+$BC$24)</f>
+        <v>8.1130393648093904</v>
+      </c>
+      <c r="DO16" s="1">
         <f t="shared" si="39"/>
-        <v>3.0999999999999397</v>
-      </c>
-      <c r="AK16" s="8">
+        <v>8.0319089711612968</v>
+      </c>
+      <c r="DP16" s="1">
         <f t="shared" si="39"/>
-        <v>-97.999999999999844</v>
-      </c>
-      <c r="AL16" s="8">
+        <v>7.9515898814496841</v>
+      </c>
+      <c r="DQ16" s="1">
         <f t="shared" si="39"/>
-        <v>-37.881535999999798</v>
-      </c>
-      <c r="AM16" s="8">
+        <v>7.8720739826351869</v>
+      </c>
+      <c r="DR16" s="1">
         <f t="shared" si="39"/>
-        <v>-17.363813507999957</v>
-      </c>
-      <c r="AN16" s="8">
+        <v>7.793353242808835</v>
+      </c>
+      <c r="DS16" s="1">
         <f t="shared" si="39"/>
-        <v>-7.6902210323999505</v>
-      </c>
-      <c r="AO16" s="8">
+        <v>7.7154197103807469</v>
+      </c>
+      <c r="DT16" s="1">
         <f t="shared" si="39"/>
-        <v>16.29391966329608</v>
-      </c>
-      <c r="AP16" s="8">
+        <v>7.6382655132769397</v>
+      </c>
+      <c r="DU16" s="1">
         <f t="shared" si="39"/>
-        <v>23.902939978804163</v>
-      </c>
-      <c r="AQ16" s="8">
+        <v>7.5618828581441706</v>
+      </c>
+      <c r="DV16" s="1">
         <f t="shared" si="39"/>
-        <v>27.881323062134122</v>
-      </c>
-      <c r="AR16" s="8">
+        <v>7.4862640295627285</v>
+      </c>
+      <c r="DW16" s="1">
         <f t="shared" si="39"/>
-        <v>31.972369488114634</v>
-      </c>
-      <c r="AS16" s="8">
+        <v>7.4114013892671009</v>
+      </c>
+      <c r="DX16" s="1">
         <f t="shared" si="39"/>
-        <v>36.178606253552942</v>
-      </c>
-      <c r="AT16" s="8">
+        <v>7.3372873753744301</v>
+      </c>
+      <c r="DY16" s="1">
         <f t="shared" si="39"/>
-        <v>40.502611915686387</v>
-      </c>
-      <c r="AU16" s="8">
+        <v>7.2639145016206861</v>
+      </c>
+      <c r="DZ16" s="1">
         <f t="shared" si="39"/>
-        <v>44.94701758209149</v>
-      </c>
-      <c r="AV16" s="8">
+        <v>7.1912753566044794</v>
+      </c>
+      <c r="EA16" s="1">
         <f t="shared" si="39"/>
-        <v>49.514507918433765</v>
-      </c>
-      <c r="AW16" s="1">
-        <f>AV16*(1+$AY$24)</f>
-        <v>49.019362839249425</v>
-      </c>
-      <c r="AX16" s="1">
-        <f t="shared" ref="AX16:DI16" si="40">AW16*(1+$AY$24)</f>
-        <v>48.529169210856928</v>
-      </c>
-      <c r="AY16" s="1">
-        <f t="shared" si="40"/>
-        <v>48.04387751874836</v>
-      </c>
-      <c r="AZ16" s="1">
-        <f t="shared" si="40"/>
-        <v>47.563438743560873</v>
-      </c>
-      <c r="BA16" s="1">
-        <f t="shared" si="40"/>
-        <v>47.087804356125261</v>
-      </c>
-      <c r="BB16" s="1">
-        <f t="shared" si="40"/>
-        <v>46.616926312564011</v>
-      </c>
-      <c r="BC16" s="1">
-        <f t="shared" si="40"/>
-        <v>46.150757049438369</v>
-      </c>
-      <c r="BD16" s="1">
-        <f t="shared" si="40"/>
-        <v>45.689249478943985</v>
-      </c>
-      <c r="BE16" s="1">
-        <f t="shared" si="40"/>
-        <v>45.232356984154542</v>
-      </c>
-      <c r="BF16" s="1">
-        <f t="shared" si="40"/>
-        <v>44.780033414312996</v>
-      </c>
-      <c r="BG16" s="1">
-        <f t="shared" si="40"/>
-        <v>44.332233080169864</v>
-      </c>
-      <c r="BH16" s="1">
-        <f t="shared" si="40"/>
-        <v>43.888910749368165</v>
-      </c>
-      <c r="BI16" s="1">
-        <f t="shared" si="40"/>
-        <v>43.450021641874486</v>
-      </c>
-      <c r="BJ16" s="1">
-        <f t="shared" si="40"/>
-        <v>43.015521425455738</v>
-      </c>
-      <c r="BK16" s="1">
-        <f t="shared" si="40"/>
-        <v>42.585366211201183</v>
-      </c>
-      <c r="BL16" s="1">
-        <f t="shared" si="40"/>
-        <v>42.159512549089172</v>
-      </c>
-      <c r="BM16" s="1">
-        <f t="shared" si="40"/>
-        <v>41.737917423598283</v>
-      </c>
-      <c r="BN16" s="1">
-        <f t="shared" si="40"/>
-        <v>41.320538249362301</v>
-      </c>
-      <c r="BO16" s="1">
-        <f t="shared" si="40"/>
-        <v>40.907332866868678</v>
-      </c>
-      <c r="BP16" s="1">
-        <f t="shared" si="40"/>
-        <v>40.498259538199989</v>
-      </c>
-      <c r="BQ16" s="1">
-        <f t="shared" si="40"/>
-        <v>40.093276942817987</v>
-      </c>
-      <c r="BR16" s="1">
-        <f t="shared" si="40"/>
-        <v>39.692344173389806</v>
-      </c>
-      <c r="BS16" s="1">
-        <f t="shared" si="40"/>
-        <v>39.295420731655909</v>
-      </c>
-      <c r="BT16" s="1">
-        <f t="shared" si="40"/>
-        <v>38.902466524339353</v>
-      </c>
-      <c r="BU16" s="1">
-        <f t="shared" si="40"/>
-        <v>38.513441859095956</v>
-      </c>
-      <c r="BV16" s="1">
-        <f t="shared" si="40"/>
-        <v>38.128307440504997</v>
-      </c>
-      <c r="BW16" s="1">
-        <f t="shared" si="40"/>
-        <v>37.74702436609995</v>
-      </c>
-      <c r="BX16" s="1">
-        <f t="shared" si="40"/>
-        <v>37.369554122438949</v>
-      </c>
-      <c r="BY16" s="1">
-        <f t="shared" si="40"/>
-        <v>36.995858581214556</v>
-      </c>
-      <c r="BZ16" s="1">
-        <f t="shared" si="40"/>
-        <v>36.625899995402413</v>
-      </c>
-      <c r="CA16" s="1">
-        <f t="shared" si="40"/>
-        <v>36.259640995448386</v>
-      </c>
-      <c r="CB16" s="1">
-        <f t="shared" si="40"/>
-        <v>35.897044585493902</v>
-      </c>
-      <c r="CC16" s="1">
-        <f t="shared" si="40"/>
-        <v>35.538074139638965</v>
-      </c>
-      <c r="CD16" s="1">
-        <f t="shared" si="40"/>
-        <v>35.182693398242577</v>
-      </c>
-      <c r="CE16" s="1">
-        <f t="shared" si="40"/>
-        <v>34.830866464260154</v>
-      </c>
-      <c r="CF16" s="1">
-        <f t="shared" si="40"/>
-        <v>34.482557799617553</v>
-      </c>
-      <c r="CG16" s="1">
-        <f t="shared" si="40"/>
-        <v>34.137732221621377</v>
-      </c>
-      <c r="CH16" s="1">
-        <f t="shared" si="40"/>
-        <v>33.796354899405166</v>
-      </c>
-      <c r="CI16" s="1">
-        <f t="shared" si="40"/>
-        <v>33.458391350411112</v>
-      </c>
-      <c r="CJ16" s="1">
-        <f t="shared" si="40"/>
-        <v>33.123807436907001</v>
-      </c>
-      <c r="CK16" s="1">
-        <f t="shared" si="40"/>
-        <v>32.792569362537932</v>
-      </c>
-      <c r="CL16" s="1">
-        <f t="shared" si="40"/>
-        <v>32.464643668912551</v>
-      </c>
-      <c r="CM16" s="1">
-        <f t="shared" si="40"/>
-        <v>32.139997232223422</v>
-      </c>
-      <c r="CN16" s="1">
-        <f t="shared" si="40"/>
-        <v>31.818597259901189</v>
-      </c>
-      <c r="CO16" s="1">
-        <f t="shared" si="40"/>
-        <v>31.500411287302178</v>
-      </c>
-      <c r="CP16" s="1">
-        <f t="shared" si="40"/>
-        <v>31.185407174429155</v>
-      </c>
-      <c r="CQ16" s="1">
-        <f t="shared" si="40"/>
-        <v>30.873553102684863</v>
-      </c>
-      <c r="CR16" s="1">
-        <f t="shared" si="40"/>
-        <v>30.564817571658015</v>
-      </c>
-      <c r="CS16" s="1">
-        <f t="shared" si="40"/>
-        <v>30.259169395941434</v>
-      </c>
-      <c r="CT16" s="1">
-        <f t="shared" si="40"/>
-        <v>29.95657770198202</v>
-      </c>
-      <c r="CU16" s="1">
-        <f t="shared" si="40"/>
-        <v>29.657011924962198</v>
-      </c>
-      <c r="CV16" s="1">
-        <f t="shared" si="40"/>
-        <v>29.360441805712576</v>
-      </c>
-      <c r="CW16" s="1">
-        <f t="shared" si="40"/>
-        <v>29.06683738765545</v>
-      </c>
-      <c r="CX16" s="1">
-        <f t="shared" si="40"/>
-        <v>28.776169013778894</v>
-      </c>
-      <c r="CY16" s="1">
-        <f t="shared" si="40"/>
-        <v>28.488407323641106</v>
-      </c>
-      <c r="CZ16" s="1">
-        <f t="shared" si="40"/>
-        <v>28.203523250404693</v>
-      </c>
-      <c r="DA16" s="1">
-        <f t="shared" si="40"/>
-        <v>27.921488017900646</v>
-      </c>
-      <c r="DB16" s="1">
-        <f t="shared" si="40"/>
-        <v>27.642273137721638</v>
-      </c>
-      <c r="DC16" s="1">
-        <f t="shared" si="40"/>
-        <v>27.365850406344421</v>
-      </c>
-      <c r="DD16" s="1">
-        <f t="shared" si="40"/>
-        <v>27.092191902280977</v>
-      </c>
-      <c r="DE16" s="1">
-        <f t="shared" si="40"/>
-        <v>26.821269983258166</v>
-      </c>
-      <c r="DF16" s="1">
-        <f t="shared" si="40"/>
-        <v>26.553057283425584</v>
-      </c>
-      <c r="DG16" s="1">
-        <f t="shared" si="40"/>
-        <v>26.28752671059133</v>
-      </c>
-      <c r="DH16" s="1">
-        <f t="shared" si="40"/>
-        <v>26.024651443485418</v>
-      </c>
-      <c r="DI16" s="1">
-        <f t="shared" si="40"/>
-        <v>25.764404929050563</v>
-      </c>
-      <c r="DJ16" s="1">
-        <f t="shared" ref="DJ16:FB16" si="41">DI16*(1+$AY$24)</f>
-        <v>25.506760879760058</v>
-      </c>
-      <c r="DK16" s="1">
-        <f t="shared" si="41"/>
-        <v>25.251693270962459</v>
-      </c>
-      <c r="DL16" s="1">
-        <f t="shared" si="41"/>
-        <v>24.999176338252834</v>
-      </c>
-      <c r="DM16" s="1">
-        <f t="shared" si="41"/>
-        <v>24.749184574870306</v>
-      </c>
-      <c r="DN16" s="1">
-        <f t="shared" si="41"/>
-        <v>24.501692729121601</v>
-      </c>
-      <c r="DO16" s="1">
-        <f t="shared" si="41"/>
-        <v>24.256675801830383</v>
-      </c>
-      <c r="DP16" s="1">
-        <f t="shared" si="41"/>
-        <v>24.014109043812081</v>
-      </c>
-      <c r="DQ16" s="1">
-        <f t="shared" si="41"/>
-        <v>23.773967953373958</v>
-      </c>
-      <c r="DR16" s="1">
-        <f t="shared" si="41"/>
-        <v>23.536228273840219</v>
-      </c>
-      <c r="DS16" s="1">
-        <f t="shared" si="41"/>
-        <v>23.300865991101816</v>
-      </c>
-      <c r="DT16" s="1">
-        <f t="shared" si="41"/>
-        <v>23.067857331190798</v>
-      </c>
-      <c r="DU16" s="1">
-        <f t="shared" si="41"/>
-        <v>22.837178757878888</v>
-      </c>
-      <c r="DV16" s="1">
-        <f t="shared" si="41"/>
-        <v>22.608806970300098</v>
-      </c>
-      <c r="DW16" s="1">
-        <f t="shared" si="41"/>
-        <v>22.382718900597098</v>
-      </c>
-      <c r="DX16" s="1">
-        <f t="shared" si="41"/>
-        <v>22.158891711591128</v>
-      </c>
-      <c r="DY16" s="1">
-        <f t="shared" si="41"/>
-        <v>21.937302794475215</v>
-      </c>
-      <c r="DZ16" s="1">
-        <f t="shared" si="41"/>
-        <v>21.717929766530464</v>
-      </c>
-      <c r="EA16" s="1">
-        <f t="shared" si="41"/>
-        <v>21.50075046886516</v>
+        <v>7.1193626030384349</v>
       </c>
       <c r="EB16" s="1">
-        <f t="shared" si="41"/>
-        <v>21.285742964176507</v>
+        <f t="shared" si="39"/>
+        <v>7.0481689770080509</v>
       </c>
       <c r="EC16" s="1">
-        <f t="shared" si="41"/>
-        <v>21.072885534534741</v>
+        <f t="shared" si="39"/>
+        <v>6.9776872872379707</v>
       </c>
       <c r="ED16" s="1">
-        <f t="shared" si="41"/>
-        <v>20.862156679189393</v>
+        <f t="shared" si="39"/>
+        <v>6.9079104143655909</v>
       </c>
       <c r="EE16" s="1">
-        <f t="shared" si="41"/>
-        <v>20.653535112397499</v>
+        <f t="shared" si="39"/>
+        <v>6.8388313102219351</v>
       </c>
       <c r="EF16" s="1">
-        <f t="shared" si="41"/>
-        <v>20.446999761273524</v>
+        <f t="shared" si="39"/>
+        <v>6.7704429971197158</v>
       </c>
       <c r="EG16" s="1">
-        <f t="shared" si="41"/>
-        <v>20.242529763660787</v>
+        <f t="shared" si="39"/>
+        <v>6.7027385671485185</v>
       </c>
       <c r="EH16" s="1">
-        <f t="shared" si="41"/>
-        <v>20.040104466024179</v>
+        <f t="shared" si="39"/>
+        <v>6.6357111814770331</v>
       </c>
       <c r="EI16" s="1">
-        <f t="shared" si="41"/>
-        <v>19.839703421363936</v>
+        <f t="shared" si="39"/>
+        <v>6.5693540696622623</v>
       </c>
       <c r="EJ16" s="1">
-        <f t="shared" si="41"/>
-        <v>19.641306387150298</v>
+        <f t="shared" si="39"/>
+        <v>6.5036605289656393</v>
       </c>
       <c r="EK16" s="1">
-        <f t="shared" si="41"/>
-        <v>19.444893323278794</v>
+        <f t="shared" si="39"/>
+        <v>6.4386239236759826</v>
       </c>
       <c r="EL16" s="1">
-        <f t="shared" si="41"/>
-        <v>19.250444390046006</v>
+        <f t="shared" si="39"/>
+        <v>6.3742376844392226</v>
       </c>
       <c r="EM16" s="1">
-        <f t="shared" si="41"/>
-        <v>19.057939946145545</v>
+        <f t="shared" si="39"/>
+        <v>6.31049530759483</v>
       </c>
       <c r="EN16" s="1">
-        <f t="shared" si="41"/>
-        <v>18.86736054668409</v>
+        <f t="shared" si="39"/>
+        <v>6.247390354518882</v>
       </c>
       <c r="EO16" s="1">
-        <f t="shared" si="41"/>
-        <v>18.678686941217247</v>
+        <f t="shared" si="39"/>
+        <v>6.1849164509736934</v>
       </c>
       <c r="EP16" s="1">
-        <f t="shared" si="41"/>
-        <v>18.491900071805073</v>
+        <f t="shared" si="39"/>
+        <v>6.1230672864639564</v>
       </c>
       <c r="EQ16" s="1">
-        <f t="shared" si="41"/>
-        <v>18.306981071087023</v>
+        <f t="shared" si="39"/>
+        <v>6.0618366135993167</v>
       </c>
       <c r="ER16" s="1">
-        <f t="shared" si="41"/>
-        <v>18.123911260376154</v>
+        <f t="shared" si="39"/>
+        <v>6.0012182474633233</v>
       </c>
       <c r="ES16" s="1">
-        <f t="shared" si="41"/>
-        <v>17.942672147772392</v>
+        <f t="shared" si="39"/>
+        <v>5.9412060649886902</v>
       </c>
       <c r="ET16" s="1">
-        <f t="shared" si="41"/>
-        <v>17.763245426294667</v>
+        <f t="shared" si="39"/>
+        <v>5.8817940043388033</v>
       </c>
       <c r="EU16" s="1">
-        <f t="shared" si="41"/>
-        <v>17.585612972031718</v>
+        <f t="shared" si="39"/>
+        <v>5.8229760642954149</v>
       </c>
       <c r="EV16" s="1">
-        <f t="shared" si="41"/>
-        <v>17.409756842311403</v>
+        <f t="shared" si="39"/>
+        <v>5.7647463036524611</v>
       </c>
       <c r="EW16" s="1">
-        <f t="shared" si="41"/>
-        <v>17.235659273888288</v>
+        <f t="shared" si="39"/>
+        <v>5.7070988406159362</v>
       </c>
       <c r="EX16" s="1">
-        <f t="shared" si="41"/>
-        <v>17.063302681149406</v>
+        <f t="shared" si="39"/>
+        <v>5.6500278522097771</v>
       </c>
       <c r="EY16" s="1">
-        <f t="shared" si="41"/>
-        <v>16.892669654337912</v>
+        <f t="shared" si="39"/>
+        <v>5.5935275736876795</v>
       </c>
       <c r="EZ16" s="1">
-        <f t="shared" si="41"/>
-        <v>16.723742957794531</v>
+        <f t="shared" si="39"/>
+        <v>5.5375922979508028</v>
       </c>
       <c r="FA16" s="1">
-        <f t="shared" si="41"/>
-        <v>16.556505528216586</v>
+        <f t="shared" si="39"/>
+        <v>5.4822163749712951</v>
       </c>
       <c r="FB16" s="1">
-        <f t="shared" si="41"/>
-        <v>16.390940472934421</v>
+        <f t="shared" si="39"/>
+        <v>5.4273942112215821</v>
+      </c>
+      <c r="FC16" s="1">
+        <f t="shared" si="39"/>
+        <v>5.373120269109366</v>
+      </c>
+      <c r="FD16" s="1">
+        <f t="shared" si="39"/>
+        <v>5.3193890664182719</v>
+      </c>
+      <c r="FE16" s="1">
+        <f t="shared" si="39"/>
+        <v>5.2661951757540892</v>
+      </c>
+      <c r="FF16" s="1">
+        <f t="shared" si="39"/>
+        <v>5.2135332239965484</v>
       </c>
     </row>
-    <row r="17" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>2</v>
       </c>
@@ -3621,74 +3800,78 @@
         <v>106.6</v>
       </c>
       <c r="AC17" s="4"/>
-      <c r="AE17" s="4">
+      <c r="AD17" s="4"/>
+      <c r="AE17" s="4"/>
+      <c r="AF17" s="4"/>
+      <c r="AG17" s="4"/>
+      <c r="AI17" s="4">
         <v>91.9</v>
       </c>
-      <c r="AF17" s="4">
+      <c r="AJ17" s="4">
         <v>91.9</v>
       </c>
-      <c r="AG17" s="4">
+      <c r="AK17" s="4">
         <v>91.9</v>
       </c>
-      <c r="AH17" s="4">
+      <c r="AL17" s="4">
         <v>92.2</v>
       </c>
-      <c r="AI17" s="4">
+      <c r="AM17" s="4">
         <v>92.2</v>
       </c>
-      <c r="AJ17" s="4">
+      <c r="AN17" s="4">
         <v>92.2</v>
       </c>
-      <c r="AK17" s="4">
-        <f t="shared" ref="AK17" si="42">104.9</f>
+      <c r="AO17" s="4">
+        <f t="shared" ref="AO17" si="40">104.9</f>
         <v>104.9</v>
       </c>
-      <c r="AL17" s="4">
-        <f t="shared" ref="AL17:AV17" si="43">106.6</f>
+      <c r="AP17" s="4">
+        <f t="shared" ref="AP17:AZ17" si="41">106.6</f>
         <v>106.6</v>
       </c>
-      <c r="AM17" s="4">
-        <f t="shared" si="43"/>
+      <c r="AQ17" s="4">
+        <f t="shared" si="41"/>
         <v>106.6</v>
       </c>
-      <c r="AN17" s="4">
-        <f t="shared" si="43"/>
+      <c r="AR17" s="4">
+        <f t="shared" si="41"/>
         <v>106.6</v>
       </c>
-      <c r="AO17" s="4">
-        <f t="shared" si="43"/>
+      <c r="AS17" s="4">
+        <f t="shared" si="41"/>
         <v>106.6</v>
       </c>
-      <c r="AP17" s="4">
-        <f t="shared" si="43"/>
+      <c r="AT17" s="4">
+        <f t="shared" si="41"/>
         <v>106.6</v>
       </c>
-      <c r="AQ17" s="4">
-        <f t="shared" si="43"/>
+      <c r="AU17" s="4">
+        <f t="shared" si="41"/>
         <v>106.6</v>
       </c>
-      <c r="AR17" s="4">
-        <f t="shared" si="43"/>
+      <c r="AV17" s="4">
+        <f t="shared" si="41"/>
         <v>106.6</v>
       </c>
-      <c r="AS17" s="4">
-        <f t="shared" si="43"/>
+      <c r="AW17" s="4">
+        <f t="shared" si="41"/>
         <v>106.6</v>
       </c>
-      <c r="AT17" s="4">
-        <f t="shared" si="43"/>
+      <c r="AX17" s="4">
+        <f t="shared" si="41"/>
         <v>106.6</v>
       </c>
-      <c r="AU17" s="4">
-        <f t="shared" si="43"/>
+      <c r="AY17" s="4">
+        <f t="shared" si="41"/>
         <v>106.6</v>
       </c>
-      <c r="AV17" s="4">
-        <f t="shared" si="43"/>
+      <c r="AZ17" s="4">
+        <f t="shared" si="41"/>
         <v>106.6</v>
       </c>
     </row>
-    <row r="18" spans="2:51" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:55" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>32</v>
       </c>
@@ -3701,7 +3884,7 @@
         <v>6.6376496191512521E-2</v>
       </c>
       <c r="E18" s="7">
-        <f t="shared" ref="E18" si="44">E16/E17</f>
+        <f t="shared" ref="E18" si="42">E16/E17</f>
         <v>1.1930585683297084E-2</v>
       </c>
       <c r="G18" s="7">
@@ -3713,43 +3896,43 @@
         <v>0.46789989118607134</v>
       </c>
       <c r="I18" s="7">
-        <f t="shared" ref="I18" si="45">I16/I17</f>
+        <f t="shared" ref="I18" si="43">I16/I17</f>
         <v>0.50650759219088881</v>
       </c>
       <c r="J18" s="7">
-        <f t="shared" ref="J18:Q18" si="46">J16/J17</f>
+        <f t="shared" ref="J18:Q18" si="44">J16/J17</f>
         <v>0.26361031518624595</v>
       </c>
       <c r="K18" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1.6236867239732732E-2</v>
       </c>
       <c r="L18" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0.23686723973256935</v>
       </c>
       <c r="M18" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>-4.8710601719197548E-2</v>
       </c>
       <c r="N18" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>-0.56733524355300891</v>
       </c>
       <c r="O18" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>-8.4049665711556684E-2</v>
       </c>
       <c r="P18" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0.11938872970391605</v>
       </c>
       <c r="Q18" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>-9.5510983763134969E-3</v>
       </c>
       <c r="R18" s="7">
-        <f t="shared" ref="R18" si="47">R16/R17</f>
+        <f t="shared" ref="R18" si="45">R16/R17</f>
         <v>1.0506208213944438E-2</v>
       </c>
       <c r="S18" s="7">
@@ -3765,7 +3948,7 @@
         <v>-0.11843361986628449</v>
       </c>
       <c r="V18" s="7">
-        <f t="shared" ref="V18" si="48">V16/V17</f>
+        <f t="shared" ref="V18" si="46">V16/V17</f>
         <v>-0.28175740210124145</v>
       </c>
       <c r="W18" s="7">
@@ -3777,138 +3960,190 @@
         <v>2.0972354623451362E-2</v>
       </c>
       <c r="Y18" s="7">
-        <f t="shared" ref="Y18:AB18" si="49">Y16/Y17</f>
+        <f t="shared" ref="Y18:AB18" si="47">Y16/Y17</f>
         <v>-9.829867674858192E-2</v>
       </c>
       <c r="Z18" s="7">
+        <f t="shared" si="47"/>
+        <v>-0.19754253308128514</v>
+      </c>
+      <c r="AA18" s="7">
+        <f t="shared" si="47"/>
+        <v>-9.9437148217635787E-2</v>
+      </c>
+      <c r="AB18" s="7">
+        <f t="shared" si="47"/>
+        <v>0.24296435272044989</v>
+      </c>
+      <c r="AC18" s="7"/>
+      <c r="AD18" s="7"/>
+      <c r="AE18" s="7"/>
+      <c r="AF18" s="7"/>
+      <c r="AG18" s="7"/>
+      <c r="AI18" s="7">
+        <f>AI16/AI17</f>
+        <v>-0.14907508161044572</v>
+      </c>
+      <c r="AJ18" s="7">
+        <f>AJ16/AJ17</f>
+        <v>-9.0315560391729388E-2</v>
+      </c>
+      <c r="AK18" s="7">
+        <f>AK16/AK17</f>
+        <v>1.1240478781284005</v>
+      </c>
+      <c r="AL18" s="7">
+        <f>AL16/AL17</f>
+        <v>1.093275488069414</v>
+      </c>
+      <c r="AM18" s="7">
+        <f t="shared" ref="AM18:AV18" si="48">AM16/AM17</f>
+        <v>-0.65943600867679131</v>
+      </c>
+      <c r="AN18" s="7">
+        <f t="shared" si="48"/>
+        <v>3.3622559652927764E-2</v>
+      </c>
+      <c r="AO18" s="7">
+        <f t="shared" si="48"/>
+        <v>-0.93422306959008428</v>
+      </c>
+      <c r="AP18" s="7">
+        <f t="shared" si="48"/>
+        <v>-0.15009380863039437</v>
+      </c>
+      <c r="AQ18" s="7">
+        <f t="shared" si="48"/>
+        <v>-0.45158518198874298</v>
+      </c>
+      <c r="AR18" s="7">
+        <f t="shared" si="48"/>
+        <v>-0.2879966093808633</v>
+      </c>
+      <c r="AS18" s="7">
+        <f t="shared" si="48"/>
+        <v>-0.10756172363977483</v>
+      </c>
+      <c r="AT18" s="7">
+        <f t="shared" si="48"/>
+        <v>-7.0022527292870548E-2</v>
+      </c>
+      <c r="AU18" s="7">
+        <f t="shared" si="48"/>
+        <v>-3.6328345339694E-2</v>
+      </c>
+      <c r="AV18" s="7">
+        <f t="shared" si="48"/>
+        <v>-1.6254115164210429E-3</v>
+      </c>
+      <c r="AW18" s="7">
+        <f t="shared" ref="AW18:AZ18" si="49">AW16/AW17</f>
+        <v>3.4109315553841585E-2</v>
+      </c>
+      <c r="AX18" s="7">
         <f t="shared" si="49"/>
-        <v>-0.19754253308128514</v>
-      </c>
-      <c r="AA18" s="7">
+        <v>7.0899352268635238E-2</v>
+      </c>
+      <c r="AY18" s="7">
         <f t="shared" si="49"/>
-        <v>-9.9437148217635787E-2</v>
-      </c>
-      <c r="AB18" s="7">
+        <v>0.10876869925438716</v>
+      </c>
+      <c r="AZ18" s="7">
         <f t="shared" si="49"/>
-        <v>3.7696660412758098E-2</v>
-      </c>
-      <c r="AC18" s="7"/>
-      <c r="AE18" s="7">
-        <f>AE16/AE17</f>
-        <v>-0.14907508161044572</v>
-      </c>
-      <c r="AF18" s="7">
-        <f>AF16/AF17</f>
-        <v>-9.0315560391729388E-2</v>
-      </c>
-      <c r="AG18" s="7">
-        <f>AG16/AG17</f>
-        <v>1.1240478781284005</v>
-      </c>
-      <c r="AH18" s="7">
-        <f>AH16/AH17</f>
-        <v>1.093275488069414</v>
-      </c>
-      <c r="AI18" s="7">
-        <f t="shared" ref="AI18:AR18" si="50">AI16/AI17</f>
-        <v>-0.65943600867679131</v>
-      </c>
-      <c r="AJ18" s="7">
-        <f t="shared" si="50"/>
-        <v>3.3622559652927764E-2</v>
-      </c>
-      <c r="AK18" s="7">
-        <f t="shared" si="50"/>
-        <v>-0.93422306959008428</v>
-      </c>
-      <c r="AL18" s="7">
-        <f t="shared" si="50"/>
-        <v>-0.35536150093808444</v>
-      </c>
-      <c r="AM18" s="7">
-        <f t="shared" si="50"/>
-        <v>-0.16288755636022476</v>
-      </c>
-      <c r="AN18" s="7">
-        <f t="shared" si="50"/>
-        <v>-7.214091024765433E-2</v>
-      </c>
-      <c r="AO18" s="7">
-        <f t="shared" si="50"/>
-        <v>0.15285102873636097</v>
-      </c>
-      <c r="AP18" s="7">
-        <f t="shared" si="50"/>
-        <v>0.22423020618015163</v>
-      </c>
-      <c r="AQ18" s="7">
-        <f t="shared" si="50"/>
-        <v>0.26155087300313434</v>
-      </c>
-      <c r="AR18" s="7">
-        <f t="shared" si="50"/>
-        <v>0.29992841921308289</v>
-      </c>
-      <c r="AS18" s="7">
-        <f t="shared" ref="AS18:AV18" si="51">AS16/AS17</f>
-        <v>0.33938655022094694</v>
-      </c>
-      <c r="AT18" s="7">
-        <f t="shared" si="51"/>
-        <v>0.37994945511900929</v>
-      </c>
-      <c r="AU18" s="7">
-        <f t="shared" si="51"/>
-        <v>0.42164181596708716</v>
-      </c>
-      <c r="AV18" s="7">
-        <f t="shared" si="51"/>
-        <v>0.46448881724609536</v>
+        <v>0.14774185074285986</v>
       </c>
     </row>
-    <row r="20" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>90</v>
       </c>
       <c r="X20" s="9">
-        <f t="shared" ref="X20:AA22" si="52">X3/T3-1</f>
+        <f t="shared" ref="X20:AB22" si="50">X3/T3-1</f>
         <v>0.23976608187134496</v>
       </c>
       <c r="Y20" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>4.6728971962616717E-2</v>
       </c>
       <c r="Z20" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>8.9171974522292974E-2</v>
       </c>
       <c r="AA20" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>0.1049019607843138</v>
       </c>
+      <c r="AB20" s="9">
+        <f t="shared" si="50"/>
+        <v>-2.77122641509433E-2</v>
+      </c>
+      <c r="AC20" s="9">
+        <f t="shared" ref="AC20:AC22" si="51">AC3/Y3-1</f>
+        <v>-1</v>
+      </c>
+      <c r="AD20" s="9">
+        <f t="shared" ref="AD20:AD22" si="52">AD3/Z3-1</f>
+        <v>-1</v>
+      </c>
+      <c r="AE20" s="9">
+        <f t="shared" ref="AE20:AE22" si="53">AE3/AA3-1</f>
+        <v>-1</v>
+      </c>
+      <c r="AF20" s="9">
+        <f t="shared" ref="AF20:AF22" si="54">AF3/AB3-1</f>
+        <v>-1</v>
+      </c>
+      <c r="AP20" s="9">
+        <f t="shared" ref="AK20:AV22" si="55">AP3/AO3-1</f>
+        <v>4.1032148900169485E-2</v>
+      </c>
     </row>
-    <row r="21" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>91</v>
       </c>
       <c r="X21" s="9">
+        <f t="shared" si="50"/>
+        <v>-0.12976827094474153</v>
+      </c>
+      <c r="Y21" s="9">
+        <f t="shared" si="50"/>
+        <v>0.11940946591402524</v>
+      </c>
+      <c r="Z21" s="9">
+        <f t="shared" si="50"/>
+        <v>0.30161579892280077</v>
+      </c>
+      <c r="AA21" s="9">
+        <f t="shared" si="50"/>
+        <v>0.15281899109792296</v>
+      </c>
+      <c r="AB21" s="9">
+        <f t="shared" si="50"/>
+        <v>0.11429741909053659</v>
+      </c>
+      <c r="AC21" s="9">
+        <f t="shared" si="51"/>
+        <v>-1</v>
+      </c>
+      <c r="AD21" s="9">
         <f t="shared" si="52"/>
-        <v>-0.12976827094474153</v>
-      </c>
-      <c r="Y21" s="9">
-        <f t="shared" si="52"/>
-        <v>0.11940946591402524</v>
-      </c>
-      <c r="Z21" s="9">
-        <f t="shared" si="52"/>
-        <v>0.30161579892280077</v>
-      </c>
-      <c r="AA21" s="9">
-        <f t="shared" si="52"/>
-        <v>0.15281899109792296</v>
+        <v>-1</v>
+      </c>
+      <c r="AE21" s="9">
+        <f t="shared" si="53"/>
+        <v>-1</v>
+      </c>
+      <c r="AF21" s="9">
+        <f t="shared" si="54"/>
+        <v>-1</v>
+      </c>
+      <c r="AP21" s="9">
+        <f t="shared" si="55"/>
+        <v>0.16202441626170438</v>
       </c>
     </row>
-    <row r="22" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>33</v>
       </c>
@@ -3928,149 +4163,165 @@
       </c>
       <c r="J22" s="9"/>
       <c r="K22" s="9">
-        <f t="shared" ref="K22:L22" si="53">K5/G5-1</f>
+        <f t="shared" ref="K22:L22" si="56">K5/G5-1</f>
         <v>-0.14438853642528982</v>
       </c>
       <c r="L22" s="9">
+        <f t="shared" si="56"/>
+        <v>-8.2149919108394642E-2</v>
+      </c>
+      <c r="M22" s="9">
+        <f t="shared" ref="M22" si="57">M5/I5-1</f>
+        <v>-0.28088401964488097</v>
+      </c>
+      <c r="N22" s="9">
+        <f t="shared" ref="N22" si="58">N5/J5-1</f>
+        <v>-0.39966166208500742</v>
+      </c>
+      <c r="O22" s="9">
+        <f t="shared" ref="O22" si="59">O5/K5-1</f>
+        <v>-0.20276144208642288</v>
+      </c>
+      <c r="P22" s="9">
+        <f t="shared" ref="P22" si="60">P5/L5-1</f>
+        <v>-0.21915393654524096</v>
+      </c>
+      <c r="Q22" s="9">
+        <f t="shared" ref="Q22" si="61">Q5/M5-1</f>
+        <v>-7.0133963750985018E-2</v>
+      </c>
+      <c r="R22" s="9">
+        <f t="shared" ref="R22" si="62">R5/N5-1</f>
+        <v>0.1461782317717506</v>
+      </c>
+      <c r="S22" s="9">
+        <f t="shared" ref="S22" si="63">S5/O5-1</f>
+        <v>0.16484926234765873</v>
+      </c>
+      <c r="T22" s="9">
+        <f t="shared" ref="T22" si="64">T5/P5-1</f>
+        <v>4.6651617757712538E-2</v>
+      </c>
+      <c r="U22" s="9">
+        <f t="shared" ref="U22" si="65">U5/Q5-1</f>
+        <v>-4.7175141242937868E-2</v>
+      </c>
+      <c r="V22" s="9">
+        <f t="shared" ref="V22" si="66">V5/R5-1</f>
+        <v>-0.19698832206515049</v>
+      </c>
+      <c r="W22" s="9">
+        <f t="shared" ref="W22" si="67">W5/S5-1</f>
+        <v>-0.1624449339207048</v>
+      </c>
+      <c r="X22" s="9">
+        <f t="shared" ref="X22" si="68">X5/T5-1</f>
+        <v>-8.8665228852145006E-3</v>
+      </c>
+      <c r="Y22" s="9">
+        <f t="shared" ref="Y22" si="69">Y5/U5-1</f>
+        <v>9.6353394604209885E-2</v>
+      </c>
+      <c r="Z22" s="9">
+        <f t="shared" ref="Z22" si="70">Z5/V5-1</f>
+        <v>0.22502870264064301</v>
+      </c>
+      <c r="AA22" s="9">
+        <f t="shared" si="50"/>
+        <v>0.13675213675213693</v>
+      </c>
+      <c r="AB22" s="9">
+        <f t="shared" ref="AB22" si="71">AB5/X5-1</f>
+        <v>5.6334622823984493E-2</v>
+      </c>
+      <c r="AC22" s="9">
+        <f t="shared" si="51"/>
+        <v>-1</v>
+      </c>
+      <c r="AD22" s="9">
+        <f t="shared" si="52"/>
+        <v>-1</v>
+      </c>
+      <c r="AE22" s="9">
         <f t="shared" si="53"/>
-        <v>-8.2149919108394642E-2</v>
-      </c>
-      <c r="M22" s="9">
-        <f t="shared" ref="M22" si="54">M5/I5-1</f>
-        <v>-0.28088401964488097</v>
-      </c>
-      <c r="N22" s="9">
-        <f t="shared" ref="N22" si="55">N5/J5-1</f>
-        <v>-0.39966166208500742</v>
-      </c>
-      <c r="O22" s="9">
-        <f t="shared" ref="O22" si="56">O5/K5-1</f>
-        <v>-0.20276144208642288</v>
-      </c>
-      <c r="P22" s="9">
-        <f t="shared" ref="P22" si="57">P5/L5-1</f>
-        <v>-0.21915393654524096</v>
-      </c>
-      <c r="Q22" s="9">
-        <f t="shared" ref="Q22" si="58">Q5/M5-1</f>
-        <v>-7.0133963750985018E-2</v>
-      </c>
-      <c r="R22" s="9">
-        <f t="shared" ref="R22" si="59">R5/N5-1</f>
-        <v>0.1461782317717506</v>
-      </c>
-      <c r="S22" s="9">
-        <f t="shared" ref="S22" si="60">S5/O5-1</f>
-        <v>0.16484926234765873</v>
-      </c>
-      <c r="T22" s="9">
-        <f t="shared" ref="T22" si="61">T5/P5-1</f>
-        <v>4.6651617757712538E-2</v>
-      </c>
-      <c r="U22" s="9">
-        <f t="shared" ref="U22" si="62">U5/Q5-1</f>
-        <v>-4.7175141242937868E-2</v>
-      </c>
-      <c r="V22" s="9">
-        <f t="shared" ref="V22" si="63">V5/R5-1</f>
-        <v>-0.19698832206515049</v>
-      </c>
-      <c r="W22" s="9">
-        <f t="shared" ref="W22" si="64">W5/S5-1</f>
-        <v>-0.1624449339207048</v>
-      </c>
-      <c r="X22" s="9">
-        <f t="shared" ref="X22" si="65">X5/T5-1</f>
-        <v>-8.8665228852145006E-3</v>
-      </c>
-      <c r="Y22" s="9">
-        <f t="shared" ref="Y22" si="66">Y5/U5-1</f>
-        <v>9.6353394604209885E-2</v>
-      </c>
-      <c r="Z22" s="9">
-        <f t="shared" ref="Z22" si="67">Z5/V5-1</f>
-        <v>0.22502870264064301</v>
-      </c>
-      <c r="AA22" s="9">
-        <f t="shared" si="52"/>
-        <v>0.13675213675213693</v>
-      </c>
-      <c r="AB22" s="9">
-        <f t="shared" ref="AB22" si="68">AB5/X5-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AC22" s="9"/>
-      <c r="AE22" s="9"/>
+        <v>-1</v>
+      </c>
       <c r="AF22" s="9">
-        <f>AF5/AE5-1</f>
+        <f t="shared" si="54"/>
+        <v>-1</v>
+      </c>
+      <c r="AG22" s="9"/>
+      <c r="AI22" s="9"/>
+      <c r="AJ22" s="9">
+        <f>AJ5/AI5-1</f>
         <v>0.17022184300341303</v>
       </c>
-      <c r="AG22" s="9">
-        <f t="shared" ref="AG22:AR22" si="69">AG5/AF5-1</f>
+      <c r="AK22" s="9">
+        <f t="shared" si="55"/>
         <v>0.55158585490339052</v>
       </c>
-      <c r="AH22" s="9">
-        <f t="shared" si="69"/>
+      <c r="AL22" s="9">
+        <f t="shared" si="55"/>
         <v>0.11842105263157898</v>
       </c>
-      <c r="AI22" s="9">
-        <f t="shared" si="69"/>
+      <c r="AM22" s="9">
+        <f t="shared" si="55"/>
         <v>-0.27778361344537816</v>
       </c>
-      <c r="AJ22" s="9">
-        <f t="shared" si="69"/>
+      <c r="AN22" s="9">
+        <f t="shared" si="55"/>
         <v>6.1668242309650179E-2</v>
       </c>
-      <c r="AK22" s="9">
-        <f t="shared" si="69"/>
+      <c r="AO22" s="9">
+        <f t="shared" si="55"/>
         <v>-9.8294403726282509E-2</v>
       </c>
-      <c r="AL22" s="9">
-        <f t="shared" si="69"/>
-        <v>0.10409905803707087</v>
-      </c>
-      <c r="AM22" s="9">
-        <f t="shared" si="69"/>
-        <v>6.0000000000000053E-2</v>
-      </c>
-      <c r="AN22" s="9">
-        <f t="shared" si="69"/>
+      <c r="AP22" s="9">
+        <f t="shared" si="55"/>
+        <v>0.11865694317836506</v>
+      </c>
+      <c r="AQ22" s="9">
+        <f t="shared" si="55"/>
+        <v>-4.6467472497623175E-2</v>
+      </c>
+      <c r="AR22" s="9">
+        <f t="shared" si="55"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AO22" s="9">
-        <f t="shared" si="69"/>
+      <c r="AS22" s="9">
+        <f t="shared" si="55"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AP22" s="9">
-        <f t="shared" si="69"/>
+      <c r="AT22" s="9">
+        <f t="shared" si="55"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AQ22" s="9">
-        <f t="shared" si="69"/>
+      <c r="AU22" s="9">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AR22" s="9">
-        <f t="shared" si="69"/>
+      <c r="AV22" s="9">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AS22" s="9">
-        <f t="shared" ref="AS22" si="70">AS5/AR5-1</f>
+      <c r="AW22" s="9">
+        <f t="shared" ref="AW22" si="72">AW5/AV5-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AT22" s="9">
-        <f t="shared" ref="AT22" si="71">AT5/AS5-1</f>
+      <c r="AX22" s="9">
+        <f t="shared" ref="AX22" si="73">AX5/AW5-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AU22" s="9">
-        <f t="shared" ref="AU22" si="72">AU5/AT5-1</f>
+      <c r="AY22" s="9">
+        <f t="shared" ref="AY22" si="74">AY5/AX5-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AV22" s="9">
-        <f t="shared" ref="AV22" si="73">AV5/AU5-1</f>
+      <c r="AZ22" s="9">
+        <f t="shared" ref="AZ22" si="75">AZ5/AY5-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
-    <row r="23" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>34</v>
       </c>
@@ -4083,7 +4334,7 @@
         <v>0.21586037966932026</v>
       </c>
       <c r="E23" s="9">
-        <f t="shared" ref="E23" si="74">E7/E5</f>
+        <f t="shared" ref="E23" si="76">E7/E5</f>
         <v>0.25478119935170174</v>
       </c>
       <c r="F23" s="9"/>
@@ -4096,160 +4347,176 @@
         <v>0.27646953082868947</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" ref="I23:L23" si="75">I7/I5</f>
+        <f t="shared" ref="I23:L23" si="77">I7/I5</f>
         <v>0.30279561768039281</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>0.27553393952209759</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>0.25901304014318588</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>0.23854289071680376</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" ref="M23:X23" si="76">M7/M5</f>
+        <f t="shared" ref="M23:X23" si="78">M7/M5</f>
         <v>0.238508011557657</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>0.12856639661852756</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>0.22963438101347025</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>0.24529721595184353</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>0.24124293785310727</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>0.25445605408727717</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>0.24614537444933915</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>0.24610591900311524</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>0.25704120960569232</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>0.24148488327592812</v>
       </c>
       <c r="W23" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>0.2291255752794214</v>
       </c>
       <c r="X23" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>0.2616054158607351</v>
       </c>
       <c r="Y23" s="9">
-        <f t="shared" ref="Y23:AB23" si="77">Y7/Y5</f>
+        <f t="shared" ref="Y23:AB23" si="79">Y7/Y5</f>
         <v>0.27690643591130348</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>0.26835363948766017</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>0.26923076923076927</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
+        <v>0.33096818493934532</v>
+      </c>
+      <c r="AC23" s="9" t="e">
+        <f t="shared" ref="AC23:AF23" si="80">AC7/AC5</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD23" s="9" t="e">
+        <f t="shared" si="80"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE23" s="9" t="e">
+        <f t="shared" si="80"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF23" s="9" t="e">
+        <f t="shared" si="80"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG23" s="9"/>
+      <c r="AI23" s="9">
+        <f t="shared" ref="AI23:AV23" si="81">AI7/AI5</f>
+        <v>0.20552474402730381</v>
+      </c>
+      <c r="AJ23" s="9">
+        <f t="shared" si="81"/>
+        <v>0.20442945679912511</v>
+      </c>
+      <c r="AK23" s="9">
+        <f t="shared" si="81"/>
+        <v>0.2734375</v>
+      </c>
+      <c r="AL23" s="9">
+        <f t="shared" si="81"/>
+        <v>0.26980042016806727</v>
+      </c>
+      <c r="AM23" s="9">
+        <f t="shared" si="81"/>
+        <v>0.21576612609991988</v>
+      </c>
+      <c r="AN23" s="9">
+        <f t="shared" si="81"/>
+        <v>0.24679772587163504</v>
+      </c>
+      <c r="AO23" s="9">
+        <f t="shared" si="81"/>
+        <v>0.24893649346703139</v>
+      </c>
+      <c r="AP23" s="9">
+        <f t="shared" si="81"/>
+        <v>0.28928425913350536</v>
+      </c>
+      <c r="AQ23" s="9">
+        <f t="shared" si="81"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="AC23" s="9"/>
-      <c r="AE23" s="9">
-        <f t="shared" ref="AE23:AR23" si="78">AE7/AE5</f>
-        <v>0.20552474402730381</v>
-      </c>
-      <c r="AF23" s="9">
-        <f t="shared" si="78"/>
-        <v>0.20442945679912511</v>
-      </c>
-      <c r="AG23" s="9">
-        <f t="shared" si="78"/>
-        <v>0.2734375</v>
-      </c>
-      <c r="AH23" s="9">
-        <f t="shared" si="78"/>
-        <v>0.26980042016806727</v>
-      </c>
-      <c r="AI23" s="9">
-        <f t="shared" si="78"/>
-        <v>0.21576612609991988</v>
-      </c>
-      <c r="AJ23" s="9">
-        <f t="shared" si="78"/>
-        <v>0.24679772587163504</v>
-      </c>
-      <c r="AK23" s="9">
-        <f t="shared" si="78"/>
-        <v>0.24893649346703139</v>
-      </c>
-      <c r="AL23" s="9">
-        <f t="shared" si="78"/>
-        <v>0.27408573889734411</v>
-      </c>
-      <c r="AM23" s="9">
-        <f t="shared" si="78"/>
-        <v>0.27</v>
-      </c>
-      <c r="AN23" s="9">
-        <f t="shared" si="78"/>
-        <v>0.27</v>
-      </c>
-      <c r="AO23" s="9">
-        <f t="shared" si="78"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="AP23" s="9">
-        <f t="shared" si="78"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="AQ23" s="9">
-        <f t="shared" si="78"/>
-        <v>0.28000000000000003</v>
-      </c>
       <c r="AR23" s="9">
-        <f t="shared" si="78"/>
-        <v>0.28000000000000003</v>
+        <f t="shared" si="81"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AS23" s="9">
-        <f t="shared" ref="AS23:AV23" si="79">AS7/AS5</f>
-        <v>0.28000000000000003</v>
+        <f t="shared" si="81"/>
+        <v>0.3</v>
       </c>
       <c r="AT23" s="9">
-        <f t="shared" si="79"/>
-        <v>0.28000000000000003</v>
+        <f t="shared" si="81"/>
+        <v>0.3</v>
       </c>
       <c r="AU23" s="9">
-        <f t="shared" si="79"/>
-        <v>0.28000000000000003</v>
+        <f t="shared" si="81"/>
+        <v>0.3</v>
       </c>
       <c r="AV23" s="9">
-        <f t="shared" si="79"/>
-        <v>0.28000000000000003</v>
+        <f t="shared" si="81"/>
+        <v>0.3</v>
+      </c>
+      <c r="AW23" s="9">
+        <f t="shared" ref="AW23:AZ23" si="82">AW7/AW5</f>
+        <v>0.3</v>
+      </c>
+      <c r="AX23" s="9">
+        <f t="shared" si="82"/>
+        <v>0.29999999999999993</v>
+      </c>
+      <c r="AY23" s="9">
+        <f t="shared" si="82"/>
+        <v>0.3</v>
+      </c>
+      <c r="AZ23" s="9">
+        <f t="shared" si="82"/>
+        <v>0.3</v>
       </c>
     </row>
-    <row r="24" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>35</v>
       </c>
@@ -4262,7 +4529,7 @@
         <v>4.378444580526638E-2</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" ref="E24" si="80">E10/E5</f>
+        <f t="shared" ref="E24" si="83">E10/E5</f>
         <v>4.3111831442463507E-2</v>
       </c>
       <c r="F24" s="9"/>
@@ -4275,166 +4542,182 @@
         <v>0.10587812331475817</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" ref="I24:L24" si="81">I10/I5</f>
+        <f t="shared" ref="I24:L24" si="84">I10/I5</f>
         <v>0.12693615413675849</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>7.3165574117149398E-2</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>2.7358731782152944E-2</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>4.9353701527614591E-2</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" ref="M24:X24" si="82">M10/M5</f>
+        <f t="shared" ref="M24:X24" si="85">M10/M5</f>
         <v>-6.3041765169424332E-3</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>-0.1933779499823883</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>-3.4958306606799175E-2</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>3.4110860295961908E-2</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>3.1073446327682954E-3</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>-8.6047940995698114E-3</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>-1.9273127753304631E-3</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>2.9235561945842301E-2</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>-2.9943670323154422E-2</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>-9.4527363184079533E-2</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>-6.870479947403027E-2</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>1.4264990328820231E-2</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" ref="Y24:AB24" si="83">Y10/Y5</f>
+        <f t="shared" ref="Y24:AB24" si="86">Y10/Y5</f>
         <v>-5.9491617090318208E-3</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>-5.2796001249609377E-2</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>-1.6194331983805599E-2</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="83"/>
-        <v>1.9593906199130588E-2</v>
-      </c>
-      <c r="AC24" s="9"/>
-      <c r="AE24" s="9">
-        <f t="shared" ref="AE24:AR24" si="84">AE10/AE5</f>
+        <f t="shared" si="86"/>
+        <v>6.1570153353169975E-2</v>
+      </c>
+      <c r="AC24" s="9" t="e">
+        <f t="shared" ref="AC24:AF24" si="87">AC10/AC5</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD24" s="9" t="e">
+        <f t="shared" si="87"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE24" s="9" t="e">
+        <f t="shared" si="87"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF24" s="9" t="e">
+        <f t="shared" si="87"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG24" s="9"/>
+      <c r="AI24" s="9">
+        <f t="shared" ref="AI24:AV24" si="88">AI10/AI5</f>
         <v>2.325085324232086E-2</v>
       </c>
-      <c r="AF24" s="9">
-        <f t="shared" si="84"/>
+      <c r="AJ24" s="9">
+        <f t="shared" si="88"/>
         <v>2.1691578563616538E-2</v>
       </c>
-      <c r="AG24" s="9">
-        <f t="shared" si="84"/>
+      <c r="AK24" s="9">
+        <f t="shared" si="88"/>
         <v>9.3045112781954889E-2</v>
       </c>
-      <c r="AH24" s="9">
-        <f t="shared" si="84"/>
+      <c r="AL24" s="9">
+        <f t="shared" si="88"/>
         <v>7.2321428571428564E-2</v>
       </c>
-      <c r="AI24" s="9">
-        <f t="shared" si="84"/>
+      <c r="AM24" s="9">
+        <f t="shared" si="88"/>
         <v>-3.9706203185223013E-2</v>
       </c>
-      <c r="AJ24" s="9">
-        <f t="shared" si="84"/>
+      <c r="AN24" s="9">
+        <f t="shared" si="88"/>
         <v>6.7127885471607238E-3</v>
       </c>
-      <c r="AK24" s="9">
-        <f t="shared" si="84"/>
+      <c r="AO24" s="9">
+        <f t="shared" si="88"/>
         <v>-3.7830446672743726E-2</v>
       </c>
-      <c r="AL24" s="9">
-        <f t="shared" si="84"/>
-        <v>-1.1362674379883111E-2</v>
-      </c>
-      <c r="AM24" s="9">
-        <f t="shared" si="84"/>
-        <v>-6.9198072575139356E-3</v>
-      </c>
-      <c r="AN24" s="9">
-        <f t="shared" si="84"/>
-        <v>9.9218723555789617E-4</v>
-      </c>
-      <c r="AO24" s="9">
-        <f t="shared" si="84"/>
-        <v>1.8752027988378359E-2</v>
-      </c>
       <c r="AP24" s="9">
-        <f t="shared" si="84"/>
-        <v>2.3824804143943827E-2</v>
+        <f t="shared" si="88"/>
+        <v>1.4939562678255877E-3</v>
       </c>
       <c r="AQ24" s="9">
-        <f t="shared" si="84"/>
-        <v>2.6336325671944383E-2</v>
+        <f t="shared" si="88"/>
+        <v>-3.5429306381269531E-2</v>
       </c>
       <c r="AR24" s="9">
-        <f t="shared" si="84"/>
-        <v>2.8823224439866499E-2</v>
+        <f t="shared" si="88"/>
+        <v>-1.8943084302655653E-2</v>
       </c>
       <c r="AS24" s="9">
-        <f t="shared" ref="AS24:AV24" si="85">AS10/AS5</f>
-        <v>3.1285741847318783E-2</v>
+        <f t="shared" si="88"/>
+        <v>-2.5330194982844337E-3</v>
       </c>
       <c r="AT24" s="9">
-        <f t="shared" si="85"/>
-        <v>3.3724116927247069E-2</v>
+        <f t="shared" si="88"/>
+        <v>8.6394201252588954E-4</v>
       </c>
       <c r="AU24" s="9">
-        <f t="shared" si="85"/>
-        <v>3.6138586369136805E-2</v>
+        <f t="shared" si="88"/>
+        <v>3.7966484633834936E-3</v>
       </c>
       <c r="AV24" s="9">
-        <f t="shared" si="85"/>
-        <v>3.8529384541988392E-2</v>
-      </c>
-      <c r="AX24" t="s">
+        <f t="shared" si="88"/>
+        <v>6.7006028902130838E-3</v>
+      </c>
+      <c r="AW24" s="9">
+        <f t="shared" ref="AW24:AZ24" si="89">AW10/AW5</f>
+        <v>9.5760871756031488E-3</v>
+      </c>
+      <c r="AX24" s="9">
+        <f t="shared" si="89"/>
+        <v>1.2423380438587381E-2</v>
+      </c>
+      <c r="AY24" s="9">
+        <f t="shared" si="89"/>
+        <v>1.5242759061738517E-2</v>
+      </c>
+      <c r="AZ24" s="9">
+        <f t="shared" si="89"/>
+        <v>1.8034496717995951E-2</v>
+      </c>
+      <c r="BB24" t="s">
         <v>38</v>
       </c>
-      <c r="AY24" s="9">
+      <c r="BC24" s="9">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="25" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>36</v>
       </c>
@@ -4443,15 +4726,15 @@
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="9">
-        <f t="shared" ref="G25:I26" si="86">G8/C8-1</f>
+        <f t="shared" ref="G25:I26" si="90">G8/C8-1</f>
         <v>0.64070351758793964</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="90"/>
         <v>0.72553191489361679</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="90"/>
         <v>0.45065176908752336</v>
       </c>
       <c r="J25" s="9"/>
@@ -4464,147 +4747,163 @@
         <v>4.9321824907522238E-3</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" ref="M25:X25" si="87">M8/I8-1</f>
+        <f t="shared" ref="M25:X25" si="91">M8/I8-1</f>
         <v>-2.31065468549424E-2</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>-8.478802992518697E-2</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>-0.12089356110381067</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>-0.1595092024539877</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>-0.1130091984231274</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>-4.6321525885558712E-2</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>0.10612855007473843</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>7.7372262773722555E-2</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>0.18814814814814818</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>5.7142857142857828E-3</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>1.3513513513512265E-3</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>0.15582655826558267</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" ref="Y25:AB26" si="88">Y8/U8-1</f>
+        <f t="shared" ref="Y25:AB26" si="92">Y8/U8-1</f>
         <v>8.4788029925187081E-2</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="92"/>
         <v>0.21164772727272707</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="92"/>
         <v>0.10661268556005399</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="88"/>
-        <v>7.0000000000000062E-2</v>
-      </c>
-      <c r="AC25" s="9"/>
-      <c r="AE25" s="9"/>
+        <f t="shared" si="92"/>
+        <v>0.17702227432590867</v>
+      </c>
+      <c r="AC25" s="9">
+        <f t="shared" ref="AC25:AC26" si="93">AC8/Y8-1</f>
+        <v>-1</v>
+      </c>
+      <c r="AD25" s="9">
+        <f t="shared" ref="AD25:AD26" si="94">AD8/Z8-1</f>
+        <v>-1</v>
+      </c>
+      <c r="AE25" s="9">
+        <f t="shared" ref="AE25:AE26" si="95">AE8/AA8-1</f>
+        <v>-1</v>
+      </c>
       <c r="AF25" s="9">
-        <f t="shared" ref="AF25:AR25" si="89">AF8/AE8-1</f>
+        <f t="shared" ref="AF25:AF26" si="96">AF8/AB8-1</f>
+        <v>-1</v>
+      </c>
+      <c r="AG25" s="9"/>
+      <c r="AI25" s="9"/>
+      <c r="AJ25" s="9">
+        <f t="shared" ref="AJ25:AV25" si="97">AJ8/AI8-1</f>
         <v>0.17350611951043904</v>
       </c>
-      <c r="AG25" s="9">
-        <f t="shared" si="89"/>
+      <c r="AK25" s="9">
+        <f t="shared" si="97"/>
         <v>0.57668711656441718</v>
       </c>
-      <c r="AH25" s="9">
-        <f t="shared" si="89"/>
+      <c r="AL25" s="9">
+        <f t="shared" si="97"/>
         <v>0.22840466926070047</v>
       </c>
-      <c r="AI25" s="9">
-        <f t="shared" si="89"/>
+      <c r="AM25" s="9">
+        <f t="shared" si="97"/>
         <v>-9.7560975609756295E-2</v>
       </c>
-      <c r="AJ25" s="9">
-        <f t="shared" si="89"/>
+      <c r="AN25" s="9">
+        <f t="shared" si="97"/>
         <v>1.4040014040015425E-3</v>
       </c>
-      <c r="AK25" s="9">
-        <f t="shared" si="89"/>
+      <c r="AO25" s="9">
+        <f t="shared" si="97"/>
         <v>8.6575534525061393E-2</v>
       </c>
-      <c r="AL25" s="9">
-        <f t="shared" si="89"/>
-        <v>0.11474516129032275</v>
-      </c>
-      <c r="AM25" s="9">
-        <f t="shared" si="89"/>
+      <c r="AP25" s="9">
+        <f t="shared" si="97"/>
+        <v>0.14419354838709686</v>
+      </c>
+      <c r="AQ25" s="9">
+        <f t="shared" si="97"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AR25" s="9">
+        <f t="shared" si="97"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AN25" s="9">
-        <f t="shared" si="89"/>
+      <c r="AS25" s="9">
+        <f t="shared" si="97"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AO25" s="9">
-        <f t="shared" si="89"/>
+      <c r="AT25" s="9">
+        <f t="shared" si="97"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AU25" s="9">
+        <f t="shared" si="97"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AP25" s="9">
-        <f t="shared" si="89"/>
+      <c r="AV25" s="9">
+        <f t="shared" si="97"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AQ25" s="9">
-        <f t="shared" si="89"/>
+      <c r="AW25" s="9">
+        <f t="shared" ref="AW25:AZ26" si="98">AW8/AV8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AR25" s="9">
-        <f t="shared" si="89"/>
+      <c r="AX25" s="9">
+        <f t="shared" si="98"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AS25" s="9">
-        <f t="shared" ref="AS25:AV26" si="90">AS8/AR8-1</f>
+      <c r="AY25" s="9">
+        <f t="shared" si="98"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AT25" s="9">
-        <f t="shared" si="90"/>
+      <c r="AZ25" s="9">
+        <f t="shared" si="98"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AU25" s="9">
-        <f t="shared" si="90"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AV25" s="9">
-        <f t="shared" si="90"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AX25" t="s">
+      <c r="BB25" t="s">
         <v>39</v>
       </c>
-      <c r="AY25" s="9">
-        <v>0.1</v>
+      <c r="BC25" s="9">
+        <v>0.11</v>
       </c>
     </row>
-    <row r="26" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>37</v>
       </c>
@@ -4613,15 +4912,15 @@
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="G26" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="90"/>
         <v>0.35789473684210527</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="90"/>
         <v>0.50000000000000022</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="90"/>
         <v>0.31034482758620685</v>
       </c>
       <c r="J26" s="9"/>
@@ -4634,148 +4933,164 @@
         <v>9.4202898550724612E-2</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" ref="M26:X26" si="91">M9/I9-1</f>
+        <f t="shared" ref="M26:X26" si="99">M9/I9-1</f>
         <v>0.12500000000000022</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>0.16129032258064524</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>7.5862068965517171E-2</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>3.9735099337748325E-2</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>-1.7543859649122862E-2</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>-0.1333333333333333</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>3.2051282051282159E-2</v>
       </c>
       <c r="T26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>6.3694267515923553E-2</v>
       </c>
       <c r="U26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>-1.1904761904761862E-2</v>
       </c>
       <c r="V26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>0.11538461538461542</v>
       </c>
       <c r="W26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>2.4844720496894235E-2</v>
       </c>
       <c r="X26" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>1.7964071856287456E-2</v>
       </c>
       <c r="Y26" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="92"/>
         <v>6.024096385542177E-2</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="92"/>
         <v>5.7471264367816577E-3</v>
       </c>
       <c r="AA26" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="92"/>
         <v>1.2121212121211977E-2</v>
       </c>
       <c r="AB26" s="9">
-        <f t="shared" si="88"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AC26" s="9"/>
-      <c r="AE26" s="9"/>
+        <f t="shared" si="92"/>
+        <v>1.7647058823529349E-2</v>
+      </c>
+      <c r="AC26" s="9">
+        <f t="shared" si="93"/>
+        <v>-1</v>
+      </c>
+      <c r="AD26" s="9">
+        <f t="shared" si="94"/>
+        <v>-1</v>
+      </c>
+      <c r="AE26" s="9">
+        <f t="shared" si="95"/>
+        <v>-1</v>
+      </c>
       <c r="AF26" s="9">
-        <f t="shared" ref="AF26:AR26" si="92">AF9/AE9-1</f>
+        <f t="shared" si="96"/>
+        <v>-1</v>
+      </c>
+      <c r="AG26" s="9"/>
+      <c r="AI26" s="9"/>
+      <c r="AJ26" s="9">
+        <f t="shared" ref="AJ26:AV26" si="100">AJ9/AI9-1</f>
         <v>0.171875</v>
       </c>
-      <c r="AG26" s="9">
-        <f t="shared" si="92"/>
+      <c r="AK26" s="9">
+        <f t="shared" si="100"/>
         <v>0.33600000000000008</v>
       </c>
-      <c r="AH26" s="9">
-        <f t="shared" si="92"/>
+      <c r="AL26" s="9">
+        <f t="shared" si="100"/>
         <v>0.20359281437125754</v>
       </c>
-      <c r="AI26" s="9">
-        <f t="shared" si="92"/>
+      <c r="AM26" s="9">
+        <f t="shared" si="100"/>
         <v>0.1011608623548923</v>
       </c>
-      <c r="AJ26" s="9">
-        <f t="shared" si="92"/>
+      <c r="AN26" s="9">
+        <f t="shared" si="100"/>
         <v>-1.8072289156626509E-2</v>
       </c>
-      <c r="AK26" s="9">
-        <f t="shared" si="92"/>
+      <c r="AO26" s="9">
+        <f t="shared" si="100"/>
         <v>3.5276073619631809E-2</v>
       </c>
-      <c r="AL26" s="9">
-        <f t="shared" si="92"/>
-        <v>2.6814814814814847E-2</v>
-      </c>
-      <c r="AM26" s="9">
-        <f t="shared" si="92"/>
+      <c r="AP26" s="9">
+        <f t="shared" si="100"/>
+        <v>2.370370370370356E-2</v>
+      </c>
+      <c r="AQ26" s="9">
+        <f t="shared" si="100"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AN26" s="9">
-        <f t="shared" si="92"/>
+      <c r="AR26" s="9">
+        <f t="shared" si="100"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AO26" s="9">
-        <f t="shared" si="92"/>
+      <c r="AS26" s="9">
+        <f t="shared" si="100"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AP26" s="9">
-        <f t="shared" si="92"/>
+      <c r="AT26" s="9">
+        <f t="shared" si="100"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AQ26" s="9">
-        <f t="shared" si="92"/>
+      <c r="AU26" s="9">
+        <f t="shared" si="100"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AR26" s="9">
-        <f t="shared" si="92"/>
+      <c r="AV26" s="9">
+        <f t="shared" si="100"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AS26" s="9">
-        <f t="shared" si="90"/>
+      <c r="AW26" s="9">
+        <f t="shared" si="98"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AT26" s="9">
-        <f t="shared" si="90"/>
+      <c r="AX26" s="9">
+        <f t="shared" si="98"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AU26" s="9">
-        <f t="shared" si="90"/>
+      <c r="AY26" s="9">
+        <f t="shared" si="98"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AV26" s="9">
-        <f t="shared" si="90"/>
+      <c r="AZ26" s="9">
+        <f t="shared" si="98"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AX26" t="s">
+      <c r="BB26" t="s">
         <v>40</v>
       </c>
-      <c r="AY26" s="4">
-        <f>NPV(AY25,AL16:FB16)</f>
-        <v>228.47772862366949</v>
+      <c r="BC26" s="4">
+        <f>NPV(BC25,AQ16:FF16)</f>
+        <v>-23.107437064803573</v>
       </c>
     </row>
-    <row r="27" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>30</v>
       </c>
@@ -4788,7 +5103,7 @@
         <v>-7.0175438596491224E-2</v>
       </c>
       <c r="E27" s="9">
-        <f t="shared" ref="E27" si="93">E14/E13</f>
+        <f t="shared" ref="E27" si="101">E14/E13</f>
         <v>0.71052631578947534</v>
       </c>
       <c r="F27" s="9"/>
@@ -4801,167 +5116,183 @@
         <v>0.16827852998065776</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" ref="I27:L27" si="94">I14/I13</f>
+        <f t="shared" ref="I27:L27" si="102">I14/I13</f>
         <v>0.22036727879799684</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="102"/>
         <v>7.6923076923077038E-2</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="102"/>
         <v>0.19047619047618894</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="102"/>
         <v>-0.10222222222222217</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" ref="M27:X27" si="95">M14/M13</f>
+        <f t="shared" ref="M27:X27" si="103">M14/M13</f>
         <v>0.238095238095239</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="103"/>
         <v>7.4999999999999956E-2</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="103"/>
         <v>0.51260504201680734</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="103"/>
         <v>0.16470588235294095</v>
       </c>
       <c r="Q27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="103"/>
         <v>0.27272727272726982</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="103"/>
         <v>0.35937499999999906</v>
       </c>
       <c r="S27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="103"/>
         <v>3.3333333333333069E-2</v>
       </c>
       <c r="T27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="103"/>
         <v>7.4074074074074139E-2</v>
       </c>
       <c r="U27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="103"/>
         <v>0.14173228346456707</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="103"/>
         <v>0.14598540145985411</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="103"/>
         <v>-1.1020408163265303</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="103"/>
         <v>0.16129032258064266</v>
       </c>
       <c r="Y27" s="9">
-        <f t="shared" ref="Y27:AB27" si="96">Y14/Y13</f>
+        <f t="shared" ref="Y27:AB27" si="104">Y14/Y13</f>
         <v>-0.25609756097561076</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="104"/>
         <v>1.9323671497584575E-2</v>
       </c>
       <c r="AA27" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="104"/>
         <v>-0.25301204819277184</v>
       </c>
       <c r="AB27" s="9">
-        <f t="shared" si="96"/>
-        <v>0.2</v>
-      </c>
-      <c r="AC27" s="9"/>
-      <c r="AE27" s="9">
-        <f t="shared" ref="AE27:AR27" si="97">AE14/AE13</f>
+        <f t="shared" si="104"/>
+        <v>-3.968253968253975E-2</v>
+      </c>
+      <c r="AC27" s="9" t="e">
+        <f t="shared" ref="AC27:AF27" si="105">AC14/AC13</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD27" s="9" t="e">
+        <f t="shared" si="105"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE27" s="9" t="e">
+        <f t="shared" si="105"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF27" s="9" t="e">
+        <f t="shared" si="105"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG27" s="9"/>
+      <c r="AI27" s="9">
+        <f t="shared" ref="AI27:AV27" si="106">AI14/AI13</f>
         <v>-0.28037383177570191</v>
       </c>
-      <c r="AF27" s="9">
-        <f t="shared" si="97"/>
+      <c r="AJ27" s="9">
+        <f t="shared" si="106"/>
         <v>0.37593984962406207</v>
       </c>
-      <c r="AG27" s="9">
-        <f t="shared" si="97"/>
+      <c r="AK27" s="9">
+        <f t="shared" si="106"/>
         <v>0.15397215397215397</v>
       </c>
-      <c r="AH27" s="9">
-        <f t="shared" si="97"/>
+      <c r="AL27" s="9">
+        <f t="shared" si="106"/>
         <v>0.11888111888111891</v>
       </c>
-      <c r="AI27" s="9">
-        <f t="shared" si="97"/>
+      <c r="AM27" s="9">
+        <f t="shared" si="106"/>
         <v>0.1556603773584902</v>
       </c>
-      <c r="AJ27" s="9">
-        <f t="shared" si="97"/>
+      <c r="AN27" s="9">
+        <f t="shared" si="106"/>
         <v>0.68571428571427406</v>
       </c>
-      <c r="AK27" s="9">
-        <f t="shared" si="97"/>
+      <c r="AO27" s="9">
+        <f t="shared" si="106"/>
         <v>-0.35284552845528544</v>
       </c>
-      <c r="AL27" s="9">
-        <f t="shared" si="97"/>
-        <v>-0.14931870421407747</v>
-      </c>
-      <c r="AM27" s="9">
-        <f t="shared" si="97"/>
+      <c r="AP27" s="9">
+        <f t="shared" si="106"/>
+        <v>-0.23333333333333259</v>
+      </c>
+      <c r="AQ27" s="9">
+        <f t="shared" si="106"/>
         <v>0.19</v>
       </c>
-      <c r="AN27" s="9">
-        <f t="shared" si="97"/>
+      <c r="AR27" s="9">
+        <f t="shared" si="106"/>
         <v>0.19</v>
       </c>
-      <c r="AO27" s="9">
-        <f t="shared" si="97"/>
+      <c r="AS27" s="9">
+        <f t="shared" si="106"/>
         <v>0.19</v>
       </c>
-      <c r="AP27" s="9">
-        <f t="shared" si="97"/>
+      <c r="AT27" s="9">
+        <f t="shared" si="106"/>
         <v>0.19</v>
       </c>
-      <c r="AQ27" s="9">
-        <f t="shared" si="97"/>
+      <c r="AU27" s="9">
+        <f t="shared" si="106"/>
         <v>0.19</v>
       </c>
-      <c r="AR27" s="9">
-        <f t="shared" si="97"/>
+      <c r="AV27" s="9">
+        <f t="shared" si="106"/>
         <v>0.19</v>
       </c>
-      <c r="AS27" s="9">
-        <f t="shared" ref="AS27:AV27" si="98">AS14/AS13</f>
+      <c r="AW27" s="9">
+        <f t="shared" ref="AW27:AZ27" si="107">AW14/AW13</f>
         <v>0.19</v>
       </c>
-      <c r="AT27" s="9">
-        <f t="shared" si="98"/>
+      <c r="AX27" s="9">
+        <f t="shared" si="107"/>
         <v>0.19</v>
       </c>
-      <c r="AU27" s="9">
-        <f t="shared" si="98"/>
+      <c r="AY27" s="9">
+        <f t="shared" si="107"/>
         <v>0.19</v>
       </c>
-      <c r="AV27" s="9">
-        <f t="shared" si="98"/>
+      <c r="AZ27" s="9">
+        <f t="shared" si="107"/>
         <v>0.19</v>
       </c>
-      <c r="AX27" t="s">
+      <c r="BB27" t="s">
         <v>41</v>
       </c>
-      <c r="AY27" s="4">
+      <c r="BC27" s="4">
         <f>Main!D8</f>
-        <v>-56.899999999999977</v>
+        <v>-22.700000000000003</v>
       </c>
     </row>
-    <row r="28" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>47</v>
       </c>
@@ -4970,193 +5301,209 @@
         <v>5.625879043600515E-3</v>
       </c>
       <c r="D28" s="9">
-        <f t="shared" ref="D28:L28" si="99">D16/D5</f>
+        <f t="shared" ref="D28:L28" si="108">D16/D5</f>
         <v>1.8677281077770978E-2</v>
       </c>
       <c r="E28" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="108"/>
         <v>3.5656401944894368E-3</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="108"/>
         <v>7.9413695033909507E-2</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="108"/>
         <v>7.7296422793456693E-2</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="108"/>
         <v>8.8213071401586601E-2</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="108"/>
         <v>5.83632903362232E-2</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="108"/>
         <v>4.3467143952953639E-3</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="108"/>
         <v>4.8570309439874677E-2</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" ref="M28:X28" si="100">M16/M5</f>
+        <f t="shared" ref="M28:X28" si="109">M16/M5</f>
         <v>-1.3396375098502715E-2</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="109"/>
         <v>-0.20922860162028897</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="109"/>
         <v>-2.8223220012828686E-2</v>
       </c>
       <c r="P28" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="109"/>
         <v>3.1351893654376753E-2</v>
       </c>
       <c r="Q28" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="109"/>
         <v>-2.8248587570622119E-3</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="109"/>
         <v>3.3804548248309247E-3</v>
       </c>
       <c r="S28" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="109"/>
         <v>-8.535242290748965E-3</v>
       </c>
       <c r="T28" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="109"/>
         <v>1.4617780972921142E-2</v>
       </c>
       <c r="U28" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="109"/>
         <v>-3.6762525941298502E-2</v>
       </c>
       <c r="V28" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="109"/>
         <v>-0.11289705319556058</v>
       </c>
       <c r="W28" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="109"/>
         <v>-0.1916502301117686</v>
       </c>
       <c r="X28" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="109"/>
         <v>5.3191489361703289E-3</v>
       </c>
       <c r="Y28" s="9">
-        <f t="shared" ref="Y28:AB28" si="101">Y16/Y5</f>
+        <f t="shared" ref="Y28:AB28" si="110">Y16/Y5</f>
         <v>-2.8123309897241662E-2</v>
       </c>
       <c r="Z28" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="110"/>
         <v>-6.5292096219931164E-2</v>
       </c>
       <c r="AA28" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="110"/>
         <v>-3.0653556969346369E-2</v>
       </c>
       <c r="AB28" s="9">
-        <f t="shared" si="101"/>
-        <v>9.6196257923665002E-3</v>
-      </c>
-      <c r="AC28" s="9"/>
-      <c r="AE28" s="9">
-        <f t="shared" ref="AE28:AR28" si="102">AE16/AE5</f>
+        <f t="shared" si="110"/>
+        <v>5.9281300068665499E-2</v>
+      </c>
+      <c r="AC28" s="9" t="e">
+        <f t="shared" ref="AC28:AF28" si="111">AC16/AC5</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD28" s="9" t="e">
+        <f t="shared" si="111"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE28" s="9" t="e">
+        <f t="shared" si="111"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF28" s="9" t="e">
+        <f t="shared" si="111"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG28" s="9"/>
+      <c r="AI28" s="9">
+        <f t="shared" ref="AI28:AV28" si="112">AI16/AI5</f>
         <v>-1.4611774744027264E-2</v>
       </c>
-      <c r="AF28" s="9">
-        <f t="shared" si="102"/>
+      <c r="AJ28" s="9">
+        <f t="shared" si="112"/>
         <v>-7.5647101713451799E-3</v>
       </c>
-      <c r="AG28" s="9">
-        <f t="shared" si="102"/>
+      <c r="AK28" s="9">
+        <f t="shared" si="112"/>
         <v>6.0679041353383464E-2</v>
       </c>
-      <c r="AH28" s="9">
-        <f t="shared" si="102"/>
+      <c r="AL28" s="9">
+        <f t="shared" si="112"/>
         <v>5.2941176470588228E-2</v>
       </c>
-      <c r="AI28" s="9">
-        <f t="shared" si="102"/>
+      <c r="AM28" s="9">
+        <f t="shared" si="112"/>
         <v>-4.4214966184277629E-2</v>
       </c>
-      <c r="AJ28" s="9">
-        <f t="shared" si="102"/>
+      <c r="AN28" s="9">
+        <f t="shared" si="112"/>
         <v>2.1234331118569353E-3</v>
       </c>
-      <c r="AK28" s="9">
-        <f t="shared" si="102"/>
+      <c r="AO28" s="9">
+        <f t="shared" si="112"/>
         <v>-7.4445457307809049E-2</v>
       </c>
-      <c r="AL28" s="9">
-        <f t="shared" si="102"/>
-        <v>-2.6063435885721693E-2</v>
-      </c>
-      <c r="AM28" s="9">
-        <f t="shared" si="102"/>
-        <v>-1.1270503922857696E-2</v>
-      </c>
-      <c r="AN28" s="9">
-        <f t="shared" si="102"/>
-        <v>-4.7538748588167243E-3</v>
-      </c>
-      <c r="AO28" s="9">
-        <f t="shared" si="102"/>
-        <v>9.6850340982718754E-3</v>
-      </c>
       <c r="AP28" s="9">
-        <f t="shared" si="102"/>
-        <v>1.3793982784279905E-2</v>
+        <f t="shared" si="112"/>
+        <v>-1.0865136493277224E-2</v>
       </c>
       <c r="AQ28" s="9">
-        <f t="shared" si="102"/>
-        <v>1.5774353373212174E-2</v>
+        <f t="shared" si="112"/>
+        <v>-3.4282823186903032E-2</v>
       </c>
       <c r="AR28" s="9">
-        <f t="shared" si="102"/>
-        <v>1.773425048874808E-2</v>
+        <f t="shared" si="112"/>
+        <v>-2.0822600731452937E-2</v>
       </c>
       <c r="AS28" s="9">
-        <f t="shared" ref="AS28:AV28" si="103">AS16/AS5</f>
-        <v>1.9673864477926156E-2</v>
+        <f t="shared" si="112"/>
+        <v>-7.4777684086978066E-3</v>
       </c>
       <c r="AT28" s="9">
-        <f t="shared" si="103"/>
-        <v>2.1593383719938637E-2</v>
+        <f t="shared" si="112"/>
+        <v>-4.7262295849414453E-3</v>
       </c>
       <c r="AU28" s="9">
-        <f t="shared" si="103"/>
-        <v>2.3492994644426855E-2</v>
+        <f t="shared" si="112"/>
+        <v>-2.403933659894701E-3</v>
       </c>
       <c r="AV28" s="9">
-        <f t="shared" si="103"/>
-        <v>2.5372881749587874E-2</v>
-      </c>
-      <c r="AX28" t="s">
+        <f t="shared" si="112"/>
+        <v>-1.0544840666504022E-4</v>
+      </c>
+      <c r="AW28" s="9">
+        <f t="shared" ref="AW28:AZ28" si="113">AW16/AW5</f>
+        <v>2.1694493865819157E-3</v>
+      </c>
+      <c r="AX28" s="9">
+        <f t="shared" si="113"/>
+        <v>4.4209806430730979E-3</v>
+      </c>
+      <c r="AY28" s="9">
+        <f t="shared" si="113"/>
+        <v>6.6493640188825505E-3</v>
+      </c>
+      <c r="AZ28" s="9">
+        <f t="shared" si="113"/>
+        <v>8.8548159241655256E-3</v>
+      </c>
+      <c r="BB28" t="s">
         <v>42</v>
       </c>
-      <c r="AY28" s="4">
-        <f>AY26+AY27</f>
-        <v>171.57772862366951</v>
+      <c r="BC28" s="4">
+        <f>BC26+BC27</f>
+        <v>-45.80743706480358</v>
       </c>
     </row>
-    <row r="29" spans="2:51" x14ac:dyDescent="0.3">
-      <c r="AX29" t="s">
+    <row r="29" spans="2:55" x14ac:dyDescent="0.3">
+      <c r="BB29" t="s">
         <v>43</v>
       </c>
-      <c r="AY29" s="5">
-        <f>AY28/AR17</f>
-        <v>1.6095471728299204</v>
+      <c r="BC29" s="5">
+        <f>BC28/AV17</f>
+        <v>-0.42971329329084035</v>
       </c>
     </row>
-    <row r="30" spans="2:51" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:55" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B30" s="11" t="s">
         <v>85</v>
       </c>
@@ -5164,153 +5511,157 @@
         <f>1221.9</f>
         <v>1221.9000000000001</v>
       </c>
-      <c r="AX30" t="s">
+      <c r="BB30" t="s">
         <v>44</v>
       </c>
-      <c r="AY30" s="5">
+      <c r="BC30" s="5">
         <f>Main!D3</f>
-        <v>5.04</v>
+        <v>6.79</v>
       </c>
     </row>
-    <row r="31" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>86</v>
       </c>
       <c r="AA31" s="13">
         <f>Main!D9/Model!AA30</f>
-        <v>0.48626237826336027</v>
-      </c>
-      <c r="AX31" s="1" t="s">
+        <v>0.61094524920206228</v>
+      </c>
+      <c r="BB31" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AY31" s="10">
-        <f>AY29/AY30-1</f>
-        <v>-0.68064540221628556</v>
+      <c r="BC31" s="10">
+        <f>BC29/BC30-1</f>
+        <v>-1.0632861993064566</v>
       </c>
     </row>
-    <row r="32" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>87</v>
       </c>
       <c r="AA32" s="9">
         <f>AA30/Main!D9-1</f>
-        <v>1.0565029183861698</v>
-      </c>
-      <c r="AX32" t="s">
+        <v>0.63680788304037184</v>
+      </c>
+      <c r="BB32" t="s">
         <v>46</v>
       </c>
-      <c r="AY32" s="6" t="s">
+      <c r="BC32" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="2:51" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:55" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>67</v>
       </c>
       <c r="T34" s="8">
-        <f t="shared" ref="T34:AB34" si="104">T16</f>
+        <f t="shared" ref="T34:AB34" si="114">T16</f>
         <v>6.0999999999999925</v>
       </c>
       <c r="U34" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>-12.399999999999986</v>
       </c>
       <c r="V34" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>-29.499999999999982</v>
       </c>
       <c r="W34" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>-58.300000000000004</v>
       </c>
       <c r="X34" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>2.2000000000000481</v>
       </c>
       <c r="Y34" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>-10.399999999999967</v>
       </c>
       <c r="Z34" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>-20.899999999999967</v>
       </c>
       <c r="AA34" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>-10.599999999999975</v>
       </c>
       <c r="AB34" s="8">
-        <f t="shared" si="104"/>
-        <v>4.0184640000000131</v>
-      </c>
-      <c r="AG34" s="8">
-        <f t="shared" ref="AG34:AV34" si="105">AG16</f>
+        <f t="shared" si="114"/>
+        <v>25.899999999999956</v>
+      </c>
+      <c r="AC34" s="8"/>
+      <c r="AD34" s="8"/>
+      <c r="AE34" s="8"/>
+      <c r="AF34" s="8"/>
+      <c r="AK34" s="8">
+        <f t="shared" ref="AK34:AZ34" si="115">AK16</f>
         <v>103.30000000000001</v>
       </c>
-      <c r="AH34" s="8">
-        <f t="shared" si="105"/>
+      <c r="AL34" s="8">
+        <f t="shared" si="115"/>
         <v>100.79999999999998</v>
       </c>
-      <c r="AI34" s="8">
-        <f t="shared" si="105"/>
+      <c r="AM34" s="8">
+        <f t="shared" si="115"/>
         <v>-60.800000000000161</v>
       </c>
-      <c r="AJ34" s="8">
-        <f t="shared" si="105"/>
+      <c r="AN34" s="8">
+        <f t="shared" si="115"/>
         <v>3.0999999999999397</v>
       </c>
-      <c r="AK34" s="8">
-        <f t="shared" si="105"/>
+      <c r="AO34" s="8">
+        <f t="shared" si="115"/>
         <v>-97.999999999999844</v>
       </c>
-      <c r="AL34" s="8">
-        <f t="shared" si="105"/>
-        <v>-37.881535999999798</v>
-      </c>
-      <c r="AM34" s="8">
-        <f t="shared" si="105"/>
-        <v>-17.363813507999957</v>
-      </c>
-      <c r="AN34" s="8">
-        <f t="shared" si="105"/>
-        <v>-7.6902210323999505</v>
-      </c>
-      <c r="AO34" s="8">
-        <f t="shared" si="105"/>
-        <v>16.29391966329608</v>
-      </c>
       <c r="AP34" s="8">
-        <f t="shared" si="105"/>
-        <v>23.902939978804163</v>
+        <f t="shared" si="115"/>
+        <v>-16.000000000000039</v>
       </c>
       <c r="AQ34" s="8">
-        <f t="shared" si="105"/>
-        <v>27.881323062134122</v>
+        <f t="shared" si="115"/>
+        <v>-48.138980400000001</v>
       </c>
       <c r="AR34" s="8">
-        <f t="shared" si="105"/>
-        <v>31.972369488114634</v>
+        <f t="shared" si="115"/>
+        <v>-30.700438560000023</v>
       </c>
       <c r="AS34" s="8">
-        <f t="shared" si="105"/>
-        <v>36.178606253552942</v>
+        <f t="shared" si="115"/>
+        <v>-11.466079739999996</v>
       </c>
       <c r="AT34" s="8">
-        <f t="shared" si="105"/>
-        <v>40.502611915686387</v>
+        <f t="shared" si="115"/>
+        <v>-7.4644014094200006</v>
       </c>
       <c r="AU34" s="8">
-        <f t="shared" si="105"/>
-        <v>44.94701758209149</v>
+        <f t="shared" si="115"/>
+        <v>-3.8726016132113799</v>
       </c>
       <c r="AV34" s="8">
-        <f t="shared" si="105"/>
-        <v>49.514507918433765</v>
-      </c>
-      <c r="AX34"/>
-      <c r="AY34"/>
+        <f t="shared" si="115"/>
+        <v>-0.17326886765048316</v>
+      </c>
+      <c r="AW34" s="8">
+        <f t="shared" si="115"/>
+        <v>3.6360530380395124</v>
+      </c>
+      <c r="AX34" s="8">
+        <f t="shared" si="115"/>
+        <v>7.5578709518365166</v>
+      </c>
+      <c r="AY34" s="8">
+        <f t="shared" si="115"/>
+        <v>11.59474334051767</v>
+      </c>
+      <c r="AZ34" s="8">
+        <f t="shared" si="115"/>
+        <v>15.749281289188861</v>
+      </c>
+      <c r="BB34"/>
+      <c r="BC34"/>
     </row>
-    <row r="35" spans="2:51" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:55" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>68</v>
       </c>
@@ -5340,71 +5691,75 @@
       </c>
       <c r="AB35" s="8">
         <f>AB34</f>
-        <v>4.0184640000000131</v>
-      </c>
-      <c r="AG35" s="8">
+        <v>25.899999999999956</v>
+      </c>
+      <c r="AC35" s="8"/>
+      <c r="AD35" s="8"/>
+      <c r="AE35" s="8"/>
+      <c r="AF35" s="8"/>
+      <c r="AK35" s="8">
         <v>103.2</v>
       </c>
-      <c r="AH35" s="8">
+      <c r="AL35" s="8">
         <v>101</v>
       </c>
-      <c r="AI35" s="8">
+      <c r="AM35" s="8">
         <v>-53.9</v>
       </c>
-      <c r="AJ35" s="8">
+      <c r="AN35" s="8">
         <v>-1</v>
       </c>
-      <c r="AK35" s="8">
+      <c r="AO35" s="8">
         <v>-83.4</v>
       </c>
-      <c r="AL35" s="8">
-        <f>AL34*0.9</f>
-        <v>-34.093382399999818</v>
-      </c>
-      <c r="AM35" s="8">
-        <f t="shared" ref="AM35:AV35" si="106">AM34*0.9</f>
-        <v>-15.627432157199962</v>
-      </c>
-      <c r="AN35" s="8">
-        <f t="shared" si="106"/>
-        <v>-6.9211989291599556</v>
-      </c>
-      <c r="AO35" s="8">
-        <f t="shared" si="106"/>
-        <v>14.664527696966472</v>
-      </c>
       <c r="AP35" s="8">
-        <f t="shared" si="106"/>
-        <v>21.512645980923747</v>
+        <f>AP34*0.9</f>
+        <v>-14.400000000000036</v>
       </c>
       <c r="AQ35" s="8">
-        <f t="shared" si="106"/>
-        <v>25.093190755920709</v>
+        <f t="shared" ref="AQ35:AZ35" si="116">AQ34*0.9</f>
+        <v>-43.325082360000003</v>
       </c>
       <c r="AR35" s="8">
-        <f t="shared" si="106"/>
-        <v>28.775132539303172</v>
+        <f t="shared" si="116"/>
+        <v>-27.630394704000022</v>
       </c>
       <c r="AS35" s="8">
-        <f t="shared" si="106"/>
-        <v>32.560745628197651</v>
+        <f t="shared" si="116"/>
+        <v>-10.319471765999996</v>
       </c>
       <c r="AT35" s="8">
-        <f t="shared" si="106"/>
-        <v>36.45235072411775</v>
+        <f t="shared" si="116"/>
+        <v>-6.7179612684780006</v>
       </c>
       <c r="AU35" s="8">
-        <f t="shared" si="106"/>
-        <v>40.452315823882344</v>
+        <f t="shared" si="116"/>
+        <v>-3.4853414518902421</v>
       </c>
       <c r="AV35" s="8">
-        <f t="shared" si="106"/>
-        <v>44.563057126590387</v>
-      </c>
-      <c r="AX35"/>
-      <c r="AY35"/>
+        <f t="shared" si="116"/>
+        <v>-0.15594198088543484</v>
+      </c>
+      <c r="AW35" s="8">
+        <f t="shared" si="116"/>
+        <v>3.2724477342355613</v>
+      </c>
+      <c r="AX35" s="8">
+        <f t="shared" si="116"/>
+        <v>6.8020838566528647</v>
+      </c>
+      <c r="AY35" s="8">
+        <f t="shared" si="116"/>
+        <v>10.435269006465903</v>
+      </c>
+      <c r="AZ35" s="8">
+        <f t="shared" si="116"/>
+        <v>14.174353160269975</v>
+      </c>
+      <c r="BB35"/>
+      <c r="BC35"/>
     </row>
-    <row r="36" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>69</v>
       </c>
@@ -5433,69 +5788,73 @@
         <v>5.2</v>
       </c>
       <c r="AB36" s="4">
-        <v>5.2</v>
-      </c>
-      <c r="AG36" s="4">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="AC36" s="4"/>
+      <c r="AD36" s="4"/>
+      <c r="AE36" s="4"/>
+      <c r="AF36" s="4"/>
+      <c r="AK36" s="4">
         <v>5.8</v>
       </c>
-      <c r="AH36" s="4">
+      <c r="AL36" s="4">
         <v>17.2</v>
       </c>
-      <c r="AI36" s="4">
+      <c r="AM36" s="4">
         <v>22.2</v>
       </c>
-      <c r="AJ36" s="4">
+      <c r="AN36" s="4">
         <v>30.9</v>
       </c>
-      <c r="AK36" s="4">
+      <c r="AO36" s="4">
         <v>30.6</v>
       </c>
-      <c r="AL36" s="4">
+      <c r="AP36" s="4">
         <f>SUM(Y36:AB36)</f>
-        <v>29</v>
-      </c>
-      <c r="AM36" s="4">
-        <f>AL36*0.85</f>
-        <v>24.65</v>
-      </c>
-      <c r="AN36" s="4">
-        <f>AM36*1.01</f>
-        <v>24.8965</v>
-      </c>
-      <c r="AO36" s="4">
-        <f t="shared" ref="AO36:AP36" si="107">AN36*0.95</f>
-        <v>23.651674999999997</v>
-      </c>
-      <c r="AP36" s="4">
-        <f t="shared" si="107"/>
-        <v>22.469091249999998</v>
+        <v>33.1</v>
       </c>
       <c r="AQ36" s="4">
         <f>AP36*1.01</f>
-        <v>22.6937821625</v>
+        <v>33.431000000000004</v>
       </c>
       <c r="AR36" s="4">
-        <f t="shared" ref="AR36:AV36" si="108">AQ36*1.01</f>
-        <v>22.920719984125</v>
+        <f t="shared" ref="AR36:AZ36" si="117">AQ36*1.01</f>
+        <v>33.765310000000007</v>
       </c>
       <c r="AS36" s="4">
-        <f t="shared" si="108"/>
-        <v>23.149927183966252</v>
+        <f t="shared" si="117"/>
+        <v>34.102963100000004</v>
       </c>
       <c r="AT36" s="4">
-        <f t="shared" si="108"/>
-        <v>23.381426455805915</v>
+        <f t="shared" si="117"/>
+        <v>34.443992731000002</v>
       </c>
       <c r="AU36" s="4">
-        <f t="shared" si="108"/>
-        <v>23.615240720363975</v>
+        <f t="shared" si="117"/>
+        <v>34.788432658310001</v>
       </c>
       <c r="AV36" s="4">
-        <f t="shared" si="108"/>
-        <v>23.851393127567615</v>
+        <f t="shared" si="117"/>
+        <v>35.136316984893099</v>
+      </c>
+      <c r="AW36" s="4">
+        <f t="shared" si="117"/>
+        <v>35.48768015474203</v>
+      </c>
+      <c r="AX36" s="4">
+        <f t="shared" si="117"/>
+        <v>35.842556956289449</v>
+      </c>
+      <c r="AY36" s="4">
+        <f t="shared" si="117"/>
+        <v>36.200982525852346</v>
+      </c>
+      <c r="AZ36" s="4">
+        <f t="shared" si="117"/>
+        <v>36.562992351110871</v>
       </c>
     </row>
-    <row r="37" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>70</v>
       </c>
@@ -5524,69 +5883,73 @@
         <v>3.5</v>
       </c>
       <c r="AB37" s="4">
-        <v>3.5</v>
-      </c>
-      <c r="AG37" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="AC37" s="4"/>
+      <c r="AD37" s="4"/>
+      <c r="AE37" s="4"/>
+      <c r="AF37" s="4"/>
+      <c r="AK37" s="4">
         <v>9.3000000000000007</v>
       </c>
-      <c r="AH37" s="4">
+      <c r="AL37" s="4">
         <v>10.3</v>
       </c>
-      <c r="AI37" s="4">
+      <c r="AM37" s="4">
         <v>10.7</v>
       </c>
-      <c r="AJ37" s="4">
+      <c r="AN37" s="4">
         <v>12.2</v>
       </c>
-      <c r="AK37" s="4">
+      <c r="AO37" s="4">
         <v>13.4</v>
       </c>
-      <c r="AL37" s="4">
-        <f t="shared" ref="AL37:AL47" si="109">SUM(Y37:AB37)</f>
-        <v>13.8</v>
-      </c>
-      <c r="AM37" s="4">
-        <f>AL37*1.03</f>
-        <v>14.214</v>
-      </c>
-      <c r="AN37" s="4">
-        <f t="shared" ref="AN37:AV37" si="110">AM37*1.03</f>
-        <v>14.640420000000001</v>
-      </c>
-      <c r="AO37" s="4">
-        <f t="shared" si="110"/>
-        <v>15.079632600000002</v>
-      </c>
       <c r="AP37" s="4">
-        <f t="shared" si="110"/>
-        <v>15.532021578000002</v>
+        <f t="shared" ref="AP37:AP47" si="118">SUM(Y37:AB37)</f>
+        <v>14.100000000000001</v>
       </c>
       <c r="AQ37" s="4">
-        <f t="shared" si="110"/>
-        <v>15.997982225340003</v>
+        <f>AP37*1.03</f>
+        <v>14.523000000000001</v>
       </c>
       <c r="AR37" s="4">
-        <f t="shared" si="110"/>
-        <v>16.477921692100203</v>
+        <f t="shared" ref="AR37:AZ37" si="119">AQ37*1.03</f>
+        <v>14.958690000000002</v>
       </c>
       <c r="AS37" s="4">
-        <f t="shared" si="110"/>
-        <v>16.972259342863211</v>
+        <f t="shared" si="119"/>
+        <v>15.407450700000004</v>
       </c>
       <c r="AT37" s="4">
-        <f t="shared" si="110"/>
-        <v>17.481427123149107</v>
+        <f t="shared" si="119"/>
+        <v>15.869674221000004</v>
       </c>
       <c r="AU37" s="4">
-        <f t="shared" si="110"/>
-        <v>18.005869936843581</v>
+        <f t="shared" si="119"/>
+        <v>16.345764447630003</v>
       </c>
       <c r="AV37" s="4">
-        <f t="shared" si="110"/>
-        <v>18.54604603494889</v>
+        <f t="shared" si="119"/>
+        <v>16.836137381058904</v>
+      </c>
+      <c r="AW37" s="4">
+        <f t="shared" si="119"/>
+        <v>17.341221502490672</v>
+      </c>
+      <c r="AX37" s="4">
+        <f t="shared" si="119"/>
+        <v>17.861458147565394</v>
+      </c>
+      <c r="AY37" s="4">
+        <f t="shared" si="119"/>
+        <v>18.397301891992356</v>
+      </c>
+      <c r="AZ37" s="4">
+        <f t="shared" si="119"/>
+        <v>18.949220948752128</v>
       </c>
     </row>
-    <row r="38" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>71</v>
       </c>
@@ -5615,69 +5978,73 @@
         <v>10.1</v>
       </c>
       <c r="AB38" s="4">
-        <v>10.1</v>
-      </c>
-      <c r="AG38" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="AC38" s="4"/>
+      <c r="AD38" s="4"/>
+      <c r="AE38" s="4"/>
+      <c r="AF38" s="4"/>
+      <c r="AK38" s="4">
         <v>33.9</v>
       </c>
-      <c r="AH38" s="4">
+      <c r="AL38" s="4">
         <v>34.799999999999997</v>
       </c>
-      <c r="AI38" s="4">
+      <c r="AM38" s="4">
         <v>42.8</v>
       </c>
-      <c r="AJ38" s="4">
+      <c r="AN38" s="4">
         <v>38.5</v>
       </c>
-      <c r="AK38" s="4">
+      <c r="AO38" s="4">
         <v>38.4</v>
       </c>
-      <c r="AL38" s="4">
-        <f t="shared" si="109"/>
-        <v>39.900000000000006</v>
-      </c>
-      <c r="AM38" s="4">
-        <f>AL38*1.01</f>
-        <v>40.299000000000007</v>
-      </c>
-      <c r="AN38" s="4">
-        <f t="shared" ref="AN38:AV38" si="111">AM38*1.01</f>
-        <v>40.701990000000009</v>
-      </c>
-      <c r="AO38" s="4">
-        <f t="shared" si="111"/>
-        <v>41.109009900000011</v>
-      </c>
       <c r="AP38" s="4">
-        <f t="shared" si="111"/>
-        <v>41.52009999900001</v>
+        <f t="shared" si="118"/>
+        <v>40.300000000000004</v>
       </c>
       <c r="AQ38" s="4">
-        <f t="shared" si="111"/>
-        <v>41.935300998990009</v>
+        <f>AP38*1.01</f>
+        <v>40.703000000000003</v>
       </c>
       <c r="AR38" s="4">
-        <f t="shared" si="111"/>
-        <v>42.354654008979907</v>
+        <f t="shared" ref="AR38:AZ38" si="120">AQ38*1.01</f>
+        <v>41.110030000000002</v>
       </c>
       <c r="AS38" s="4">
-        <f t="shared" si="111"/>
-        <v>42.778200549069709</v>
+        <f t="shared" si="120"/>
+        <v>41.521130300000003</v>
       </c>
       <c r="AT38" s="4">
-        <f t="shared" si="111"/>
-        <v>43.205982554560407</v>
+        <f t="shared" si="120"/>
+        <v>41.936341603000002</v>
       </c>
       <c r="AU38" s="4">
-        <f t="shared" si="111"/>
-        <v>43.638042380106015</v>
+        <f t="shared" si="120"/>
+        <v>42.355705019030005</v>
       </c>
       <c r="AV38" s="4">
-        <f t="shared" si="111"/>
-        <v>44.074422803907076</v>
+        <f t="shared" si="120"/>
+        <v>42.779262069220302</v>
+      </c>
+      <c r="AW38" s="4">
+        <f t="shared" si="120"/>
+        <v>43.207054689912503</v>
+      </c>
+      <c r="AX38" s="4">
+        <f t="shared" si="120"/>
+        <v>43.63912523681163</v>
+      </c>
+      <c r="AY38" s="4">
+        <f t="shared" si="120"/>
+        <v>44.075516489179748</v>
+      </c>
+      <c r="AZ38" s="4">
+        <f t="shared" si="120"/>
+        <v>44.516271654071545</v>
       </c>
     </row>
-    <row r="39" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>84</v>
       </c>
@@ -5708,27 +6075,31 @@
       <c r="AB39" s="4">
         <v>0</v>
       </c>
-      <c r="AG39" s="4"/>
-      <c r="AH39" s="4"/>
-      <c r="AI39" s="4"/>
-      <c r="AJ39" s="4"/>
+      <c r="AC39" s="4"/>
+      <c r="AD39" s="4"/>
+      <c r="AE39" s="4"/>
+      <c r="AF39" s="4"/>
       <c r="AK39" s="4"/>
-      <c r="AL39" s="4">
-        <f t="shared" si="109"/>
-        <v>1.4</v>
-      </c>
+      <c r="AL39" s="4"/>
       <c r="AM39" s="4"/>
       <c r="AN39" s="4"/>
       <c r="AO39" s="4"/>
-      <c r="AP39" s="4"/>
+      <c r="AP39" s="4">
+        <f t="shared" si="118"/>
+        <v>1.4</v>
+      </c>
       <c r="AQ39" s="4"/>
       <c r="AR39" s="4"/>
       <c r="AS39" s="4"/>
       <c r="AT39" s="4"/>
       <c r="AU39" s="4"/>
       <c r="AV39" s="4"/>
+      <c r="AW39" s="4"/>
+      <c r="AX39" s="4"/>
+      <c r="AY39" s="4"/>
+      <c r="AZ39" s="4"/>
     </row>
-    <row r="40" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>82</v>
       </c>
@@ -5759,39 +6130,31 @@
       <c r="AB40" s="4">
         <v>0</v>
       </c>
-      <c r="AG40" s="4">
+      <c r="AC40" s="4"/>
+      <c r="AD40" s="4"/>
+      <c r="AE40" s="4"/>
+      <c r="AF40" s="4"/>
+      <c r="AK40" s="4">
         <f>2.6+4.1</f>
         <v>6.6999999999999993</v>
       </c>
-      <c r="AH40" s="4">
+      <c r="AL40" s="4">
         <f>1.5+4.9</f>
         <v>6.4</v>
       </c>
-      <c r="AI40" s="4">
+      <c r="AM40" s="4">
         <v>0.4</v>
       </c>
-      <c r="AJ40" s="4">
-        <v>0</v>
-      </c>
-      <c r="AK40" s="4">
+      <c r="AN40" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO40" s="4">
         <v>-2.6</v>
       </c>
-      <c r="AL40" s="4">
-        <f t="shared" si="109"/>
+      <c r="AP40" s="4">
+        <f t="shared" si="118"/>
         <v>2.6</v>
       </c>
-      <c r="AM40" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN40" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO40" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP40" s="4">
-        <v>0</v>
-      </c>
       <c r="AQ40" s="4">
         <v>0</v>
       </c>
@@ -5810,8 +6173,20 @@
       <c r="AV40" s="4">
         <v>0</v>
       </c>
+      <c r="AW40" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX40" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY40" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ40" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>72</v>
       </c>
@@ -5840,38 +6215,30 @@
         <v>0.1</v>
       </c>
       <c r="AB41" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG41" s="4">
+        <v>-3.3</v>
+      </c>
+      <c r="AC41" s="4"/>
+      <c r="AD41" s="4"/>
+      <c r="AE41" s="4"/>
+      <c r="AF41" s="4"/>
+      <c r="AK41" s="4">
         <v>-7.5</v>
       </c>
-      <c r="AH41" s="4">
+      <c r="AL41" s="4">
         <v>-12</v>
       </c>
-      <c r="AI41" s="4">
+      <c r="AM41" s="4">
         <v>-21.7</v>
       </c>
-      <c r="AJ41" s="4">
+      <c r="AN41" s="4">
         <v>-6.3</v>
       </c>
-      <c r="AK41" s="4">
+      <c r="AO41" s="4">
         <v>11.4</v>
       </c>
-      <c r="AL41" s="4">
-        <f t="shared" si="109"/>
-        <v>-3.1999999999999997</v>
-      </c>
-      <c r="AM41" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN41" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO41" s="4">
-        <v>0</v>
-      </c>
       <c r="AP41" s="4">
-        <v>0</v>
+        <f t="shared" si="118"/>
+        <v>-6.5</v>
       </c>
       <c r="AQ41" s="4">
         <v>0</v>
@@ -5891,8 +6258,20 @@
       <c r="AV41" s="4">
         <v>0</v>
       </c>
+      <c r="AW41" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX41" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY41" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ41" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>73</v>
       </c>
@@ -5921,38 +6300,30 @@
         <v>0</v>
       </c>
       <c r="AB42" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG42" s="4">
+        <v>-0.7</v>
+      </c>
+      <c r="AC42" s="4"/>
+      <c r="AD42" s="4"/>
+      <c r="AE42" s="4"/>
+      <c r="AF42" s="4"/>
+      <c r="AK42" s="4">
         <v>2.6</v>
       </c>
-      <c r="AH42" s="4">
+      <c r="AL42" s="4">
         <v>3.3</v>
       </c>
-      <c r="AI42" s="4">
+      <c r="AM42" s="4">
         <v>4.5</v>
       </c>
-      <c r="AJ42" s="4">
+      <c r="AN42" s="4">
         <v>4.9000000000000004</v>
       </c>
-      <c r="AK42" s="4">
+      <c r="AO42" s="4">
         <v>5.7</v>
       </c>
-      <c r="AL42" s="4">
-        <f t="shared" si="109"/>
-        <v>3.6</v>
-      </c>
-      <c r="AM42" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN42" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO42" s="4">
-        <v>0</v>
-      </c>
       <c r="AP42" s="4">
-        <v>0</v>
+        <f t="shared" si="118"/>
+        <v>2.9000000000000004</v>
       </c>
       <c r="AQ42" s="4">
         <v>0</v>
@@ -5972,8 +6343,20 @@
       <c r="AV42" s="4">
         <v>0</v>
       </c>
+      <c r="AW42" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX42" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY42" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ42" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>74</v>
       </c>
@@ -6002,38 +6385,30 @@
         <v>-14</v>
       </c>
       <c r="AB43" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG43" s="4">
+        <v>-41.7</v>
+      </c>
+      <c r="AC43" s="4"/>
+      <c r="AD43" s="4"/>
+      <c r="AE43" s="4"/>
+      <c r="AF43" s="4"/>
+      <c r="AK43" s="4">
         <v>-91.5</v>
       </c>
-      <c r="AH43" s="4">
+      <c r="AL43" s="4">
         <v>0.4</v>
       </c>
-      <c r="AI43" s="4">
+      <c r="AM43" s="4">
         <v>55.8</v>
       </c>
-      <c r="AJ43" s="4">
+      <c r="AN43" s="4">
         <v>-17.7</v>
       </c>
-      <c r="AK43" s="4">
+      <c r="AO43" s="4">
         <v>32.299999999999997</v>
       </c>
-      <c r="AL43" s="4">
-        <f t="shared" si="109"/>
-        <v>24</v>
-      </c>
-      <c r="AM43" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN43" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO43" s="4">
-        <v>0</v>
-      </c>
       <c r="AP43" s="4">
-        <v>0</v>
+        <f t="shared" si="118"/>
+        <v>-17.700000000000003</v>
       </c>
       <c r="AQ43" s="4">
         <v>0</v>
@@ -6053,8 +6428,20 @@
       <c r="AV43" s="4">
         <v>0</v>
       </c>
+      <c r="AW43" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX43" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY43" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ43" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>75</v>
       </c>
@@ -6083,38 +6470,30 @@
         <v>-19.5</v>
       </c>
       <c r="AB44" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG44" s="4">
+        <v>11.6</v>
+      </c>
+      <c r="AC44" s="4"/>
+      <c r="AD44" s="4"/>
+      <c r="AE44" s="4"/>
+      <c r="AF44" s="4"/>
+      <c r="AK44" s="4">
         <v>-80.099999999999994</v>
       </c>
-      <c r="AH44" s="4">
+      <c r="AL44" s="4">
         <v>-71.3</v>
       </c>
-      <c r="AI44" s="4">
+      <c r="AM44" s="4">
         <v>111.3</v>
       </c>
-      <c r="AJ44" s="4">
+      <c r="AN44" s="4">
         <v>-39.5</v>
       </c>
-      <c r="AK44" s="4">
+      <c r="AO44" s="4">
         <v>18.3</v>
       </c>
-      <c r="AL44" s="4">
-        <f t="shared" si="109"/>
-        <v>-63.2</v>
-      </c>
-      <c r="AM44" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN44" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO44" s="4">
-        <v>0</v>
-      </c>
       <c r="AP44" s="4">
-        <v>0</v>
+        <f t="shared" si="118"/>
+        <v>-51.6</v>
       </c>
       <c r="AQ44" s="4">
         <v>0</v>
@@ -6134,10 +6513,22 @@
       <c r="AV44" s="4">
         <v>0</v>
       </c>
-      <c r="AX44" s="1"/>
-      <c r="AY44" s="1"/>
+      <c r="AW44" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX44" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY44" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ44" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB44" s="1"/>
+      <c r="BC44" s="1"/>
     </row>
-    <row r="45" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>76</v>
       </c>
@@ -6166,38 +6557,30 @@
         <v>0.7</v>
       </c>
       <c r="AB45" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG45" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="AC45" s="4"/>
+      <c r="AD45" s="4"/>
+      <c r="AE45" s="4"/>
+      <c r="AF45" s="4"/>
+      <c r="AK45" s="4">
         <v>-8</v>
       </c>
-      <c r="AH45" s="4">
+      <c r="AL45" s="4">
         <v>-13.2</v>
       </c>
-      <c r="AI45" s="4">
+      <c r="AM45" s="4">
         <v>1.3</v>
       </c>
-      <c r="AJ45" s="4">
+      <c r="AN45" s="4">
         <v>1.9</v>
       </c>
-      <c r="AK45" s="4">
+      <c r="AO45" s="4">
         <v>5.9</v>
       </c>
-      <c r="AL45" s="4">
-        <f t="shared" si="109"/>
-        <v>4.7</v>
-      </c>
-      <c r="AM45" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN45" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO45" s="4">
-        <v>0</v>
-      </c>
       <c r="AP45" s="4">
-        <v>0</v>
+        <f t="shared" si="118"/>
+        <v>9</v>
       </c>
       <c r="AQ45" s="4">
         <v>0</v>
@@ -6217,8 +6600,20 @@
       <c r="AV45" s="4">
         <v>0</v>
       </c>
+      <c r="AW45" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX45" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY45" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ45" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>77</v>
       </c>
@@ -6247,38 +6642,30 @@
         <v>-11.3</v>
       </c>
       <c r="AB46" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG46" s="4">
+        <v>-32.799999999999997</v>
+      </c>
+      <c r="AC46" s="4"/>
+      <c r="AD46" s="4"/>
+      <c r="AE46" s="4"/>
+      <c r="AF46" s="4"/>
+      <c r="AK46" s="4">
         <v>116.5</v>
       </c>
-      <c r="AH46" s="4">
+      <c r="AL46" s="4">
         <v>-63.7</v>
       </c>
-      <c r="AI46" s="4">
+      <c r="AM46" s="4">
         <v>-65.900000000000006</v>
       </c>
-      <c r="AJ46" s="4">
+      <c r="AN46" s="4">
         <v>62.2</v>
       </c>
-      <c r="AK46" s="4">
+      <c r="AO46" s="4">
         <v>-39.5</v>
       </c>
-      <c r="AL46" s="4">
-        <f t="shared" si="109"/>
-        <v>38.299999999999997</v>
-      </c>
-      <c r="AM46" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN46" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO46" s="4">
-        <v>0</v>
-      </c>
       <c r="AP46" s="4">
-        <v>0</v>
+        <f t="shared" si="118"/>
+        <v>5.5</v>
       </c>
       <c r="AQ46" s="4">
         <v>0</v>
@@ -6298,10 +6685,22 @@
       <c r="AV46" s="4">
         <v>0</v>
       </c>
-      <c r="AX46" s="1"/>
-      <c r="AY46" s="1"/>
+      <c r="AW46" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX46" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY46" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ46" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB46" s="1"/>
+      <c r="BC46" s="1"/>
     </row>
-    <row r="47" spans="2:51" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:55" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>78</v>
       </c>
@@ -6330,38 +6729,30 @@
         <v>-1.4</v>
       </c>
       <c r="AB47" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG47" s="4">
+        <v>51.3</v>
+      </c>
+      <c r="AC47" s="4"/>
+      <c r="AD47" s="4"/>
+      <c r="AE47" s="4"/>
+      <c r="AF47" s="4"/>
+      <c r="AK47" s="4">
         <v>77.900000000000006</v>
       </c>
-      <c r="AH47" s="4">
+      <c r="AL47" s="4">
         <v>7</v>
       </c>
-      <c r="AI47" s="4">
+      <c r="AM47" s="4">
         <v>-41</v>
       </c>
-      <c r="AJ47" s="4">
+      <c r="AN47" s="4">
         <v>3.8</v>
       </c>
-      <c r="AK47" s="4">
+      <c r="AO47" s="4">
         <v>5.3</v>
       </c>
-      <c r="AL47" s="4">
-        <f t="shared" si="109"/>
-        <v>-19.099999999999998</v>
-      </c>
-      <c r="AM47" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN47" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO47" s="4">
-        <v>0</v>
-      </c>
       <c r="AP47" s="4">
-        <v>0</v>
+        <f t="shared" si="118"/>
+        <v>32.200000000000003</v>
       </c>
       <c r="AQ47" s="4">
         <v>0</v>
@@ -6381,115 +6772,131 @@
       <c r="AV47" s="4">
         <v>0</v>
       </c>
+      <c r="AW47" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX47" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY47" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ47" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:51" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:55" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
         <v>79</v>
       </c>
       <c r="T48" s="8">
-        <f t="shared" ref="T48:AB48" si="112">T34+SUM(T36:T47)</f>
+        <f t="shared" ref="T48:AB48" si="121">T34+SUM(T36:T47)</f>
         <v>55.79999999999999</v>
       </c>
       <c r="U48" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="121"/>
         <v>-27.79999999999999</v>
       </c>
       <c r="V48" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="121"/>
         <v>-24.499999999999986</v>
       </c>
       <c r="W48" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="121"/>
         <v>18.299999999999976</v>
       </c>
       <c r="X48" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="121"/>
         <v>55.100000000000037</v>
       </c>
       <c r="Y48" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="121"/>
         <v>18.700000000000035</v>
       </c>
       <c r="Z48" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="121"/>
         <v>29.600000000000019</v>
       </c>
       <c r="AA48" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="121"/>
         <v>-37.199999999999974</v>
       </c>
       <c r="AB48" s="8">
-        <f t="shared" si="112"/>
-        <v>22.818464000000009</v>
-      </c>
-      <c r="AG48" s="8">
-        <f t="shared" ref="AG48:AM48" si="113">AG34+SUM(AG35:AG47)</f>
+        <f t="shared" si="121"/>
+        <v>38.199999999999953</v>
+      </c>
+      <c r="AC48" s="8"/>
+      <c r="AD48" s="8"/>
+      <c r="AE48" s="8"/>
+      <c r="AF48" s="8"/>
+      <c r="AK48" s="8">
+        <f t="shared" ref="AK48:AQ48" si="122">AK34+SUM(AK35:AK47)</f>
         <v>272.10000000000002</v>
       </c>
-      <c r="AH48" s="8">
-        <f t="shared" si="113"/>
+      <c r="AL48" s="8">
+        <f t="shared" si="122"/>
         <v>121.00000000000001</v>
       </c>
-      <c r="AI48" s="8">
-        <f t="shared" si="113"/>
+      <c r="AM48" s="8">
+        <f t="shared" si="122"/>
         <v>5.6999999999998394</v>
       </c>
-      <c r="AJ48" s="8">
-        <f t="shared" si="113"/>
+      <c r="AN48" s="8">
+        <f t="shared" si="122"/>
         <v>92.999999999999929</v>
       </c>
-      <c r="AK48" s="8">
-        <f t="shared" si="113"/>
+      <c r="AO48" s="8">
+        <f t="shared" si="122"/>
         <v>-62.199999999999847</v>
       </c>
-      <c r="AL48" s="8">
-        <f t="shared" si="113"/>
-        <v>-0.1749183999995978</v>
-      </c>
-      <c r="AM48" s="8">
-        <f t="shared" si="113"/>
-        <v>46.171754334800085</v>
-      </c>
-      <c r="AN48" s="8">
-        <f t="shared" ref="AN48:AV48" si="114">AN34+SUM(AN35:AN47)</f>
-        <v>65.627490038440115</v>
-      </c>
-      <c r="AO48" s="8">
-        <f t="shared" si="114"/>
-        <v>110.79876486026257</v>
-      </c>
       <c r="AP48" s="8">
-        <f t="shared" si="114"/>
-        <v>124.93679878672791</v>
+        <f t="shared" si="122"/>
+        <v>34.899999999999935</v>
       </c>
       <c r="AQ48" s="8">
-        <f t="shared" si="114"/>
-        <v>133.60157920488484</v>
+        <f t="shared" si="122"/>
+        <v>-2.8070627599999938</v>
       </c>
       <c r="AR48" s="8">
-        <f t="shared" si="114"/>
-        <v>142.5007977126229</v>
+        <f t="shared" ref="AR48:AZ48" si="123">AR34+SUM(AR35:AR47)</f>
+        <v>31.503196735999964</v>
       </c>
       <c r="AS48" s="8">
-        <f t="shared" si="114"/>
-        <v>151.63973895764977</v>
+        <f t="shared" si="123"/>
+        <v>69.245992594000015</v>
       </c>
       <c r="AT48" s="8">
-        <f t="shared" si="114"/>
-        <v>161.02379877331958</v>
+        <f t="shared" si="123"/>
+        <v>78.067645877102009</v>
       </c>
       <c r="AU48" s="8">
-        <f t="shared" si="114"/>
-        <v>170.65848644328742</v>
+        <f t="shared" si="123"/>
+        <v>86.131959059868393</v>
       </c>
       <c r="AV48" s="8">
-        <f t="shared" si="114"/>
-        <v>180.54942701144773</v>
-      </c>
-      <c r="AX48"/>
-      <c r="AY48"/>
+        <f t="shared" si="123"/>
+        <v>94.42250558663639</v>
+      </c>
+      <c r="AW48" s="8">
+        <f t="shared" si="123"/>
+        <v>102.94445711942026</v>
+      </c>
+      <c r="AX48" s="8">
+        <f t="shared" si="123"/>
+        <v>111.70309514915586</v>
+      </c>
+      <c r="AY48" s="8">
+        <f t="shared" si="123"/>
+        <v>120.70381325400803</v>
+      </c>
+      <c r="AZ48" s="8">
+        <f t="shared" si="123"/>
+        <v>129.9521194033934</v>
+      </c>
+      <c r="BB48"/>
+      <c r="BC48"/>
     </row>
-    <row r="49" spans="2:143" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:147" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>80</v>
       </c>
@@ -6518,612 +6925,620 @@
         <v>4.3</v>
       </c>
       <c r="AB49" s="4">
-        <v>4</v>
-      </c>
-      <c r="AG49" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="AC49" s="4"/>
+      <c r="AD49" s="4"/>
+      <c r="AE49" s="4"/>
+      <c r="AF49" s="4"/>
+      <c r="AK49" s="4">
         <v>9</v>
       </c>
-      <c r="AH49" s="4">
+      <c r="AL49" s="4">
         <v>11</v>
       </c>
-      <c r="AI49" s="4">
+      <c r="AM49" s="4">
         <v>12.8</v>
       </c>
-      <c r="AJ49" s="4">
+      <c r="AN49" s="4">
         <v>12.8</v>
       </c>
-      <c r="AK49" s="4">
+      <c r="AO49" s="4">
         <v>9.8000000000000007</v>
       </c>
-      <c r="AL49" s="4">
+      <c r="AP49" s="4">
         <f>SUM(Y49:AB49)</f>
-        <v>14.100000000000001</v>
-      </c>
-      <c r="AM49" s="4">
-        <f t="shared" ref="AM49" si="115">AL49*1.05</f>
-        <v>14.805000000000001</v>
-      </c>
-      <c r="AN49" s="4">
-        <f>AM49*1.04</f>
-        <v>15.397200000000002</v>
-      </c>
-      <c r="AO49" s="4">
-        <f>AN49*1.03</f>
-        <v>15.859116000000002</v>
-      </c>
-      <c r="AP49" s="4">
-        <f t="shared" ref="AP49:AV49" si="116">AO49*1.03</f>
-        <v>16.334889480000001</v>
+        <v>15.400000000000002</v>
       </c>
       <c r="AQ49" s="4">
-        <f t="shared" si="116"/>
-        <v>16.8249361644</v>
+        <f t="shared" ref="AQ49" si="124">AP49*1.05</f>
+        <v>16.170000000000002</v>
       </c>
       <c r="AR49" s="4">
-        <f t="shared" si="116"/>
-        <v>17.329684249332001</v>
+        <f>AQ49*1.04</f>
+        <v>16.816800000000001</v>
       </c>
       <c r="AS49" s="4">
-        <f t="shared" si="116"/>
-        <v>17.849574776811963</v>
+        <f>AR49*1.03</f>
+        <v>17.321304000000001</v>
       </c>
       <c r="AT49" s="4">
-        <f t="shared" si="116"/>
-        <v>18.385062020116322</v>
+        <f t="shared" ref="AT49:AZ49" si="125">AS49*1.03</f>
+        <v>17.840943120000002</v>
       </c>
       <c r="AU49" s="4">
-        <f t="shared" si="116"/>
-        <v>18.936613880719811</v>
+        <f t="shared" si="125"/>
+        <v>18.376171413600002</v>
       </c>
       <c r="AV49" s="4">
-        <f t="shared" si="116"/>
-        <v>19.504712297141406</v>
+        <f t="shared" si="125"/>
+        <v>18.927456556008003</v>
+      </c>
+      <c r="AW49" s="4">
+        <f t="shared" si="125"/>
+        <v>19.495280252688243</v>
+      </c>
+      <c r="AX49" s="4">
+        <f t="shared" si="125"/>
+        <v>20.08013866026889</v>
+      </c>
+      <c r="AY49" s="4">
+        <f t="shared" si="125"/>
+        <v>20.682542820076957</v>
+      </c>
+      <c r="AZ49" s="4">
+        <f t="shared" si="125"/>
+        <v>21.303019104679265</v>
       </c>
     </row>
-    <row r="50" spans="2:143" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:147" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
         <v>81</v>
       </c>
       <c r="T50" s="8">
-        <f t="shared" ref="T50:AB50" si="117">T48-T49</f>
+        <f t="shared" ref="T50:AB50" si="126">T48-T49</f>
         <v>53.79999999999999</v>
       </c>
       <c r="U50" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="126"/>
         <v>-30.29999999999999</v>
       </c>
       <c r="V50" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="126"/>
         <v>-26.999999999999986</v>
       </c>
       <c r="W50" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="126"/>
         <v>14.999999999999975</v>
       </c>
       <c r="X50" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="126"/>
         <v>53.600000000000037</v>
       </c>
       <c r="Y50" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="126"/>
         <v>15.600000000000035</v>
       </c>
       <c r="Z50" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="126"/>
         <v>26.90000000000002</v>
       </c>
       <c r="AA50" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="126"/>
         <v>-41.499999999999972</v>
       </c>
       <c r="AB50" s="8">
-        <f t="shared" si="117"/>
-        <v>18.818464000000009</v>
-      </c>
-      <c r="AG50" s="8">
-        <f t="shared" ref="AG50:AM50" si="118">AG48-AG49</f>
+        <f t="shared" si="126"/>
+        <v>32.899999999999956</v>
+      </c>
+      <c r="AC50" s="8"/>
+      <c r="AD50" s="8"/>
+      <c r="AE50" s="8"/>
+      <c r="AF50" s="8"/>
+      <c r="AK50" s="8">
+        <f t="shared" ref="AK50:AQ50" si="127">AK48-AK49</f>
         <v>263.10000000000002</v>
       </c>
-      <c r="AH50" s="8">
-        <f t="shared" si="118"/>
+      <c r="AL50" s="8">
+        <f t="shared" si="127"/>
         <v>110.00000000000001</v>
       </c>
-      <c r="AI50" s="8">
-        <f t="shared" si="118"/>
+      <c r="AM50" s="8">
+        <f t="shared" si="127"/>
         <v>-7.1000000000001613</v>
       </c>
-      <c r="AJ50" s="8">
-        <f t="shared" si="118"/>
+      <c r="AN50" s="8">
+        <f t="shared" si="127"/>
         <v>80.199999999999932</v>
       </c>
-      <c r="AK50" s="8">
-        <f t="shared" si="118"/>
+      <c r="AO50" s="8">
+        <f t="shared" si="127"/>
         <v>-71.999999999999844</v>
       </c>
-      <c r="AL50" s="8">
-        <f t="shared" si="118"/>
-        <v>-14.274918399999599</v>
-      </c>
-      <c r="AM50" s="8">
-        <f t="shared" si="118"/>
-        <v>31.366754334800085</v>
-      </c>
-      <c r="AN50" s="8">
-        <f t="shared" ref="AN50:AV50" si="119">AN48-AN49</f>
-        <v>50.230290038440117</v>
-      </c>
-      <c r="AO50" s="8">
-        <f t="shared" si="119"/>
-        <v>94.939648860262565</v>
-      </c>
       <c r="AP50" s="8">
-        <f t="shared" si="119"/>
-        <v>108.6019093067279</v>
+        <f t="shared" si="127"/>
+        <v>19.499999999999932</v>
       </c>
       <c r="AQ50" s="8">
-        <f t="shared" si="119"/>
-        <v>116.77664304048484</v>
+        <f t="shared" si="127"/>
+        <v>-18.977062759999995</v>
       </c>
       <c r="AR50" s="8">
-        <f t="shared" si="119"/>
-        <v>125.17111346329089</v>
+        <f t="shared" ref="AR50:AZ50" si="128">AR48-AR49</f>
+        <v>14.686396735999963</v>
       </c>
       <c r="AS50" s="8">
-        <f t="shared" si="119"/>
-        <v>133.79016418083779</v>
+        <f t="shared" si="128"/>
+        <v>51.924688594000017</v>
       </c>
       <c r="AT50" s="8">
-        <f t="shared" si="119"/>
-        <v>142.63873675320326</v>
+        <f t="shared" si="128"/>
+        <v>60.226702757102004</v>
       </c>
       <c r="AU50" s="8">
-        <f t="shared" si="119"/>
-        <v>151.7218725625676</v>
+        <f t="shared" si="128"/>
+        <v>67.755787646268388</v>
       </c>
       <c r="AV50" s="8">
-        <f t="shared" si="119"/>
-        <v>161.04471471430634</v>
-      </c>
-      <c r="AW50" s="1">
-        <f>AV50*(1+$AY$24)</f>
-        <v>159.43426756716326</v>
-      </c>
-      <c r="AX50" s="1">
-        <f t="shared" ref="AX50:DI50" si="120">AW50*(1+$AY$24)</f>
-        <v>157.83992489149162</v>
-      </c>
-      <c r="AY50" s="1">
-        <f t="shared" si="120"/>
-        <v>156.26152564257671</v>
-      </c>
-      <c r="AZ50" s="1">
-        <f t="shared" si="120"/>
-        <v>154.69891038615094</v>
+        <f t="shared" si="128"/>
+        <v>75.495049030628394</v>
+      </c>
+      <c r="AW50" s="8">
+        <f t="shared" si="128"/>
+        <v>83.449176866732017</v>
+      </c>
+      <c r="AX50" s="8">
+        <f t="shared" si="128"/>
+        <v>91.62295648888697</v>
+      </c>
+      <c r="AY50" s="8">
+        <f t="shared" si="128"/>
+        <v>100.02127043393106</v>
+      </c>
+      <c r="AZ50" s="8">
+        <f t="shared" si="128"/>
+        <v>108.64910029871413</v>
       </c>
       <c r="BA50" s="1">
-        <f t="shared" si="120"/>
-        <v>153.15192128228944</v>
+        <f>AZ50*(1+$BC$24)</f>
+        <v>107.56260929572699</v>
       </c>
       <c r="BB50" s="1">
-        <f t="shared" si="120"/>
-        <v>151.62040206946654</v>
+        <f t="shared" ref="BB50:DM50" si="129">BA50*(1+$BC$24)</f>
+        <v>106.48698320276972</v>
       </c>
       <c r="BC50" s="1">
-        <f t="shared" si="120"/>
-        <v>150.10419804877188</v>
+        <f t="shared" si="129"/>
+        <v>105.42211337074203</v>
       </c>
       <c r="BD50" s="1">
-        <f t="shared" si="120"/>
-        <v>148.60315606828416</v>
+        <f t="shared" si="129"/>
+        <v>104.36789223703461</v>
       </c>
       <c r="BE50" s="1">
-        <f t="shared" si="120"/>
-        <v>147.11712450760132</v>
+        <f t="shared" si="129"/>
+        <v>103.32421331466426</v>
       </c>
       <c r="BF50" s="1">
-        <f t="shared" si="120"/>
-        <v>145.6459532625253</v>
+        <f t="shared" si="129"/>
+        <v>102.29097118151762</v>
       </c>
       <c r="BG50" s="1">
-        <f t="shared" si="120"/>
-        <v>144.18949372990005</v>
+        <f t="shared" si="129"/>
+        <v>101.26806146970245</v>
       </c>
       <c r="BH50" s="1">
-        <f t="shared" si="120"/>
-        <v>142.74759879260105</v>
+        <f t="shared" si="129"/>
+        <v>100.25538085500541</v>
       </c>
       <c r="BI50" s="1">
-        <f t="shared" si="120"/>
-        <v>141.32012280467504</v>
+        <f t="shared" si="129"/>
+        <v>99.252827046455351</v>
       </c>
       <c r="BJ50" s="1">
-        <f t="shared" si="120"/>
-        <v>139.90692157662829</v>
+        <f t="shared" si="129"/>
+        <v>98.26029877599079</v>
       </c>
       <c r="BK50" s="1">
-        <f t="shared" si="120"/>
-        <v>138.50785236086202</v>
+        <f t="shared" si="129"/>
+        <v>97.277695788230886</v>
       </c>
       <c r="BL50" s="1">
-        <f t="shared" si="120"/>
-        <v>137.12277383725339</v>
+        <f t="shared" si="129"/>
+        <v>96.304918830348583</v>
       </c>
       <c r="BM50" s="1">
-        <f t="shared" si="120"/>
-        <v>135.75154609888085</v>
+        <f t="shared" si="129"/>
+        <v>95.341869642045097</v>
       </c>
       <c r="BN50" s="1">
-        <f t="shared" si="120"/>
-        <v>134.39403063789203</v>
+        <f t="shared" si="129"/>
+        <v>94.388450945624641</v>
       </c>
       <c r="BO50" s="1">
-        <f t="shared" si="120"/>
-        <v>133.0500903315131</v>
+        <f t="shared" si="129"/>
+        <v>93.444566436168387</v>
       </c>
       <c r="BP50" s="1">
-        <f t="shared" si="120"/>
-        <v>131.71958942819796</v>
+        <f t="shared" si="129"/>
+        <v>92.510120771806697</v>
       </c>
       <c r="BQ50" s="1">
-        <f t="shared" si="120"/>
-        <v>130.40239353391598</v>
+        <f t="shared" si="129"/>
+        <v>91.585019564088626</v>
       </c>
       <c r="BR50" s="1">
-        <f t="shared" si="120"/>
-        <v>129.09836959857682</v>
+        <f t="shared" si="129"/>
+        <v>90.66916936844774</v>
       </c>
       <c r="BS50" s="1">
-        <f t="shared" si="120"/>
-        <v>127.80738590259105</v>
+        <f t="shared" si="129"/>
+        <v>89.762477674763261</v>
       </c>
       <c r="BT50" s="1">
-        <f t="shared" si="120"/>
-        <v>126.52931204356514</v>
+        <f t="shared" si="129"/>
+        <v>88.864852898015627</v>
       </c>
       <c r="BU50" s="1">
-        <f t="shared" si="120"/>
-        <v>125.26401892312948</v>
+        <f t="shared" si="129"/>
+        <v>87.976204369035472</v>
       </c>
       <c r="BV50" s="1">
-        <f t="shared" si="120"/>
-        <v>124.01137873389818</v>
+        <f t="shared" si="129"/>
+        <v>87.096442325345123</v>
       </c>
       <c r="BW50" s="1">
-        <f t="shared" si="120"/>
-        <v>122.7712649465592</v>
+        <f t="shared" si="129"/>
+        <v>86.225477902091669</v>
       </c>
       <c r="BX50" s="1">
-        <f t="shared" si="120"/>
-        <v>121.54355229709361</v>
+        <f t="shared" si="129"/>
+        <v>85.363223123070753</v>
       </c>
       <c r="BY50" s="1">
-        <f t="shared" si="120"/>
-        <v>120.32811677412268</v>
+        <f t="shared" si="129"/>
+        <v>84.509590891840048</v>
       </c>
       <c r="BZ50" s="1">
-        <f t="shared" si="120"/>
-        <v>119.12483560638145</v>
+        <f t="shared" si="129"/>
+        <v>83.664494982921653</v>
       </c>
       <c r="CA50" s="1">
-        <f t="shared" si="120"/>
-        <v>117.93358725031764</v>
+        <f t="shared" si="129"/>
+        <v>82.827850033092432</v>
       </c>
       <c r="CB50" s="1">
-        <f t="shared" si="120"/>
-        <v>116.75425137781447</v>
+        <f t="shared" si="129"/>
+        <v>81.999571532761507</v>
       </c>
       <c r="CC50" s="1">
-        <f t="shared" si="120"/>
-        <v>115.58670886403632</v>
+        <f t="shared" si="129"/>
+        <v>81.179575817433886</v>
       </c>
       <c r="CD50" s="1">
-        <f t="shared" si="120"/>
-        <v>114.43084177539596</v>
+        <f t="shared" si="129"/>
+        <v>80.367780059259545</v>
       </c>
       <c r="CE50" s="1">
-        <f t="shared" si="120"/>
-        <v>113.286533357642</v>
+        <f t="shared" si="129"/>
+        <v>79.564102258666949</v>
       </c>
       <c r="CF50" s="1">
-        <f t="shared" si="120"/>
-        <v>112.15366802406558</v>
+        <f t="shared" si="129"/>
+        <v>78.768461236080284</v>
       </c>
       <c r="CG50" s="1">
-        <f t="shared" si="120"/>
-        <v>111.03213134382493</v>
+        <f t="shared" si="129"/>
+        <v>77.980776623719478</v>
       </c>
       <c r="CH50" s="1">
-        <f t="shared" si="120"/>
-        <v>109.92181003038668</v>
+        <f t="shared" si="129"/>
+        <v>77.20096885748228</v>
       </c>
       <c r="CI50" s="1">
-        <f t="shared" si="120"/>
-        <v>108.82259193008281</v>
+        <f t="shared" si="129"/>
+        <v>76.428959168907454</v>
       </c>
       <c r="CJ50" s="1">
-        <f t="shared" si="120"/>
-        <v>107.73436601078198</v>
+        <f t="shared" si="129"/>
+        <v>75.664669577218376</v>
       </c>
       <c r="CK50" s="1">
-        <f t="shared" si="120"/>
-        <v>106.65702235067417</v>
+        <f t="shared" si="129"/>
+        <v>74.908022881446186</v>
       </c>
       <c r="CL50" s="1">
-        <f t="shared" si="120"/>
-        <v>105.59045212716742</v>
+        <f t="shared" si="129"/>
+        <v>74.158942652631723</v>
       </c>
       <c r="CM50" s="1">
-        <f t="shared" si="120"/>
-        <v>104.53454760589575</v>
+        <f t="shared" si="129"/>
+        <v>73.417353226105405</v>
       </c>
       <c r="CN50" s="1">
-        <f t="shared" si="120"/>
-        <v>103.4892021298368</v>
+        <f t="shared" si="129"/>
+        <v>72.683179693844352</v>
       </c>
       <c r="CO50" s="1">
-        <f t="shared" si="120"/>
-        <v>102.45431010853842</v>
+        <f t="shared" si="129"/>
+        <v>71.95634789690591</v>
       </c>
       <c r="CP50" s="1">
-        <f t="shared" si="120"/>
-        <v>101.42976700745304</v>
+        <f t="shared" si="129"/>
+        <v>71.236784417936846</v>
       </c>
       <c r="CQ50" s="1">
-        <f t="shared" si="120"/>
-        <v>100.41546933737851</v>
+        <f t="shared" si="129"/>
+        <v>70.524416573757478</v>
       </c>
       <c r="CR50" s="1">
-        <f t="shared" si="120"/>
-        <v>99.411314644004719</v>
+        <f t="shared" si="129"/>
+        <v>69.819172408019895</v>
       </c>
       <c r="CS50" s="1">
-        <f t="shared" si="120"/>
-        <v>98.417201497564676</v>
+        <f t="shared" si="129"/>
+        <v>69.120980683939692</v>
       </c>
       <c r="CT50" s="1">
-        <f t="shared" si="120"/>
-        <v>97.433029482589035</v>
+        <f t="shared" si="129"/>
+        <v>68.429770877100296</v>
       </c>
       <c r="CU50" s="1">
-        <f t="shared" si="120"/>
-        <v>96.458699187763145</v>
+        <f t="shared" si="129"/>
+        <v>67.745473168329298</v>
       </c>
       <c r="CV50" s="1">
-        <f t="shared" si="120"/>
-        <v>95.494112195885506</v>
+        <f t="shared" si="129"/>
+        <v>67.068018436646</v>
       </c>
       <c r="CW50" s="1">
-        <f t="shared" si="120"/>
-        <v>94.539171073926653</v>
+        <f t="shared" si="129"/>
+        <v>66.397338252279539</v>
       </c>
       <c r="CX50" s="1">
-        <f t="shared" si="120"/>
-        <v>93.59377936318738</v>
+        <f t="shared" si="129"/>
+        <v>65.733364869756741</v>
       </c>
       <c r="CY50" s="1">
-        <f t="shared" si="120"/>
-        <v>92.657841569555501</v>
+        <f t="shared" si="129"/>
+        <v>65.076031221059168</v>
       </c>
       <c r="CZ50" s="1">
-        <f t="shared" si="120"/>
-        <v>91.731263153859942</v>
+        <f t="shared" si="129"/>
+        <v>64.425270908848574</v>
       </c>
       <c r="DA50" s="1">
-        <f t="shared" si="120"/>
-        <v>90.813950522321335</v>
+        <f t="shared" si="129"/>
+        <v>63.781018199760091</v>
       </c>
       <c r="DB50" s="1">
-        <f t="shared" si="120"/>
-        <v>89.905811017098117</v>
+        <f t="shared" si="129"/>
+        <v>63.14320801776249</v>
       </c>
       <c r="DC50" s="1">
-        <f t="shared" si="120"/>
-        <v>89.006752906927133</v>
+        <f t="shared" si="129"/>
+        <v>62.511775937584865</v>
       </c>
       <c r="DD50" s="1">
-        <f t="shared" si="120"/>
-        <v>88.116685377857863</v>
+        <f t="shared" si="129"/>
+        <v>61.886658178209018</v>
       </c>
       <c r="DE50" s="1">
-        <f t="shared" si="120"/>
-        <v>87.235518524079282</v>
+        <f t="shared" si="129"/>
+        <v>61.267791596426925</v>
       </c>
       <c r="DF50" s="1">
-        <f t="shared" si="120"/>
-        <v>86.36316333883849</v>
+        <f t="shared" si="129"/>
+        <v>60.655113680462655</v>
       </c>
       <c r="DG50" s="1">
-        <f t="shared" si="120"/>
-        <v>85.49953170545011</v>
+        <f t="shared" si="129"/>
+        <v>60.048562543658029</v>
       </c>
       <c r="DH50" s="1">
-        <f t="shared" si="120"/>
-        <v>84.644536388395608</v>
+        <f t="shared" si="129"/>
+        <v>59.448076918221446</v>
       </c>
       <c r="DI50" s="1">
-        <f t="shared" si="120"/>
-        <v>83.798091024511649</v>
+        <f t="shared" si="129"/>
+        <v>58.853596149039234</v>
       </c>
       <c r="DJ50" s="1">
-        <f t="shared" ref="DJ50:EM50" si="121">DI50*(1+$AY$24)</f>
-        <v>82.960110114266527</v>
+        <f t="shared" si="129"/>
+        <v>58.265060187548841</v>
       </c>
       <c r="DK50" s="1">
-        <f t="shared" si="121"/>
-        <v>82.130509013123856</v>
+        <f t="shared" si="129"/>
+        <v>57.682409585673355</v>
       </c>
       <c r="DL50" s="1">
-        <f t="shared" si="121"/>
-        <v>81.309203922992623</v>
+        <f t="shared" si="129"/>
+        <v>57.105585489816619</v>
       </c>
       <c r="DM50" s="1">
-        <f t="shared" si="121"/>
-        <v>80.496111883762694</v>
+        <f t="shared" si="129"/>
+        <v>56.534529634918449</v>
       </c>
       <c r="DN50" s="1">
-        <f t="shared" si="121"/>
-        <v>79.691150764925069</v>
+        <f t="shared" ref="DN50:EQ50" si="130">DM50*(1+$BC$24)</f>
+        <v>55.969184338569264</v>
       </c>
       <c r="DO50" s="1">
-        <f t="shared" si="121"/>
-        <v>78.894239257275814</v>
+        <f t="shared" si="130"/>
+        <v>55.409492495183571</v>
       </c>
       <c r="DP50" s="1">
-        <f t="shared" si="121"/>
-        <v>78.10529686470305</v>
+        <f t="shared" si="130"/>
+        <v>54.855397570231737</v>
       </c>
       <c r="DQ50" s="1">
-        <f t="shared" si="121"/>
-        <v>77.324243896056018</v>
+        <f t="shared" si="130"/>
+        <v>54.306843594529418</v>
       </c>
       <c r="DR50" s="1">
-        <f t="shared" si="121"/>
-        <v>76.551001457095452</v>
+        <f t="shared" si="130"/>
+        <v>53.763775158584124</v>
       </c>
       <c r="DS50" s="1">
-        <f t="shared" si="121"/>
-        <v>75.785491442524503</v>
+        <f t="shared" si="130"/>
+        <v>53.226137406998284</v>
       </c>
       <c r="DT50" s="1">
-        <f t="shared" si="121"/>
-        <v>75.027636528099251</v>
+        <f t="shared" si="130"/>
+        <v>52.693876032928301</v>
       </c>
       <c r="DU50" s="1">
-        <f t="shared" si="121"/>
-        <v>74.277360162818255</v>
+        <f t="shared" si="130"/>
+        <v>52.166937272599014</v>
       </c>
       <c r="DV50" s="1">
-        <f t="shared" si="121"/>
-        <v>73.534586561190068</v>
+        <f t="shared" si="130"/>
+        <v>51.645267899873026</v>
       </c>
       <c r="DW50" s="1">
-        <f t="shared" si="121"/>
-        <v>72.799240695578163</v>
+        <f t="shared" si="130"/>
+        <v>51.128815220874294</v>
       </c>
       <c r="DX50" s="1">
-        <f t="shared" si="121"/>
-        <v>72.071248288622385</v>
+        <f t="shared" si="130"/>
+        <v>50.617527068665552</v>
       </c>
       <c r="DY50" s="1">
-        <f t="shared" si="121"/>
-        <v>71.350535805736158</v>
+        <f t="shared" si="130"/>
+        <v>50.111351797978898</v>
       </c>
       <c r="DZ50" s="1">
-        <f t="shared" si="121"/>
-        <v>70.637030447678796</v>
+        <f t="shared" si="130"/>
+        <v>49.610238279999109</v>
       </c>
       <c r="EA50" s="1">
-        <f t="shared" si="121"/>
-        <v>69.930660143202005</v>
+        <f t="shared" si="130"/>
+        <v>49.11413589719912</v>
       </c>
       <c r="EB50" s="1">
-        <f t="shared" si="121"/>
-        <v>69.231353541769977</v>
+        <f t="shared" si="130"/>
+        <v>48.622994538227125</v>
       </c>
       <c r="EC50" s="1">
-        <f t="shared" si="121"/>
-        <v>68.53904000635228</v>
+        <f t="shared" si="130"/>
+        <v>48.136764592844855</v>
       </c>
       <c r="ED50" s="1">
-        <f t="shared" si="121"/>
-        <v>67.853649606288755</v>
+        <f t="shared" si="130"/>
+        <v>47.655396946916404</v>
       </c>
       <c r="EE50" s="1">
-        <f t="shared" si="121"/>
-        <v>67.175113110225865</v>
+        <f t="shared" si="130"/>
+        <v>47.178842977447239</v>
       </c>
       <c r="EF50" s="1">
-        <f t="shared" si="121"/>
-        <v>66.503361979123611</v>
+        <f t="shared" si="130"/>
+        <v>46.707054547672769</v>
       </c>
       <c r="EG50" s="1">
-        <f t="shared" si="121"/>
-        <v>65.83832835933238</v>
+        <f t="shared" si="130"/>
+        <v>46.239984002196039</v>
       </c>
       <c r="EH50" s="1">
-        <f t="shared" si="121"/>
-        <v>65.179945075739056</v>
+        <f t="shared" si="130"/>
+        <v>45.77758416217408</v>
       </c>
       <c r="EI50" s="1">
-        <f t="shared" si="121"/>
-        <v>64.528145624981661</v>
+        <f t="shared" si="130"/>
+        <v>45.31980832055234</v>
       </c>
       <c r="EJ50" s="1">
-        <f t="shared" si="121"/>
-        <v>63.882864168731842</v>
+        <f t="shared" si="130"/>
+        <v>44.866610237346819</v>
       </c>
       <c r="EK50" s="1">
-        <f t="shared" si="121"/>
-        <v>63.244035527044524</v>
+        <f t="shared" si="130"/>
+        <v>44.417944134973354</v>
       </c>
       <c r="EL50" s="1">
-        <f t="shared" si="121"/>
-        <v>62.611595171774077</v>
+        <f t="shared" si="130"/>
+        <v>43.973764693623622</v>
       </c>
       <c r="EM50" s="1">
-        <f t="shared" si="121"/>
-        <v>61.985479220056334</v>
+        <f t="shared" si="130"/>
+        <v>43.534027046687385</v>
+      </c>
+      <c r="EN50" s="1">
+        <f t="shared" si="130"/>
+        <v>43.098686776220511</v>
+      </c>
+      <c r="EO50" s="1">
+        <f t="shared" si="130"/>
+        <v>42.667699908458303</v>
+      </c>
+      <c r="EP50" s="1">
+        <f t="shared" si="130"/>
+        <v>42.241022909373719</v>
+      </c>
+      <c r="EQ50" s="1">
+        <f t="shared" si="130"/>
+        <v>41.818612680279983</v>
       </c>
     </row>
-    <row r="52" spans="2:143" x14ac:dyDescent="0.3">
-      <c r="AX52" t="s">
+    <row r="52" spans="2:147" x14ac:dyDescent="0.3">
+      <c r="BB52" t="s">
         <v>83</v>
       </c>
-      <c r="AY52" s="4">
-        <f>NPV(AY25,AL50:EM50)</f>
-        <v>1058.943988523564</v>
+      <c r="BC52" s="4">
+        <f>NPV(BC25,AP50:EQ50)</f>
+        <v>581.55785087338427</v>
       </c>
     </row>
-    <row r="53" spans="2:143" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:147" x14ac:dyDescent="0.3">
       <c r="W53" s="4"/>
       <c r="AA53" s="4"/>
-      <c r="AX53" t="s">
+      <c r="BB53" t="s">
         <v>41</v>
       </c>
-      <c r="AY53" s="4">
+      <c r="BC53" s="4">
         <f>Main!D8</f>
-        <v>-56.899999999999977</v>
+        <v>-22.700000000000003</v>
       </c>
     </row>
-    <row r="54" spans="2:143" x14ac:dyDescent="0.3">
-      <c r="AX54" t="s">
+    <row r="54" spans="2:147" x14ac:dyDescent="0.3">
+      <c r="BB54" t="s">
         <v>42</v>
       </c>
-      <c r="AY54" s="4">
-        <f>AY52+AY53</f>
-        <v>1002.0439885235641</v>
+      <c r="BC54" s="4">
+        <f>BC52+BC53</f>
+        <v>558.85785087338422</v>
       </c>
     </row>
-    <row r="55" spans="2:143" x14ac:dyDescent="0.3">
-      <c r="AX55" t="s">
+    <row r="55" spans="2:147" x14ac:dyDescent="0.3">
+      <c r="BB55" t="s">
         <v>43</v>
       </c>
-      <c r="AY55" s="5">
-        <f>AY54/AV17</f>
-        <v>9.4000374157932836</v>
+      <c r="BC55" s="5">
+        <f>BC54/AZ17</f>
+        <v>5.242568957536438</v>
       </c>
     </row>
-    <row r="56" spans="2:143" x14ac:dyDescent="0.3">
-      <c r="AX56" t="s">
+    <row r="56" spans="2:147" x14ac:dyDescent="0.3">
+      <c r="BB56" t="s">
         <v>44</v>
       </c>
-      <c r="AY56" s="5">
+      <c r="BC56" s="5">
         <f>Main!D3</f>
-        <v>5.04</v>
+        <v>6.79</v>
       </c>
     </row>
-    <row r="57" spans="2:143" x14ac:dyDescent="0.3">
-      <c r="AX57" s="1" t="s">
+    <row r="57" spans="2:147" x14ac:dyDescent="0.3">
+      <c r="BB57" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AY57" s="10">
-        <f>AY55/AY56-1</f>
-        <v>0.86508678884787371</v>
+      <c r="BC57" s="10">
+        <f>BC55/BC56-1</f>
+        <v>-0.22789853349978817</v>
       </c>
     </row>
-    <row r="58" spans="2:143" x14ac:dyDescent="0.3">
-      <c r="AY58" s="6" t="s">
-        <v>92</v>
+    <row r="58" spans="2:147" x14ac:dyDescent="0.3">
+      <c r="BC58" s="6" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.3">
